--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="236">
   <si>
     <t>id</t>
   </si>
@@ -551,7 +551,7 @@
     <t>第1轴改出1个scatter+第3轴改出1个scatter+第1轴改出5个scatter</t>
   </si>
   <si>
-    <t>10200006|10200007|10200011</t>
+    <t>10200006|10200007|10200015</t>
   </si>
   <si>
     <t>第1轴改出1个scatter+第3轴改出1个scatter+第5轴改出奖池符号</t>
@@ -761,31 +761,46 @@
     <t>寻宝黄金城</t>
   </si>
   <si>
-    <t>10260001|10260004|10260005|10260006|10260007</t>
-  </si>
-  <si>
-    <t>概率改出百搭wild符号+概率改出scatter符号+概率改出占据2、3、4个格子符号</t>
-  </si>
-  <si>
-    <t>10260003|10260008</t>
+    <t>10260001|10260004|10260005|10260006|10260007|10260010</t>
+  </si>
+  <si>
+    <t>概率改出百搭wild符号+概率改出scatter符号+概率改出占据2、3、4个格子符号+异形位置不中奖</t>
+  </si>
+  <si>
+    <t>10260002|10260010</t>
+  </si>
+  <si>
+    <t>10260003|10260008|10260010</t>
   </si>
   <si>
     <t>澳门壕梦</t>
   </si>
   <si>
-    <t>10500001|10500004|10500005|10500006|10500007</t>
-  </si>
-  <si>
-    <t>概率改出wild+概率改出scatter符号+概率改出占据2、3、4格子的普通符号</t>
-  </si>
-  <si>
-    <t>改出4个或以上个数SCATTER</t>
-  </si>
-  <si>
-    <t>10500003|10500008</t>
-  </si>
-  <si>
-    <t>改出3个scatter符号+改出奖池符号</t>
+    <t>10500001|10500004|10500005|10500006|10500007|10500010</t>
+  </si>
+  <si>
+    <t>概率改出wild+概率改出scatter符号+概率改出占据2、3、4格子的普通符号+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>10500002|10500010</t>
+  </si>
+  <si>
+    <t>改出4个或以上个数SCATTER+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>10500003|10500008|10500010</t>
+  </si>
+  <si>
+    <t>改出3个scatter符号+改出奖池符号+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>免费模式</t>
+  </si>
+  <si>
+    <t>10500009|10500010</t>
+  </si>
+  <si>
+    <t>概率改出SCATTER符号+异形位置改为不中奖图案</t>
   </si>
   <si>
     <t>糖果派对</t>
@@ -2215,7 +2230,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S116"/>
+  <dimension ref="A1:S117"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -4767,7 +4782,7 @@
     </row>
     <row r="61" customFormat="1" ht="16.5" spans="1:17">
       <c r="A61" s="5" t="str">
-        <f>B61&amp;C61</f>
+        <f t="shared" si="3"/>
         <v>1036002</v>
       </c>
       <c r="B61" s="5">
@@ -6735,7 +6750,7 @@
         <v>6</v>
       </c>
       <c r="O106" s="47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q106" s="20"/>
     </row>
@@ -6768,8 +6783,8 @@
       <c r="I107" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L107" s="48">
-        <v>10260002</v>
+      <c r="L107" s="48" t="s">
+        <v>213</v>
       </c>
       <c r="M107" s="5" t="s">
         <v>194</v>
@@ -6778,7 +6793,7 @@
         <v>6</v>
       </c>
       <c r="O107" s="47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q107" s="20"/>
     </row>
@@ -6812,7 +6827,7 @@
         <v>24</v>
       </c>
       <c r="L108" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M108" s="5" t="s">
         <v>196</v>
@@ -6821,7 +6836,7 @@
         <v>6</v>
       </c>
       <c r="O108" s="47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q108" s="20"/>
     </row>
@@ -6836,7 +6851,7 @@
         <v>1</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>111</v>
@@ -6854,13 +6869,13 @@
         <v>24</v>
       </c>
       <c r="L109" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M109" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N109" s="47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O109" s="47">
         <v>6</v>
@@ -6878,7 +6893,7 @@
         <v>2</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>132</v>
@@ -6895,14 +6910,14 @@
       <c r="I110" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L110" s="48">
-        <v>10500002</v>
+      <c r="L110" s="48" t="s">
+        <v>218</v>
       </c>
       <c r="M110" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N110" s="47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O110" s="47">
         <v>6</v>
@@ -6921,7 +6936,7 @@
         <v>3</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E111" s="5" t="s">
         <v>81</v>
@@ -6939,13 +6954,13 @@
         <v>24</v>
       </c>
       <c r="L111" s="48" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M111" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N111" s="47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O111" s="47">
         <v>6</v>
@@ -6954,19 +6969,19 @@
     </row>
     <row r="112" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A112" s="48">
-        <v>1051001</v>
+        <v>1050004</v>
       </c>
       <c r="B112" s="5">
-        <v>105100</v>
+        <v>105000</v>
       </c>
       <c r="C112" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F112" s="5">
         <v>1</v>
@@ -6975,16 +6990,16 @@
         <v>23</v>
       </c>
       <c r="H112" s="5">
-        <v>2051001</v>
+        <v>2050001</v>
       </c>
       <c r="I112" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L112" s="48">
-        <v>10510008</v>
+      <c r="L112" s="48" t="s">
+        <v>223</v>
       </c>
       <c r="M112" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N112" s="47">
         <v>6</v>
@@ -6994,21 +7009,21 @@
       </c>
       <c r="Q112" s="20"/>
     </row>
-    <row r="113" customFormat="1" ht="16.5" spans="1:17">
+    <row r="113" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A113" s="48">
-        <v>1051002</v>
+        <v>1051001</v>
       </c>
       <c r="B113" s="5">
         <v>105100</v>
       </c>
       <c r="C113" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="E113" t="s">
-        <v>223</v>
+        <v>225</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>226</v>
       </c>
       <c r="F113" s="5">
         <v>1</v>
@@ -7022,11 +7037,11 @@
       <c r="I113" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L113" s="48" t="s">
-        <v>224</v>
-      </c>
-      <c r="M113" t="s">
-        <v>225</v>
+      <c r="L113" s="48">
+        <v>10510008</v>
+      </c>
+      <c r="M113" s="5" t="s">
+        <v>227</v>
       </c>
       <c r="N113" s="47">
         <v>6</v>
@@ -7034,23 +7049,23 @@
       <c r="O113" s="47">
         <v>6</v>
       </c>
-      <c r="Q113" s="10"/>
+      <c r="Q113" s="20"/>
     </row>
     <row r="114" customFormat="1" ht="16.5" spans="1:17">
       <c r="A114" s="48">
-        <v>1051003</v>
+        <v>1051002</v>
       </c>
       <c r="B114" s="5">
         <v>105100</v>
       </c>
       <c r="C114" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E114" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F114" s="5">
         <v>1</v>
@@ -7065,10 +7080,10 @@
         <v>24</v>
       </c>
       <c r="L114" s="48" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M114" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N114" s="47">
         <v>6</v>
@@ -7080,19 +7095,19 @@
     </row>
     <row r="115" customFormat="1" ht="16.5" spans="1:17">
       <c r="A115" s="48">
-        <v>1051004</v>
+        <v>1051003</v>
       </c>
       <c r="B115" s="5">
         <v>105100</v>
       </c>
       <c r="C115" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E115" t="s">
-        <v>132</v>
+        <v>231</v>
       </c>
       <c r="F115" s="5">
         <v>1</v>
@@ -7106,11 +7121,11 @@
       <c r="I115" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L115" s="48">
-        <v>10510005</v>
+      <c r="L115" s="48" t="s">
+        <v>232</v>
       </c>
       <c r="M115" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="N115" s="47">
         <v>6</v>
@@ -7122,19 +7137,19 @@
     </row>
     <row r="116" customFormat="1" ht="16.5" spans="1:17">
       <c r="A116" s="48">
-        <v>1051005</v>
+        <v>1051004</v>
       </c>
       <c r="B116" s="5">
         <v>105100</v>
       </c>
       <c r="C116" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E116" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="F116" s="5">
         <v>1</v>
@@ -7149,10 +7164,10 @@
         <v>24</v>
       </c>
       <c r="L116" s="48">
-        <v>10510009</v>
+        <v>10510005</v>
       </c>
       <c r="M116" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="N116" s="47">
         <v>6</v>
@@ -7161,6 +7176,48 @@
         <v>6</v>
       </c>
       <c r="Q116" s="10"/>
+    </row>
+    <row r="117" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A117" s="48">
+        <v>1051005</v>
+      </c>
+      <c r="B117" s="5">
+        <v>105100</v>
+      </c>
+      <c r="C117" s="5">
+        <v>5</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E117" t="s">
+        <v>81</v>
+      </c>
+      <c r="F117" s="5">
+        <v>1</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H117" s="5">
+        <v>2051001</v>
+      </c>
+      <c r="I117" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L117" s="48">
+        <v>10510009</v>
+      </c>
+      <c r="M117" t="s">
+        <v>235</v>
+      </c>
+      <c r="N117" s="47">
+        <v>6</v>
+      </c>
+      <c r="O117" s="47">
+        <v>6</v>
+      </c>
+      <c r="Q117" s="10"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="264">
   <si>
     <t>id</t>
   </si>
@@ -878,13 +878,13 @@
     <t>麻将胡了2</t>
   </si>
   <si>
-    <t>10530001|10530005|10530006|10530007|10530008|10530009|10530010|10530011|10530012|10530013|10530014|10530015|10530016</t>
-  </si>
-  <si>
-    <t>概率改出wild百搭符号+概率改出scatter+概率出金色图标+异形位置改为不中奖图案</t>
-  </si>
-  <si>
-    <t>10530003|10530016</t>
+    <t>10530001|10530004|10530005</t>
+  </si>
+  <si>
+    <t>概率出现3个以下SCATTER+概率出金色图标+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>10530002|10530005</t>
   </si>
   <si>
     <t>概率改出3个scatter+异形位置改为不中奖图案</t>
@@ -893,19 +893,19 @@
     <t>赏金大对决</t>
   </si>
   <si>
-    <t>10570001|10570002|10570006|10570015</t>
-  </si>
-  <si>
-    <t>概率改出百搭wild符号+概率改出scatter符号+概率改出金框符号+异形位置改为不中奖图案</t>
-  </si>
-  <si>
-    <t>10570003|10570015</t>
+    <t>10570001|10570004|10570006</t>
+  </si>
+  <si>
+    <t>概率改出scatter符号+概率改出金框符号+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>10570002|10570006</t>
   </si>
   <si>
     <t>改出3个以上SCATTER+异形位置改为不中奖图案</t>
   </si>
   <si>
-    <t>10570005|10570004|10570015</t>
+    <t>10570001|10570005|10570006</t>
   </si>
   <si>
     <t>改出2个SCATTER+奖池符号+异形位置改为不中奖图案</t>
@@ -915,9 +915,6 @@
   </si>
   <si>
     <t>概率改出scatter</t>
-  </si>
-  <si>
-    <t>概率改出3个SCATTER</t>
   </si>
   <si>
     <t>奖池符号</t>
@@ -6928,7 +6925,8 @@
       <c r="Q108" s="20"/>
     </row>
     <row r="109" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A109" s="5">
+      <c r="A109" s="5" t="str">
+        <f t="shared" ref="A109:A132" si="4">B109&amp;C109</f>
         <v>1050001</v>
       </c>
       <c r="B109" s="5">
@@ -6970,7 +6968,8 @@
       <c r="Q109" s="20"/>
     </row>
     <row r="110" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A110" s="5">
+      <c r="A110" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1050002</v>
       </c>
       <c r="B110" s="5">
@@ -7013,7 +7012,8 @@
       <c r="Q110" s="20"/>
     </row>
     <row r="111" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A111" s="5">
+      <c r="A111" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1050003</v>
       </c>
       <c r="B111" s="5">
@@ -7055,7 +7055,8 @@
       <c r="Q111" s="20"/>
     </row>
     <row r="112" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A112" s="5">
+      <c r="A112" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1050004</v>
       </c>
       <c r="B112" s="5">
@@ -7097,7 +7098,8 @@
       <c r="Q112" s="20"/>
     </row>
     <row r="113" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A113" s="5">
+      <c r="A113" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1051001</v>
       </c>
       <c r="B113" s="5">
@@ -7139,7 +7141,8 @@
       <c r="Q113" s="20"/>
     </row>
     <row r="114" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A114" s="5">
+      <c r="A114" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1051002</v>
       </c>
       <c r="B114" s="5">
@@ -7181,7 +7184,8 @@
       <c r="Q114" s="20"/>
     </row>
     <row r="115" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A115" s="5">
+      <c r="A115" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1051003</v>
       </c>
       <c r="B115" s="5">
@@ -7223,7 +7227,8 @@
       <c r="Q115" s="20"/>
     </row>
     <row r="116" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A116" s="5">
+      <c r="A116" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1051004</v>
       </c>
       <c r="B116" s="5">
@@ -7265,7 +7270,8 @@
       <c r="Q116" s="20"/>
     </row>
     <row r="117" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A117" s="5">
+      <c r="A117" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1051005</v>
       </c>
       <c r="B117" s="5">
@@ -7307,7 +7313,8 @@
       <c r="Q117" s="20"/>
     </row>
     <row r="118" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A118" s="5">
+      <c r="A118" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1054001</v>
       </c>
       <c r="B118" s="5">
@@ -7349,7 +7356,8 @@
       <c r="Q118" s="20"/>
     </row>
     <row r="119" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A119" s="5">
+      <c r="A119" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1054002</v>
       </c>
       <c r="B119" s="5">
@@ -7391,7 +7399,8 @@
       <c r="Q119" s="20"/>
     </row>
     <row r="120" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A120" s="5">
+      <c r="A120" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1054003</v>
       </c>
       <c r="B120" s="5">
@@ -7433,7 +7442,8 @@
       <c r="Q120" s="20"/>
     </row>
     <row r="121" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A121" s="5">
+      <c r="A121" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1054004</v>
       </c>
       <c r="B121" s="5">
@@ -7475,7 +7485,8 @@
       <c r="Q121" s="20"/>
     </row>
     <row r="122" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A122" s="5">
+      <c r="A122" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1008001</v>
       </c>
       <c r="B122" s="5">
@@ -7517,7 +7528,8 @@
       <c r="Q122" s="20"/>
     </row>
     <row r="123" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A123" s="5">
+      <c r="A123" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1008002</v>
       </c>
       <c r="B123" s="5">
@@ -7559,7 +7571,8 @@
       <c r="Q123" s="20"/>
     </row>
     <row r="124" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A124" s="5">
+      <c r="A124" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1008003</v>
       </c>
       <c r="B124" s="5">
@@ -7601,7 +7614,8 @@
       <c r="Q124" s="20"/>
     </row>
     <row r="125" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A125" s="5">
+      <c r="A125" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1053001</v>
       </c>
       <c r="B125" s="5">
@@ -7645,7 +7659,8 @@
       <c r="Q125" s="20"/>
     </row>
     <row r="126" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A126" s="5">
+      <c r="A126" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1053002</v>
       </c>
       <c r="B126" s="5">
@@ -7689,7 +7704,8 @@
       <c r="Q126" s="20"/>
     </row>
     <row r="127" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A127" s="5">
+      <c r="A127" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1057001</v>
       </c>
       <c r="B127" s="5">
@@ -7731,7 +7747,8 @@
       <c r="Q127" s="20"/>
     </row>
     <row r="128" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A128" s="5">
+      <c r="A128" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1057002</v>
       </c>
       <c r="B128" s="5">
@@ -7773,7 +7790,8 @@
       <c r="Q128" s="20"/>
     </row>
     <row r="129" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A129" s="5">
+      <c r="A129" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1057003</v>
       </c>
       <c r="B129" s="5">
@@ -7815,7 +7833,8 @@
       <c r="Q129" s="20"/>
     </row>
     <row r="130" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A130" s="5">
+      <c r="A130" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1058001</v>
       </c>
       <c r="B130" s="5">
@@ -7857,7 +7876,8 @@
       <c r="Q130" s="20"/>
     </row>
     <row r="131" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A131" s="5">
+      <c r="A131" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1058002</v>
       </c>
       <c r="B131" s="5">
@@ -7888,7 +7908,7 @@
         <v>10580002</v>
       </c>
       <c r="M131" s="5" t="s">
-        <v>263</v>
+        <v>171</v>
       </c>
       <c r="N131" s="47">
         <v>7</v>
@@ -7899,7 +7919,8 @@
       <c r="Q131" s="20"/>
     </row>
     <row r="132" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A132" s="5">
+      <c r="A132" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1058003</v>
       </c>
       <c r="B132" s="5">
@@ -7927,10 +7948,10 @@
         <v>24</v>
       </c>
       <c r="L132" s="48">
-        <v>10580003</v>
+        <v>10580004</v>
       </c>
       <c r="M132" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N132" s="47">
         <v>7</v>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="269">
   <si>
     <t>id</t>
   </si>
@@ -806,34 +806,49 @@
     <t>糖果派对</t>
   </si>
   <si>
-    <t>常规模式（第三层）</t>
-  </si>
-  <si>
-    <t>概率改出过关图标3</t>
-  </si>
-  <si>
-    <t>第二层模式</t>
-  </si>
-  <si>
-    <t>10510001|10510006</t>
-  </si>
-  <si>
-    <t>一定改出透明图标+概率改出过关图标1</t>
-  </si>
-  <si>
-    <t>第一层模式</t>
-  </si>
-  <si>
-    <t>10510002|10510007</t>
-  </si>
-  <si>
-    <t>一定改出透明图标+概率改出过关图标2</t>
-  </si>
-  <si>
-    <t>概率改出免费游戏图标</t>
-  </si>
-  <si>
-    <t>改出1-4个彩池图标</t>
+    <t>第1层，免费游戏-触发局</t>
+  </si>
+  <si>
+    <t>第1层，概率改出免费游戏图标</t>
+  </si>
+  <si>
+    <t>第2层，免费游戏-触发局</t>
+  </si>
+  <si>
+    <t>第2层，概率改出免费游戏图标</t>
+  </si>
+  <si>
+    <t>第3层，免费游戏-触发局</t>
+  </si>
+  <si>
+    <t>第3层，概率改出免费游戏图标</t>
+  </si>
+  <si>
+    <t>第1层，JACKPOT大奖</t>
+  </si>
+  <si>
+    <t>第1层，概率改出彩池图标</t>
+  </si>
+  <si>
+    <t>第2层，JACKPOT大奖</t>
+  </si>
+  <si>
+    <t>第2层，概率改出彩池图标</t>
+  </si>
+  <si>
+    <t>第3层，JACKPOT大奖</t>
+  </si>
+  <si>
+    <t>第3层，概率改出彩池图标</t>
+  </si>
+  <si>
+    <t>第1层，普通模式</t>
+  </si>
+  <si>
+    <t>第2层，普通模式</t>
+  </si>
+  <si>
+    <t>第3层，普通模式</t>
   </si>
   <si>
     <t>黄金帝国</t>
@@ -917,7 +932,7 @@
     <t>概率改出scatter</t>
   </si>
   <si>
-    <t>奖池符号</t>
+    <t>伽罗宝石</t>
   </si>
 </sst>
 </file>
@@ -2314,7 +2329,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S132"/>
+  <dimension ref="A1:S138"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -6926,7 +6941,7 @@
     </row>
     <row r="109" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A109" s="5" t="str">
-        <f t="shared" ref="A109:A132" si="4">B109&amp;C109</f>
+        <f t="shared" ref="A109:A115" si="4">B109&amp;C109</f>
         <v>1050001</v>
       </c>
       <c r="B109" s="5">
@@ -7098,8 +7113,7 @@
       <c r="Q112" s="20"/>
     </row>
     <row r="113" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A113" s="5" t="str">
-        <f t="shared" si="4"/>
+      <c r="A113" s="48">
         <v>1051001</v>
       </c>
       <c r="B113" s="5">
@@ -7127,22 +7141,21 @@
         <v>24</v>
       </c>
       <c r="L113" s="48">
-        <v>10510008</v>
+        <v>10510001</v>
       </c>
       <c r="M113" s="5" t="s">
         <v>227</v>
       </c>
       <c r="N113" s="47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O113" s="47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q113" s="20"/>
     </row>
     <row r="114" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A114" s="5" t="str">
-        <f t="shared" si="4"/>
+      <c r="A114" s="48">
         <v>1051002</v>
       </c>
       <c r="B114" s="5">
@@ -7164,28 +7177,27 @@
         <v>23</v>
       </c>
       <c r="H114" s="5">
-        <v>2051001</v>
+        <v>2051002</v>
       </c>
       <c r="I114" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L114" s="48" t="s">
+      <c r="L114" s="48">
+        <v>10510002</v>
+      </c>
+      <c r="M114" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="M114" s="5" t="s">
-        <v>230</v>
-      </c>
       <c r="N114" s="47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O114" s="47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q114" s="20"/>
     </row>
     <row r="115" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A115" s="5" t="str">
-        <f t="shared" si="4"/>
+      <c r="A115" s="48">
         <v>1051003</v>
       </c>
       <c r="B115" s="5">
@@ -7198,25 +7210,25 @@
         <v>225</v>
       </c>
       <c r="E115" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F115" s="5">
+        <v>1</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H115" s="5">
+        <v>2051003</v>
+      </c>
+      <c r="I115" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L115" s="48">
+        <v>10510003</v>
+      </c>
+      <c r="M115" s="5" t="s">
         <v>231</v>
-      </c>
-      <c r="F115" s="5">
-        <v>1</v>
-      </c>
-      <c r="G115" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H115" s="5">
-        <v>2051001</v>
-      </c>
-      <c r="I115" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L115" s="48" t="s">
-        <v>232</v>
-      </c>
-      <c r="M115" s="5" t="s">
-        <v>233</v>
       </c>
       <c r="N115" s="47">
         <v>6</v>
@@ -7227,8 +7239,7 @@
       <c r="Q115" s="20"/>
     </row>
     <row r="116" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A116" s="5" t="str">
-        <f t="shared" si="4"/>
+      <c r="A116" s="48">
         <v>1051004</v>
       </c>
       <c r="B116" s="5">
@@ -7241,7 +7252,7 @@
         <v>225</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>132</v>
+        <v>232</v>
       </c>
       <c r="F116" s="5">
         <v>1</v>
@@ -7256,22 +7267,21 @@
         <v>24</v>
       </c>
       <c r="L116" s="48">
-        <v>10510005</v>
+        <v>10510004</v>
       </c>
       <c r="M116" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N116" s="47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O116" s="47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q116" s="20"/>
     </row>
     <row r="117" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A117" s="5" t="str">
-        <f t="shared" si="4"/>
+      <c r="A117" s="48">
         <v>1051005</v>
       </c>
       <c r="B117" s="5">
@@ -7284,7 +7294,7 @@
         <v>225</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>81</v>
+        <v>234</v>
       </c>
       <c r="F117" s="5">
         <v>1</v>
@@ -7293,42 +7303,41 @@
         <v>23</v>
       </c>
       <c r="H117" s="5">
-        <v>2051001</v>
+        <v>2051002</v>
       </c>
       <c r="I117" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L117" s="48">
-        <v>10510009</v>
+        <v>10510005</v>
       </c>
       <c r="M117" s="5" t="s">
         <v>235</v>
       </c>
       <c r="N117" s="47">
+        <v>5</v>
+      </c>
+      <c r="O117" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q117" s="20"/>
+    </row>
+    <row r="118" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A118" s="48">
+        <v>1051006</v>
+      </c>
+      <c r="B118" s="5">
+        <v>105100</v>
+      </c>
+      <c r="C118" s="5">
         <v>6</v>
       </c>
-      <c r="O117" s="47">
-        <v>6</v>
-      </c>
-      <c r="Q117" s="20"/>
-    </row>
-    <row r="118" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A118" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>1054001</v>
-      </c>
-      <c r="B118" s="5">
-        <v>105400</v>
-      </c>
-      <c r="C118" s="5">
-        <v>1</v>
-      </c>
       <c r="D118" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E118" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="E118" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="F118" s="5">
         <v>1</v>
       </c>
@@ -7336,16 +7345,16 @@
         <v>23</v>
       </c>
       <c r="H118" s="5">
-        <v>2054001</v>
+        <v>2051003</v>
       </c>
       <c r="I118" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L118" s="48" t="s">
+      <c r="L118" s="48">
+        <v>10510006</v>
+      </c>
+      <c r="M118" s="5" t="s">
         <v>237</v>
-      </c>
-      <c r="M118" s="5" t="s">
-        <v>238</v>
       </c>
       <c r="N118" s="47">
         <v>6</v>
@@ -7356,21 +7365,20 @@
       <c r="Q118" s="20"/>
     </row>
     <row r="119" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A119" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>1054002</v>
+      <c r="A119" s="48">
+        <v>1051007</v>
       </c>
       <c r="B119" s="5">
-        <v>105400</v>
+        <v>105100</v>
       </c>
       <c r="C119" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>132</v>
+        <v>238</v>
       </c>
       <c r="F119" s="5">
         <v>1</v>
@@ -7379,85 +7387,73 @@
         <v>23</v>
       </c>
       <c r="H119" s="5">
-        <v>2054001</v>
+        <v>2051001</v>
       </c>
       <c r="I119" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L119" s="48" t="s">
+      <c r="L119" s="48"/>
+      <c r="N119" s="47">
+        <v>4</v>
+      </c>
+      <c r="O119" s="47">
+        <v>4</v>
+      </c>
+      <c r="Q119" s="20"/>
+    </row>
+    <row r="120" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A120" s="48">
+        <v>1051008</v>
+      </c>
+      <c r="B120" s="5">
+        <v>105100</v>
+      </c>
+      <c r="C120" s="5">
+        <v>8</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E120" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="M119" s="5" t="s">
+      <c r="F120" s="5">
+        <v>1</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H120" s="5">
+        <v>2051002</v>
+      </c>
+      <c r="I120" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L120" s="48"/>
+      <c r="N120" s="47">
+        <v>5</v>
+      </c>
+      <c r="O120" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q120" s="20"/>
+    </row>
+    <row r="121" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A121" s="48">
+        <v>1051009</v>
+      </c>
+      <c r="B121" s="5">
+        <v>105100</v>
+      </c>
+      <c r="C121" s="5">
+        <v>9</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E121" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="N119" s="47">
-        <v>6</v>
-      </c>
-      <c r="O119" s="47">
-        <v>6</v>
-      </c>
-      <c r="Q119" s="20"/>
-    </row>
-    <row r="120" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A120" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>1054003</v>
-      </c>
-      <c r="B120" s="5">
-        <v>105400</v>
-      </c>
-      <c r="C120" s="5">
-        <v>3</v>
-      </c>
-      <c r="D120" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="E120" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F120" s="5">
-        <v>1</v>
-      </c>
-      <c r="G120" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H120" s="5">
-        <v>2054001</v>
-      </c>
-      <c r="I120" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L120" s="48" t="s">
-        <v>241</v>
-      </c>
-      <c r="M120" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="N120" s="47">
-        <v>6</v>
-      </c>
-      <c r="O120" s="47">
-        <v>6</v>
-      </c>
-      <c r="Q120" s="20"/>
-    </row>
-    <row r="121" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A121" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>1054004</v>
-      </c>
-      <c r="B121" s="5">
-        <v>105400</v>
-      </c>
-      <c r="C121" s="5">
-        <v>4</v>
-      </c>
-      <c r="D121" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>222</v>
-      </c>
       <c r="F121" s="5">
         <v>1</v>
       </c>
@@ -7465,17 +7461,12 @@
         <v>23</v>
       </c>
       <c r="H121" s="5">
-        <v>2054001</v>
+        <v>2051003</v>
       </c>
       <c r="I121" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L121" s="48" t="s">
-        <v>243</v>
-      </c>
-      <c r="M121" s="5" t="s">
-        <v>224</v>
-      </c>
+      <c r="L121" s="48"/>
       <c r="N121" s="47">
         <v>6</v>
       </c>
@@ -7486,17 +7477,17 @@
     </row>
     <row r="122" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A122" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>1008001</v>
+        <f t="shared" ref="A122:A136" si="5">B122&amp;C122</f>
+        <v>1054001</v>
       </c>
       <c r="B122" s="5">
-        <v>100800</v>
+        <v>105400</v>
       </c>
       <c r="C122" s="5">
         <v>1</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E122" s="5" t="s">
         <v>111</v>
@@ -7508,16 +7499,16 @@
         <v>23</v>
       </c>
       <c r="H122" s="5">
-        <v>2008001</v>
+        <v>2054001</v>
       </c>
       <c r="I122" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L122" s="48" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="M122" s="5" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="N122" s="47">
         <v>6</v>
@@ -7529,17 +7520,17 @@
     </row>
     <row r="123" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A123" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>1008002</v>
+        <f t="shared" si="5"/>
+        <v>1054002</v>
       </c>
       <c r="B123" s="5">
-        <v>100800</v>
+        <v>105400</v>
       </c>
       <c r="C123" s="5">
         <v>2</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>132</v>
@@ -7551,16 +7542,16 @@
         <v>23</v>
       </c>
       <c r="H123" s="5">
-        <v>2008001</v>
+        <v>2054001</v>
       </c>
       <c r="I123" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L123" s="48" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="M123" s="5" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="N123" s="47">
         <v>6</v>
@@ -7572,17 +7563,17 @@
     </row>
     <row r="124" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A124" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>1008003</v>
+        <f t="shared" si="5"/>
+        <v>1054003</v>
       </c>
       <c r="B124" s="5">
-        <v>100800</v>
+        <v>105400</v>
       </c>
       <c r="C124" s="5">
         <v>3</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>81</v>
@@ -7594,16 +7585,16 @@
         <v>23</v>
       </c>
       <c r="H124" s="5">
-        <v>2008001</v>
+        <v>2054001</v>
       </c>
       <c r="I124" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L124" s="48" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M124" s="5" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="N124" s="47">
         <v>6</v>
@@ -7615,20 +7606,20 @@
     </row>
     <row r="125" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A125" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>1053001</v>
+        <f t="shared" si="5"/>
+        <v>1054004</v>
       </c>
       <c r="B125" s="5">
-        <v>105300</v>
+        <v>105400</v>
       </c>
       <c r="C125" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>22</v>
+        <v>222</v>
       </c>
       <c r="F125" s="5">
         <v>1</v>
@@ -7637,43 +7628,41 @@
         <v>23</v>
       </c>
       <c r="H125" s="5">
-        <v>2053001</v>
+        <v>2054001</v>
       </c>
       <c r="I125" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J125" s="5"/>
-      <c r="K125" s="5"/>
       <c r="L125" s="48" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M125" s="5" t="s">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="N125" s="47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O125" s="47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q125" s="20"/>
     </row>
     <row r="126" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A126" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>1053002</v>
+        <f t="shared" si="5"/>
+        <v>1008001</v>
       </c>
       <c r="B126" s="5">
-        <v>105300</v>
+        <v>100800</v>
       </c>
       <c r="C126" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D126" s="5" t="s">
         <v>249</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="F126" s="5">
         <v>1</v>
@@ -7682,43 +7671,41 @@
         <v>23</v>
       </c>
       <c r="H126" s="5">
-        <v>2053001</v>
+        <v>2008001</v>
       </c>
       <c r="I126" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J126" s="5"/>
-      <c r="K126" s="5"/>
       <c r="L126" s="48" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="M126" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="N126" s="47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O126" s="47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q126" s="20"/>
     </row>
     <row r="127" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A127" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>1057001</v>
+        <f t="shared" si="5"/>
+        <v>1008002</v>
       </c>
       <c r="B127" s="5">
-        <v>105700</v>
+        <v>100800</v>
       </c>
       <c r="C127" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>22</v>
+        <v>132</v>
       </c>
       <c r="F127" s="5">
         <v>1</v>
@@ -7727,41 +7714,41 @@
         <v>23</v>
       </c>
       <c r="H127" s="5">
-        <v>2057001</v>
+        <v>2008001</v>
       </c>
       <c r="I127" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L127" s="48" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="M127" s="5" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="N127" s="47">
         <v>6</v>
       </c>
       <c r="O127" s="47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q127" s="20"/>
     </row>
     <row r="128" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A128" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>1057002</v>
+        <f t="shared" si="5"/>
+        <v>1008003</v>
       </c>
       <c r="B128" s="5">
-        <v>105700</v>
+        <v>100800</v>
       </c>
       <c r="C128" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="F128" s="5">
         <v>1</v>
@@ -7770,41 +7757,41 @@
         <v>23</v>
       </c>
       <c r="H128" s="5">
-        <v>2057001</v>
+        <v>2008001</v>
       </c>
       <c r="I128" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L128" s="48" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="M128" s="5" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="N128" s="47">
         <v>6</v>
       </c>
       <c r="O128" s="47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q128" s="20"/>
     </row>
     <row r="129" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A129" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>1057003</v>
+        <f t="shared" si="5"/>
+        <v>1053001</v>
       </c>
       <c r="B129" s="5">
-        <v>105700</v>
+        <v>105300</v>
       </c>
       <c r="C129" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>254</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="F129" s="5">
         <v>1</v>
@@ -7813,19 +7800,21 @@
         <v>23</v>
       </c>
       <c r="H129" s="5">
-        <v>2057001</v>
+        <v>2053001</v>
       </c>
       <c r="I129" s="5" t="s">
         <v>24</v>
       </c>
+      <c r="J129" s="5"/>
+      <c r="K129" s="5"/>
       <c r="L129" s="48" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="M129" s="5" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N129" s="47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O129" s="47">
         <v>5</v>
@@ -7834,20 +7823,20 @@
     </row>
     <row r="130" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A130" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>1058001</v>
+        <f t="shared" si="5"/>
+        <v>1053002</v>
       </c>
       <c r="B130" s="5">
-        <v>105800</v>
+        <v>105300</v>
       </c>
       <c r="C130" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="F130" s="5">
         <v>1</v>
@@ -7856,84 +7845,86 @@
         <v>23</v>
       </c>
       <c r="H130" s="5">
-        <v>2058001</v>
+        <v>2053001</v>
       </c>
       <c r="I130" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L130" s="48">
-        <v>10580001</v>
+      <c r="J130" s="5"/>
+      <c r="K130" s="5"/>
+      <c r="L130" s="48" t="s">
+        <v>257</v>
       </c>
       <c r="M130" s="5" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N130" s="47">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O130" s="47">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q130" s="20"/>
     </row>
     <row r="131" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A131" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>1058002</v>
+        <f t="shared" si="5"/>
+        <v>1057001</v>
       </c>
       <c r="B131" s="5">
-        <v>105800</v>
+        <v>105700</v>
       </c>
       <c r="C131" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D131" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="E131" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F131" s="5">
+        <v>1</v>
+      </c>
+      <c r="G131" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H131" s="5">
+        <v>2057001</v>
+      </c>
+      <c r="I131" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L131" s="48" t="s">
+        <v>260</v>
+      </c>
+      <c r="M131" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="E131" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F131" s="5">
-        <v>1</v>
-      </c>
-      <c r="G131" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H131" s="5">
-        <v>2058001</v>
-      </c>
-      <c r="I131" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L131" s="48">
-        <v>10580002</v>
-      </c>
-      <c r="M131" s="5" t="s">
-        <v>171</v>
-      </c>
       <c r="N131" s="47">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O131" s="47">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q131" s="20"/>
     </row>
     <row r="132" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A132" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>1058003</v>
+        <f t="shared" si="5"/>
+        <v>1057002</v>
       </c>
       <c r="B132" s="5">
-        <v>105800</v>
+        <v>105700</v>
       </c>
       <c r="C132" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="F132" s="5">
         <v>1</v>
@@ -7942,24 +7933,280 @@
         <v>23</v>
       </c>
       <c r="H132" s="5">
-        <v>2058001</v>
+        <v>2057001</v>
       </c>
       <c r="I132" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L132" s="48">
-        <v>10580004</v>
+      <c r="L132" s="48" t="s">
+        <v>262</v>
       </c>
       <c r="M132" s="5" t="s">
         <v>263</v>
       </c>
       <c r="N132" s="47">
+        <v>6</v>
+      </c>
+      <c r="O132" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q132" s="20"/>
+    </row>
+    <row r="133" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A133" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1057003</v>
+      </c>
+      <c r="B133" s="5">
+        <v>105700</v>
+      </c>
+      <c r="C133" s="5">
+        <v>3</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F133" s="5">
+        <v>1</v>
+      </c>
+      <c r="G133" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H133" s="5">
+        <v>2057001</v>
+      </c>
+      <c r="I133" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L133" s="48" t="s">
+        <v>264</v>
+      </c>
+      <c r="M133" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="N133" s="47">
+        <v>6</v>
+      </c>
+      <c r="O133" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q133" s="20"/>
+    </row>
+    <row r="134" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A134" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1058001</v>
+      </c>
+      <c r="B134" s="5">
+        <v>105800</v>
+      </c>
+      <c r="C134" s="5">
+        <v>1</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F134" s="5">
+        <v>1</v>
+      </c>
+      <c r="G134" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H134" s="5">
+        <v>2058001</v>
+      </c>
+      <c r="I134" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L134" s="48">
+        <v>10580001</v>
+      </c>
+      <c r="M134" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="N134" s="47">
         <v>7</v>
       </c>
-      <c r="O132" s="47">
+      <c r="O134" s="47">
         <v>7</v>
       </c>
-      <c r="Q132" s="20"/>
+      <c r="Q134" s="20"/>
+    </row>
+    <row r="135" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A135" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1058002</v>
+      </c>
+      <c r="B135" s="5">
+        <v>105800</v>
+      </c>
+      <c r="C135" s="5">
+        <v>2</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F135" s="5">
+        <v>1</v>
+      </c>
+      <c r="G135" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H135" s="5">
+        <v>2058001</v>
+      </c>
+      <c r="I135" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L135" s="48">
+        <v>10580002</v>
+      </c>
+      <c r="M135" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="N135" s="47">
+        <v>7</v>
+      </c>
+      <c r="O135" s="47">
+        <v>7</v>
+      </c>
+      <c r="Q135" s="20"/>
+    </row>
+    <row r="136" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A136" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1058003</v>
+      </c>
+      <c r="B136" s="5">
+        <v>105800</v>
+      </c>
+      <c r="C136" s="5">
+        <v>3</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F136" s="5">
+        <v>1</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H136" s="5">
+        <v>2058001</v>
+      </c>
+      <c r="I136" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L136" s="48">
+        <v>10580004</v>
+      </c>
+      <c r="M136" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="N136" s="47">
+        <v>7</v>
+      </c>
+      <c r="O136" s="47">
+        <v>7</v>
+      </c>
+      <c r="Q136" s="20"/>
+    </row>
+    <row r="137" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A137" s="48">
+        <v>1055001</v>
+      </c>
+      <c r="B137" s="5">
+        <v>105500</v>
+      </c>
+      <c r="C137" s="5">
+        <v>1</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F137" s="5">
+        <v>1</v>
+      </c>
+      <c r="G137" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="H137" s="5">
+        <v>2055001</v>
+      </c>
+      <c r="I137" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="L137" s="48">
+        <v>10550002</v>
+      </c>
+      <c r="M137" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="N137" s="47">
+        <v>3</v>
+      </c>
+      <c r="O137" s="47">
+        <v>4</v>
+      </c>
+      <c r="Q137" s="20"/>
+    </row>
+    <row r="138" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A138" s="48">
+        <v>1055002</v>
+      </c>
+      <c r="B138" s="5">
+        <v>105500</v>
+      </c>
+      <c r="C138" s="5">
+        <v>2</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="E138" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F138" s="5">
+        <v>1</v>
+      </c>
+      <c r="G138" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="H138" s="5">
+        <v>2055001</v>
+      </c>
+      <c r="I138" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="L138" s="48">
+        <v>10550001</v>
+      </c>
+      <c r="M138" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="N138" s="47">
+        <v>3</v>
+      </c>
+      <c r="O138" s="47">
+        <v>4</v>
+      </c>
+      <c r="Q138" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="264">
   <si>
     <t>id</t>
   </si>
@@ -806,34 +806,118 @@
     <t>糖果派对</t>
   </si>
   <si>
+    <t>第一层模式</t>
+  </si>
+  <si>
+    <t>10510002|10510007</t>
+  </si>
+  <si>
+    <t>一定改出透明图标+概率改出过关图标2</t>
+  </si>
+  <si>
+    <t>第二层模式</t>
+  </si>
+  <si>
+    <t>10510001|10510006</t>
+  </si>
+  <si>
+    <t>一定改出透明图标+概率改出过关图标1</t>
+  </si>
+  <si>
     <t>常规模式（第三层）</t>
   </si>
   <si>
     <t>概率改出过关图标3</t>
   </si>
   <si>
-    <t>第二层模式</t>
-  </si>
-  <si>
-    <t>10510001|10510006</t>
-  </si>
-  <si>
-    <t>一定改出透明图标+概率改出过关图标1</t>
-  </si>
-  <si>
-    <t>第一层模式</t>
-  </si>
-  <si>
-    <t>10510002|10510007</t>
-  </si>
-  <si>
-    <t>一定改出透明图标+概率改出过关图标2</t>
-  </si>
-  <si>
     <t>概率改出免费游戏图标</t>
   </si>
   <si>
     <t>改出1-4个彩池图标</t>
+  </si>
+  <si>
+    <t>黄金帝国</t>
+  </si>
+  <si>
+    <t>10540003|10540004|10540005|10540006|10540007|10540010</t>
+  </si>
+  <si>
+    <t>概率改出3个SCATTER+概率改出占据1个格子的金框符号+概率改出占据2、3、4个格子符号+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>10540001|10540010</t>
+  </si>
+  <si>
+    <t>改出4个以上SCATTER+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>10540002|10540008|10540010</t>
+  </si>
+  <si>
+    <t>改出3个SCATTER+奖池符号+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>10540009|10540010</t>
+  </si>
+  <si>
+    <t>招财猫</t>
+  </si>
+  <si>
+    <t>10260001|10260004|10260005|10260006|10260007|10080010</t>
+  </si>
+  <si>
+    <t>概率改出百搭wild符号+概率改出scatter符号+概率改出占据2、3、4个格子符号+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>10260002|10080010</t>
+  </si>
+  <si>
+    <t>10500003|10500008|10080010</t>
+  </si>
+  <si>
+    <t>麻将胡了2</t>
+  </si>
+  <si>
+    <t>10530001|10530004|10530005</t>
+  </si>
+  <si>
+    <t>概率出现3个以下SCATTER+概率出金色图标+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>10530002|10530005</t>
+  </si>
+  <si>
+    <t>概率改出3个scatter+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>赏金大对决</t>
+  </si>
+  <si>
+    <t>10570001|10570004|10570006</t>
+  </si>
+  <si>
+    <t>概率改出scatter符号+概率改出金框符号+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>10570002|10570006</t>
+  </si>
+  <si>
+    <t>改出3个以上SCATTER+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>10570001|10570005|10570006</t>
+  </si>
+  <si>
+    <t>改出2个SCATTER+奖池符号+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>极速糖果1000</t>
+  </si>
+  <si>
+    <t>概率改出scatter</t>
+  </si>
+  <si>
+    <t>奖池符号</t>
   </si>
 </sst>
 </file>
@@ -2230,7 +2314,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S117"/>
+  <dimension ref="A1:S132"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -5025,7 +5109,7 @@
         <v>24</v>
       </c>
       <c r="L66" s="48">
-        <v>10340007</v>
+        <v>10340101</v>
       </c>
       <c r="M66" s="5" t="s">
         <v>108</v>
@@ -6740,7 +6824,7 @@
       <c r="I106" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L106" s="5" t="s">
+      <c r="L106" s="48" t="s">
         <v>211</v>
       </c>
       <c r="M106" s="5" t="s">
@@ -6826,7 +6910,7 @@
       <c r="I108" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L108" s="5" t="s">
+      <c r="L108" s="48" t="s">
         <v>214</v>
       </c>
       <c r="M108" s="5" t="s">
@@ -6841,7 +6925,8 @@
       <c r="Q108" s="20"/>
     </row>
     <row r="109" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A109" s="48">
+      <c r="A109" s="5" t="str">
+        <f t="shared" ref="A109:A114" si="4">B109&amp;C109</f>
         <v>1050001</v>
       </c>
       <c r="B109" s="5">
@@ -6868,7 +6953,7 @@
       <c r="I109" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L109" s="5" t="s">
+      <c r="L109" s="48" t="s">
         <v>216</v>
       </c>
       <c r="M109" s="5" t="s">
@@ -6883,7 +6968,8 @@
       <c r="Q109" s="20"/>
     </row>
     <row r="110" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A110" s="48">
+      <c r="A110" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1050002</v>
       </c>
       <c r="B110" s="5">
@@ -6922,11 +7008,12 @@
       <c r="O110" s="47">
         <v>6</v>
       </c>
-      <c r="P110" s="47"/>
+      <c r="P110" s="5"/>
       <c r="Q110" s="20"/>
     </row>
     <row r="111" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A111" s="48">
+      <c r="A111" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1050003</v>
       </c>
       <c r="B111" s="5">
@@ -6968,7 +7055,8 @@
       <c r="Q111" s="20"/>
     </row>
     <row r="112" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A112" s="48">
+      <c r="A112" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1050004</v>
       </c>
       <c r="B112" s="5">
@@ -7010,7 +7098,8 @@
       <c r="Q112" s="20"/>
     </row>
     <row r="113" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A113" s="48">
+      <c r="A113" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1051001</v>
       </c>
       <c r="B113" s="5">
@@ -7037,11 +7126,11 @@
       <c r="I113" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L113" s="48">
-        <v>10510008</v>
+      <c r="L113" s="48" t="s">
+        <v>227</v>
       </c>
       <c r="M113" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N113" s="47">
         <v>6</v>
@@ -7051,8 +7140,9 @@
       </c>
       <c r="Q113" s="20"/>
     </row>
-    <row r="114" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A114" s="48">
+    <row r="114" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A114" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>1051002</v>
       </c>
       <c r="B114" s="5">
@@ -7064,8 +7154,8 @@
       <c r="D114" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="E114" t="s">
-        <v>228</v>
+      <c r="E114" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="F114" s="5">
         <v>1</v>
@@ -7080,10 +7170,10 @@
         <v>24</v>
       </c>
       <c r="L114" s="48" t="s">
-        <v>229</v>
-      </c>
-      <c r="M114" t="s">
         <v>230</v>
+      </c>
+      <c r="M114" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="N114" s="47">
         <v>6</v>
@@ -7091,10 +7181,11 @@
       <c r="O114" s="47">
         <v>6</v>
       </c>
-      <c r="Q114" s="10"/>
-    </row>
-    <row r="115" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A115" s="48">
+      <c r="Q114" s="20"/>
+    </row>
+    <row r="115" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A115" s="5" t="str">
+        <f>B115&amp;C115</f>
         <v>1051003</v>
       </c>
       <c r="B115" s="5">
@@ -7106,8 +7197,8 @@
       <c r="D115" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="E115" t="s">
-        <v>231</v>
+      <c r="E115" s="5" t="s">
+        <v>232</v>
       </c>
       <c r="F115" s="5">
         <v>1</v>
@@ -7121,10 +7212,10 @@
       <c r="I115" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L115" s="48" t="s">
-        <v>232</v>
-      </c>
-      <c r="M115" t="s">
+      <c r="L115" s="48">
+        <v>10510008</v>
+      </c>
+      <c r="M115" s="5" t="s">
         <v>233</v>
       </c>
       <c r="N115" s="47">
@@ -7133,10 +7224,11 @@
       <c r="O115" s="47">
         <v>6</v>
       </c>
-      <c r="Q115" s="10"/>
-    </row>
-    <row r="116" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A116" s="48">
+      <c r="Q115" s="20"/>
+    </row>
+    <row r="116" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A116" s="5" t="str">
+        <f t="shared" ref="A116:A132" si="5">B116&amp;C116</f>
         <v>1051004</v>
       </c>
       <c r="B116" s="5">
@@ -7148,7 +7240,7 @@
       <c r="D116" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E116" s="5" t="s">
         <v>132</v>
       </c>
       <c r="F116" s="5">
@@ -7166,7 +7258,7 @@
       <c r="L116" s="48">
         <v>10510005</v>
       </c>
-      <c r="M116" t="s">
+      <c r="M116" s="5" t="s">
         <v>234</v>
       </c>
       <c r="N116" s="47">
@@ -7175,10 +7267,11 @@
       <c r="O116" s="47">
         <v>6</v>
       </c>
-      <c r="Q116" s="10"/>
-    </row>
-    <row r="117" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A117" s="48">
+      <c r="Q116" s="20"/>
+    </row>
+    <row r="117" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A117" s="5" t="str">
+        <f t="shared" si="5"/>
         <v>1051005</v>
       </c>
       <c r="B117" s="5">
@@ -7190,7 +7283,7 @@
       <c r="D117" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E117" s="5" t="s">
         <v>81</v>
       </c>
       <c r="F117" s="5">
@@ -7208,7 +7301,7 @@
       <c r="L117" s="48">
         <v>10510009</v>
       </c>
-      <c r="M117" t="s">
+      <c r="M117" s="5" t="s">
         <v>235</v>
       </c>
       <c r="N117" s="47">
@@ -7217,7 +7310,656 @@
       <c r="O117" s="47">
         <v>6</v>
       </c>
-      <c r="Q117" s="10"/>
+      <c r="Q117" s="20"/>
+    </row>
+    <row r="118" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A118" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1054001</v>
+      </c>
+      <c r="B118" s="5">
+        <v>105400</v>
+      </c>
+      <c r="C118" s="5">
+        <v>1</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F118" s="5">
+        <v>1</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H118" s="5">
+        <v>2054001</v>
+      </c>
+      <c r="I118" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L118" s="48" t="s">
+        <v>237</v>
+      </c>
+      <c r="M118" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="N118" s="47">
+        <v>6</v>
+      </c>
+      <c r="O118" s="47">
+        <v>6</v>
+      </c>
+      <c r="Q118" s="20"/>
+    </row>
+    <row r="119" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A119" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1054002</v>
+      </c>
+      <c r="B119" s="5">
+        <v>105400</v>
+      </c>
+      <c r="C119" s="5">
+        <v>2</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F119" s="5">
+        <v>1</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H119" s="5">
+        <v>2054001</v>
+      </c>
+      <c r="I119" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L119" s="48" t="s">
+        <v>239</v>
+      </c>
+      <c r="M119" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="N119" s="47">
+        <v>6</v>
+      </c>
+      <c r="O119" s="47">
+        <v>6</v>
+      </c>
+      <c r="Q119" s="20"/>
+    </row>
+    <row r="120" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A120" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1054003</v>
+      </c>
+      <c r="B120" s="5">
+        <v>105400</v>
+      </c>
+      <c r="C120" s="5">
+        <v>3</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F120" s="5">
+        <v>1</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H120" s="5">
+        <v>2054001</v>
+      </c>
+      <c r="I120" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L120" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="M120" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="N120" s="47">
+        <v>6</v>
+      </c>
+      <c r="O120" s="47">
+        <v>6</v>
+      </c>
+      <c r="Q120" s="20"/>
+    </row>
+    <row r="121" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A121" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1054004</v>
+      </c>
+      <c r="B121" s="5">
+        <v>105400</v>
+      </c>
+      <c r="C121" s="5">
+        <v>4</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F121" s="5">
+        <v>1</v>
+      </c>
+      <c r="G121" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H121" s="5">
+        <v>2054001</v>
+      </c>
+      <c r="I121" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L121" s="48" t="s">
+        <v>243</v>
+      </c>
+      <c r="M121" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="N121" s="47">
+        <v>6</v>
+      </c>
+      <c r="O121" s="47">
+        <v>6</v>
+      </c>
+      <c r="Q121" s="20"/>
+    </row>
+    <row r="122" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A122" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1008001</v>
+      </c>
+      <c r="B122" s="5">
+        <v>100800</v>
+      </c>
+      <c r="C122" s="5">
+        <v>1</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F122" s="5">
+        <v>1</v>
+      </c>
+      <c r="G122" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H122" s="5">
+        <v>2008001</v>
+      </c>
+      <c r="I122" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L122" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="M122" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="N122" s="47">
+        <v>6</v>
+      </c>
+      <c r="O122" s="47">
+        <v>6</v>
+      </c>
+      <c r="Q122" s="20"/>
+    </row>
+    <row r="123" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A123" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1008002</v>
+      </c>
+      <c r="B123" s="5">
+        <v>100800</v>
+      </c>
+      <c r="C123" s="5">
+        <v>2</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F123" s="5">
+        <v>1</v>
+      </c>
+      <c r="G123" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H123" s="5">
+        <v>2008001</v>
+      </c>
+      <c r="I123" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L123" s="48" t="s">
+        <v>247</v>
+      </c>
+      <c r="M123" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="N123" s="47">
+        <v>6</v>
+      </c>
+      <c r="O123" s="47">
+        <v>6</v>
+      </c>
+      <c r="Q123" s="20"/>
+    </row>
+    <row r="124" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A124" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1008003</v>
+      </c>
+      <c r="B124" s="5">
+        <v>100800</v>
+      </c>
+      <c r="C124" s="5">
+        <v>3</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F124" s="5">
+        <v>1</v>
+      </c>
+      <c r="G124" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H124" s="5">
+        <v>2008001</v>
+      </c>
+      <c r="I124" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L124" s="48" t="s">
+        <v>248</v>
+      </c>
+      <c r="M124" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="N124" s="47">
+        <v>6</v>
+      </c>
+      <c r="O124" s="47">
+        <v>6</v>
+      </c>
+      <c r="Q124" s="20"/>
+    </row>
+    <row r="125" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A125" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1053001</v>
+      </c>
+      <c r="B125" s="5">
+        <v>105300</v>
+      </c>
+      <c r="C125" s="5">
+        <v>1</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="E125" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F125" s="5">
+        <v>1</v>
+      </c>
+      <c r="G125" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H125" s="5">
+        <v>2053001</v>
+      </c>
+      <c r="I125" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J125" s="5"/>
+      <c r="K125" s="5"/>
+      <c r="L125" s="48" t="s">
+        <v>250</v>
+      </c>
+      <c r="M125" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="N125" s="47">
+        <v>5</v>
+      </c>
+      <c r="O125" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q125" s="20"/>
+    </row>
+    <row r="126" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A126" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1053002</v>
+      </c>
+      <c r="B126" s="5">
+        <v>105300</v>
+      </c>
+      <c r="C126" s="5">
+        <v>2</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F126" s="5">
+        <v>1</v>
+      </c>
+      <c r="G126" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H126" s="5">
+        <v>2053001</v>
+      </c>
+      <c r="I126" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J126" s="5"/>
+      <c r="K126" s="5"/>
+      <c r="L126" s="48" t="s">
+        <v>252</v>
+      </c>
+      <c r="M126" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="N126" s="47">
+        <v>5</v>
+      </c>
+      <c r="O126" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q126" s="20"/>
+    </row>
+    <row r="127" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A127" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1057001</v>
+      </c>
+      <c r="B127" s="5">
+        <v>105700</v>
+      </c>
+      <c r="C127" s="5">
+        <v>1</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="E127" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F127" s="5">
+        <v>1</v>
+      </c>
+      <c r="G127" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H127" s="5">
+        <v>2057001</v>
+      </c>
+      <c r="I127" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L127" s="48" t="s">
+        <v>255</v>
+      </c>
+      <c r="M127" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="N127" s="47">
+        <v>6</v>
+      </c>
+      <c r="O127" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q127" s="20"/>
+    </row>
+    <row r="128" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A128" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1057002</v>
+      </c>
+      <c r="B128" s="5">
+        <v>105700</v>
+      </c>
+      <c r="C128" s="5">
+        <v>2</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="E128" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F128" s="5">
+        <v>1</v>
+      </c>
+      <c r="G128" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H128" s="5">
+        <v>2057001</v>
+      </c>
+      <c r="I128" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L128" s="48" t="s">
+        <v>257</v>
+      </c>
+      <c r="M128" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="N128" s="47">
+        <v>6</v>
+      </c>
+      <c r="O128" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q128" s="20"/>
+    </row>
+    <row r="129" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A129" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1057003</v>
+      </c>
+      <c r="B129" s="5">
+        <v>105700</v>
+      </c>
+      <c r="C129" s="5">
+        <v>3</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F129" s="5">
+        <v>1</v>
+      </c>
+      <c r="G129" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H129" s="5">
+        <v>2057001</v>
+      </c>
+      <c r="I129" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L129" s="48" t="s">
+        <v>259</v>
+      </c>
+      <c r="M129" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="N129" s="47">
+        <v>6</v>
+      </c>
+      <c r="O129" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q129" s="20"/>
+    </row>
+    <row r="130" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A130" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1058001</v>
+      </c>
+      <c r="B130" s="5">
+        <v>105800</v>
+      </c>
+      <c r="C130" s="5">
+        <v>1</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E130" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F130" s="5">
+        <v>1</v>
+      </c>
+      <c r="G130" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H130" s="5">
+        <v>2058001</v>
+      </c>
+      <c r="I130" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L130" s="48">
+        <v>10580001</v>
+      </c>
+      <c r="M130" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="N130" s="47">
+        <v>7</v>
+      </c>
+      <c r="O130" s="47">
+        <v>7</v>
+      </c>
+      <c r="Q130" s="20"/>
+    </row>
+    <row r="131" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A131" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1058002</v>
+      </c>
+      <c r="B131" s="5">
+        <v>105800</v>
+      </c>
+      <c r="C131" s="5">
+        <v>2</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E131" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F131" s="5">
+        <v>1</v>
+      </c>
+      <c r="G131" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H131" s="5">
+        <v>2058001</v>
+      </c>
+      <c r="I131" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L131" s="48">
+        <v>10580002</v>
+      </c>
+      <c r="M131" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="N131" s="47">
+        <v>7</v>
+      </c>
+      <c r="O131" s="47">
+        <v>7</v>
+      </c>
+      <c r="Q131" s="20"/>
+    </row>
+    <row r="132" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A132" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1058003</v>
+      </c>
+      <c r="B132" s="5">
+        <v>105800</v>
+      </c>
+      <c r="C132" s="5">
+        <v>3</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F132" s="5">
+        <v>1</v>
+      </c>
+      <c r="G132" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H132" s="5">
+        <v>2058001</v>
+      </c>
+      <c r="I132" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L132" s="48">
+        <v>10580004</v>
+      </c>
+      <c r="M132" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="N132" s="47">
+        <v>7</v>
+      </c>
+      <c r="O132" s="47">
+        <v>7</v>
+      </c>
+      <c r="Q132" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="276">
   <si>
     <t>id</t>
   </si>
@@ -933,6 +933,27 @@
   </si>
   <si>
     <t>伽罗宝石</t>
+  </si>
+  <si>
+    <t>超级高尔夫</t>
+  </si>
+  <si>
+    <t>10480005|10480001|10480006|10480007</t>
+  </si>
+  <si>
+    <t>概率改出百搭wild符号+概率改出scatter符号+概率改出占据2、3个格子符号</t>
+  </si>
+  <si>
+    <t>10480004|10480008</t>
+  </si>
+  <si>
+    <t>伽罗宝石1</t>
+  </si>
+  <si>
+    <t>小游戏—触发</t>
+  </si>
+  <si>
+    <t>改出小游戏图标</t>
   </si>
 </sst>
 </file>
@@ -1116,12 +1137,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1663,7 +1684,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1796,6 +1817,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2329,7 +2356,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S138"/>
+  <dimension ref="A1:S144"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -8208,6 +8235,260 @@
       </c>
       <c r="Q138" s="20"/>
     </row>
+    <row r="139" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A139" s="48">
+        <v>1048001</v>
+      </c>
+      <c r="B139" s="5">
+        <v>104800</v>
+      </c>
+      <c r="C139" s="5">
+        <v>1</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="E139" s="64" t="s">
+        <v>22</v>
+      </c>
+      <c r="F139" s="19">
+        <v>1</v>
+      </c>
+      <c r="G139" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="H139" s="65">
+        <v>2048001</v>
+      </c>
+      <c r="I139" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="L139" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="M139" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="N139" s="47">
+        <v>6</v>
+      </c>
+      <c r="O139" s="47">
+        <v>6</v>
+      </c>
+      <c r="Q139" s="20"/>
+    </row>
+    <row r="140" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A140" s="48">
+        <v>1048002</v>
+      </c>
+      <c r="B140" s="5">
+        <v>104800</v>
+      </c>
+      <c r="C140" s="5">
+        <v>2</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="E140" s="64" t="s">
+        <v>55</v>
+      </c>
+      <c r="F140" s="19">
+        <v>1</v>
+      </c>
+      <c r="G140" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="H140" s="65">
+        <v>2048001</v>
+      </c>
+      <c r="I140" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="L140" s="48">
+        <v>10480002</v>
+      </c>
+      <c r="M140" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="N140" s="47">
+        <v>6</v>
+      </c>
+      <c r="O140" s="47">
+        <v>6</v>
+      </c>
+      <c r="Q140" s="20"/>
+    </row>
+    <row r="141" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A141" s="48">
+        <v>1048003</v>
+      </c>
+      <c r="B141" s="5">
+        <v>104800</v>
+      </c>
+      <c r="C141" s="5">
+        <v>3</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="E141" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F141" s="19">
+        <v>1</v>
+      </c>
+      <c r="G141" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="H141" s="65">
+        <v>2048001</v>
+      </c>
+      <c r="I141" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="L141" s="48" t="s">
+        <v>272</v>
+      </c>
+      <c r="M141" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="N141" s="47">
+        <v>6</v>
+      </c>
+      <c r="O141" s="47">
+        <v>6</v>
+      </c>
+      <c r="Q141" s="20"/>
+    </row>
+    <row r="142" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A142" s="48">
+        <v>1055011</v>
+      </c>
+      <c r="B142" s="5">
+        <v>105501</v>
+      </c>
+      <c r="C142" s="5">
+        <v>1</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F142" s="5">
+        <v>1</v>
+      </c>
+      <c r="G142" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="H142" s="5">
+        <v>2055011</v>
+      </c>
+      <c r="I142" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="L142" s="48">
+        <v>10550102</v>
+      </c>
+      <c r="M142" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="N142" s="47">
+        <v>3</v>
+      </c>
+      <c r="O142" s="47">
+        <v>4</v>
+      </c>
+      <c r="Q142" s="20"/>
+    </row>
+    <row r="143" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A143" s="48">
+        <v>1055012</v>
+      </c>
+      <c r="B143" s="5">
+        <v>105501</v>
+      </c>
+      <c r="C143" s="5">
+        <v>2</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F143" s="5">
+        <v>1</v>
+      </c>
+      <c r="G143" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="H143" s="5">
+        <v>2055011</v>
+      </c>
+      <c r="I143" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="L143" s="48">
+        <v>10550101</v>
+      </c>
+      <c r="M143" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="N143" s="47">
+        <v>3</v>
+      </c>
+      <c r="O143" s="47">
+        <v>4</v>
+      </c>
+      <c r="Q143" s="20"/>
+    </row>
+    <row r="144" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A144" s="48">
+        <v>1055013</v>
+      </c>
+      <c r="B144" s="5">
+        <v>105501</v>
+      </c>
+      <c r="C144" s="5">
+        <v>3</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="E144" s="52" t="s">
+        <v>274</v>
+      </c>
+      <c r="F144" s="5">
+        <v>1</v>
+      </c>
+      <c r="G144" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="H144" s="5">
+        <v>2055011</v>
+      </c>
+      <c r="I144" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="J144" s="5"/>
+      <c r="K144" s="5"/>
+      <c r="L144" s="48">
+        <v>10550103</v>
+      </c>
+      <c r="M144" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="N144" s="47">
+        <v>3</v>
+      </c>
+      <c r="O144" s="47">
+        <v>4</v>
+      </c>
+      <c r="Q144" s="10"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="19455" windowHeight="8745"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="278">
   <si>
     <t>id</t>
   </si>
@@ -929,7 +929,13 @@
     <t>极速糖果1000</t>
   </si>
   <si>
-    <t>概率改出scatter</t>
+    <t>概率改出3个以下scatter</t>
+  </si>
+  <si>
+    <t>10580004|10580001</t>
+  </si>
+  <si>
+    <t>改出奖池符号=概率改出SCATTER符号</t>
   </si>
   <si>
     <t>伽罗宝石</t>
@@ -1137,12 +1143,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -8052,7 +8058,7 @@
         <v>24</v>
       </c>
       <c r="L134" s="48">
-        <v>10580001</v>
+        <v>10580003</v>
       </c>
       <c r="M134" s="5" t="s">
         <v>267</v>
@@ -8098,7 +8104,7 @@
         <v>10580002</v>
       </c>
       <c r="M135" s="5" t="s">
-        <v>171</v>
+        <v>88</v>
       </c>
       <c r="N135" s="47">
         <v>7</v>
@@ -8137,11 +8143,11 @@
       <c r="I136" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L136" s="48">
-        <v>10580004</v>
+      <c r="L136" s="48" t="s">
+        <v>268</v>
       </c>
       <c r="M136" s="5" t="s">
-        <v>118</v>
+        <v>269</v>
       </c>
       <c r="N136" s="47">
         <v>7</v>
@@ -8162,7 +8168,7 @@
         <v>1</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>22</v>
@@ -8204,7 +8210,7 @@
         <v>2</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E138" s="5" t="s">
         <v>81</v>
@@ -8246,7 +8252,7 @@
         <v>1</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E139" s="64" t="s">
         <v>22</v>
@@ -8264,10 +8270,10 @@
         <v>24</v>
       </c>
       <c r="L139" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M139" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N139" s="47">
         <v>6</v>
@@ -8288,7 +8294,7 @@
         <v>2</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E140" s="64" t="s">
         <v>55</v>
@@ -8330,7 +8336,7 @@
         <v>3</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E141" s="5" t="s">
         <v>81</v>
@@ -8348,7 +8354,7 @@
         <v>24</v>
       </c>
       <c r="L141" s="48" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M141" s="5" t="s">
         <v>196</v>
@@ -8372,7 +8378,7 @@
         <v>1</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E142" s="5" t="s">
         <v>22</v>
@@ -8414,7 +8420,7 @@
         <v>2</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>81</v>
@@ -8456,10 +8462,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E144" s="52" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F144" s="5">
         <v>1</v>
@@ -8479,7 +8485,7 @@
         <v>10550103</v>
       </c>
       <c r="M144" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="N144" s="47">
         <v>3</v>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\slot\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_6F3B6C7BC70A60440DB75B1283E4472CFF7CFBCA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -33,13 +27,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author/>
   </authors>
   <commentList>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -61,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="N1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -83,7 +77,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="O1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -105,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="J2" authorId="0">
       <text>
         <r>
           <rPr>
@@ -812,6 +806,15 @@
     <t>糖果派对</t>
   </si>
   <si>
+    <t>第1层，普通模式</t>
+  </si>
+  <si>
+    <t>第2层，普通模式</t>
+  </si>
+  <si>
+    <t>第3层，普通模式</t>
+  </si>
+  <si>
     <t>第1层，免费游戏-触发局</t>
   </si>
   <si>
@@ -846,15 +849,6 @@
   </si>
   <si>
     <t>第3层，概率改出彩池图标</t>
-  </si>
-  <si>
-    <t>第1层，普通模式</t>
-  </si>
-  <si>
-    <t>第2层，普通模式</t>
-  </si>
-  <si>
-    <t>第3层，普通模式</t>
   </si>
   <si>
     <t>黄金帝国</t>
@@ -971,11 +965,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1001,10 +999,147 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1018,14 +1153,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="14">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1034,31 +1163,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1082,30 +1211,216 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1128,10 +1443,252 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1155,10 +1712,10 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1189,7 +1746,7 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1257,166 +1814,97 @@
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 80" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 80" xfId="49"/>
   </cellStyles>
   <dxfs count="18">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
+          <bgColor theme="8" tint="0.799340800195319"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -1427,7 +1915,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1455,40 +1943,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="17"/>
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstColumn" dxfId="14"/>
-      <tableStyleElement type="lastColumn" dxfId="13"/>
-      <tableStyleElement type="firstRowStripe" dxfId="12"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="11"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="10"/>
-      <tableStyleElement type="totalRow" dxfId="9"/>
-      <tableStyleElement type="firstRowStripe" dxfId="8"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="7"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="6"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="4"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="3"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="2"/>
-      <tableStyleElement type="pageFieldValues" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1738,14 +2340,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:S144"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
     <col min="5" max="5" width="36.375" customWidth="1"/>
@@ -1763,7 +2365,7 @@
     <col min="18" max="18" width="60.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" ht="16.5" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1801,7 +2403,7 @@
       </c>
       <c r="Q1"/>
     </row>
-    <row r="2" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="2" ht="16.5" spans="1:17">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1837,7 +2439,7 @@
       </c>
       <c r="Q2"/>
     </row>
-    <row r="3" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="3" ht="16.5" spans="1:17">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1873,7 +2475,7 @@
       </c>
       <c r="Q3"/>
     </row>
-    <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="4" ht="16.5" spans="1:17">
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -1890,7 +2492,7 @@
       <c r="O4" s="15"/>
       <c r="Q4"/>
     </row>
-    <row r="5" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A5" s="22" t="str">
         <f t="shared" ref="A5:A19" si="0">B5&amp;C5</f>
         <v>1001001</v>
@@ -1934,7 +2536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="6" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A6" s="22" t="str">
         <f t="shared" si="0"/>
         <v>1001002</v>
@@ -1976,7 +2578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="7" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A7" s="22" t="str">
         <f t="shared" si="0"/>
         <v>1001003</v>
@@ -2018,7 +2620,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="8" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A8" s="22" t="str">
         <f t="shared" si="0"/>
         <v>1001004</v>
@@ -2060,7 +2662,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="9" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A9" s="22" t="str">
         <f t="shared" si="0"/>
         <v>1001005</v>
@@ -2102,7 +2704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="10" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A10" s="22" t="str">
         <f t="shared" si="0"/>
         <v>1001006</v>
@@ -2144,7 +2746,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="11" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A11" s="22" t="str">
         <f t="shared" si="0"/>
         <v>1001007</v>
@@ -2186,7 +2788,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="12" s="2" customFormat="1" ht="16.5" spans="1:17">
       <c r="A12" s="32" t="str">
         <f t="shared" si="0"/>
         <v>1003001</v>
@@ -2231,7 +2833,7 @@
       </c>
       <c r="Q12" s="34"/>
     </row>
-    <row r="13" spans="1:17" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="13" s="2" customFormat="1" ht="16.5" spans="1:17">
       <c r="A13" s="32" t="str">
         <f t="shared" si="0"/>
         <v>1003002</v>
@@ -2274,7 +2876,7 @@
       </c>
       <c r="Q13" s="34"/>
     </row>
-    <row r="14" spans="1:17" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="14" s="2" customFormat="1" ht="16.5" spans="1:17">
       <c r="A14" s="32" t="str">
         <f t="shared" si="0"/>
         <v>1003003</v>
@@ -2321,7 +2923,7 @@
       </c>
       <c r="Q14" s="34"/>
     </row>
-    <row r="15" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="15" ht="16.5" spans="1:17">
       <c r="A15" s="35" t="str">
         <f t="shared" si="0"/>
         <v>1007001</v>
@@ -2366,7 +2968,7 @@
       </c>
       <c r="Q15"/>
     </row>
-    <row r="16" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="16" ht="16.5" spans="1:17">
       <c r="A16" s="35" t="str">
         <f t="shared" si="0"/>
         <v>1007002</v>
@@ -2409,7 +3011,7 @@
       </c>
       <c r="Q16"/>
     </row>
-    <row r="17" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="17" s="3" customFormat="1" ht="16.5" spans="1:17">
       <c r="A17" s="38" t="str">
         <f t="shared" si="0"/>
         <v>1012001</v>
@@ -2454,7 +3056,7 @@
       </c>
       <c r="Q17" s="41"/>
     </row>
-    <row r="18" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="18" s="3" customFormat="1" ht="16.5" spans="1:17">
       <c r="A18" s="38" t="str">
         <f t="shared" si="0"/>
         <v>1012002</v>
@@ -2497,7 +3099,7 @@
       </c>
       <c r="Q18" s="41"/>
     </row>
-    <row r="19" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="19" s="3" customFormat="1" ht="16.5" spans="1:17">
       <c r="A19" s="38" t="str">
         <f t="shared" si="0"/>
         <v>1012003</v>
@@ -2542,7 +3144,7 @@
       </c>
       <c r="Q19" s="41"/>
     </row>
-    <row r="20" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="20" ht="16.5" spans="1:17">
       <c r="A20" s="32" t="str">
         <f t="shared" ref="A20:A30" si="1">B20&amp;C20</f>
         <v>1014001</v>
@@ -2586,7 +3188,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="21" ht="16.5" spans="1:17">
       <c r="A21" s="32" t="str">
         <f t="shared" si="1"/>
         <v>1014002</v>
@@ -2630,7 +3232,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="22" ht="16.5" spans="1:17">
       <c r="A22" s="32" t="str">
         <f t="shared" si="1"/>
         <v>1014003</v>
@@ -2674,7 +3276,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="23" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A23" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024001</v>
@@ -2718,7 +3320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A24" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024002</v>
@@ -2760,7 +3362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A25" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024003</v>
@@ -2802,7 +3404,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="26" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A26" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024004</v>
@@ -2844,7 +3446,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A27" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024005</v>
@@ -2886,7 +3488,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A28" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024006</v>
@@ -2928,7 +3530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A29" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024007</v>
@@ -2970,7 +3572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="30" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A30" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1017001</v>
@@ -3013,7 +3615,7 @@
       </c>
       <c r="Q30" s="16"/>
     </row>
-    <row r="31" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="31" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A31" s="22" t="str">
         <f t="shared" ref="A31:A54" si="2">B31&amp;C31</f>
         <v>1017002</v>
@@ -3056,7 +3658,7 @@
       </c>
       <c r="Q31" s="16"/>
     </row>
-    <row r="32" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="32" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A32" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1017003</v>
@@ -3099,7 +3701,7 @@
       </c>
       <c r="Q32" s="16"/>
     </row>
-    <row r="33" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="33" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A33" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1022001</v>
@@ -3142,7 +3744,7 @@
       </c>
       <c r="Q33" s="16"/>
     </row>
-    <row r="34" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="34" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A34" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1022002</v>
@@ -3185,7 +3787,7 @@
       </c>
       <c r="Q34" s="16"/>
     </row>
-    <row r="35" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="35" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A35" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1022003</v>
@@ -3228,7 +3830,7 @@
       </c>
       <c r="Q35" s="16"/>
     </row>
-    <row r="36" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="36" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A36" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1022004</v>
@@ -3268,7 +3870,7 @@
       </c>
       <c r="Q36" s="16"/>
     </row>
-    <row r="37" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="37" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A37" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1022005</v>
@@ -3309,7 +3911,7 @@
       <c r="Q37" s="16"/>
       <c r="S37" s="44"/>
     </row>
-    <row r="38" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="38" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A38" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1021001</v>
@@ -3353,7 +3955,7 @@
       <c r="Q38" s="16"/>
       <c r="S38" s="44"/>
     </row>
-    <row r="39" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="39" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A39" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1021002</v>
@@ -3397,7 +3999,7 @@
       <c r="Q39" s="16"/>
       <c r="S39" s="44"/>
     </row>
-    <row r="40" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="40" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A40" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1021003</v>
@@ -3441,7 +4043,7 @@
       <c r="Q40" s="16"/>
       <c r="S40" s="44"/>
     </row>
-    <row r="41" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="41" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A41" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1021004</v>
@@ -3485,7 +4087,7 @@
       <c r="Q41" s="16"/>
       <c r="S41" s="44"/>
     </row>
-    <row r="42" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="42" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A42" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1018001</v>
@@ -3529,7 +4131,7 @@
       <c r="Q42" s="16"/>
       <c r="S42" s="44"/>
     </row>
-    <row r="43" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="43" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A43" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1018002</v>
@@ -3571,7 +4173,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="44" ht="16.5" spans="1:19">
       <c r="A44" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1018003</v>
@@ -3613,7 +4215,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="45" ht="16.5" spans="1:19">
       <c r="A45" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1025001</v>
@@ -3655,7 +4257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="46" ht="16.5" spans="1:19">
       <c r="A46" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1025002</v>
@@ -3697,7 +4299,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="47" ht="16.5" spans="1:19">
       <c r="A47" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1025003</v>
@@ -3739,7 +4341,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="48" ht="16.5" spans="1:19">
       <c r="A48" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1023001</v>
@@ -3781,7 +4383,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="49" ht="16.5" spans="1:16">
       <c r="A49" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1023002</v>
@@ -3823,7 +4425,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="50" ht="16.5" spans="1:16">
       <c r="A50" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1023003</v>
@@ -3865,7 +4467,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="51" ht="16.5" spans="1:16">
       <c r="A51" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1034001</v>
@@ -3907,7 +4509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="52" ht="16.5" spans="1:16">
       <c r="A52" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1034002</v>
@@ -3946,7 +4548,7 @@
       </c>
       <c r="P52" s="45"/>
     </row>
-    <row r="53" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="53" ht="16.5" spans="1:16">
       <c r="A53" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1034003</v>
@@ -3984,7 +4586,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="54" ht="16.5" spans="1:16">
       <c r="A54" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1035001</v>
@@ -4026,7 +4628,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="55" ht="16.5" spans="1:16">
       <c r="A55" s="4" t="str">
         <f t="shared" ref="A55:A108" si="3">B55&amp;C55</f>
         <v>1035002</v>
@@ -4068,7 +4670,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="56" ht="16.5" spans="1:16">
       <c r="A56" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1035003</v>
@@ -4110,7 +4712,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="57" ht="16.5" spans="1:16">
       <c r="A57" s="43">
         <v>1035011</v>
       </c>
@@ -4151,7 +4753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="58" ht="16.5" spans="1:16">
       <c r="A58" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1035012</v>
@@ -4193,7 +4795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="59" ht="16.5" spans="1:16">
       <c r="A59" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1035013</v>
@@ -4235,7 +4837,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="60" ht="16.5" spans="1:16">
       <c r="A60" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1036001</v>
@@ -4277,7 +4879,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="61" ht="16.5" spans="1:16">
       <c r="A61" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1036002</v>
@@ -4319,7 +4921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="62" ht="16.5" spans="1:16">
       <c r="A62" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1036003</v>
@@ -4361,7 +4963,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="63" ht="16.5" spans="1:16">
       <c r="A63" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1028001</v>
@@ -4403,7 +5005,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="64" ht="16.5" spans="1:16">
       <c r="A64" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1028002</v>
@@ -4445,7 +5047,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="65" ht="16.5" spans="1:17">
       <c r="A65" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1028003</v>
@@ -4487,7 +5089,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="66" ht="16.5" spans="1:17">
       <c r="A66" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1034011</v>
@@ -4529,7 +5131,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="67" ht="16.5" spans="1:17">
       <c r="A67" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1034012</v>
@@ -4568,7 +5170,7 @@
       </c>
       <c r="P67" s="45"/>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="68" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A68" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1034013</v>
@@ -4609,7 +5211,7 @@
       </c>
       <c r="Q68" s="46"/>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="69" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A69" s="47" t="str">
         <f t="shared" si="3"/>
         <v>1020001</v>
@@ -4652,7 +5254,7 @@
       </c>
       <c r="Q69" s="46"/>
     </row>
-    <row r="70" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="70" ht="16.5" spans="1:17">
       <c r="A70" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1020002</v>
@@ -4694,7 +5296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="71" ht="16.5" spans="1:17">
       <c r="A71" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1020003</v>
@@ -4736,7 +5338,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="72" s="6" customFormat="1" ht="16.5" spans="1:17">
       <c r="A72" s="50" t="str">
         <f t="shared" si="3"/>
         <v>1020004</v>
@@ -4779,7 +5381,7 @@
       </c>
       <c r="Q72" s="53"/>
     </row>
-    <row r="73" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="73" ht="16.5" spans="1:17">
       <c r="A73" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1020005</v>
@@ -4821,7 +5423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="74" ht="16.5" spans="1:17">
       <c r="A74" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1038001</v>
@@ -4864,7 +5466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="75" ht="16.5" spans="1:17">
       <c r="A75" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1038002</v>
@@ -4906,7 +5508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="76" ht="16.5" spans="1:17">
       <c r="A76" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1038004</v>
@@ -4948,7 +5550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="77" ht="16.5" spans="1:17">
       <c r="A77" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1038003</v>
@@ -4990,7 +5592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="78" ht="16.5" spans="1:17">
       <c r="A78" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1027001</v>
@@ -5032,7 +5634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="79" ht="16.5" spans="1:17">
       <c r="A79" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1027002</v>
@@ -5074,7 +5676,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="80" ht="16.5" spans="1:17">
       <c r="A80" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1027003</v>
@@ -5116,7 +5718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="81" ht="16.5" spans="1:17">
       <c r="A81" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1037001</v>
@@ -5158,7 +5760,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="82" ht="16.5" spans="1:17">
       <c r="A82" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1037002</v>
@@ -5200,7 +5802,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="83" ht="16.5" spans="1:17">
       <c r="A83" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1037003</v>
@@ -5242,7 +5844,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="84" ht="16.5" spans="1:17">
       <c r="A84" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1031001</v>
@@ -5284,7 +5886,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="85" ht="16.5" spans="1:17">
       <c r="A85" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1031002</v>
@@ -5326,7 +5928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="86" ht="16.5" spans="1:17">
       <c r="A86" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1031003</v>
@@ -5368,7 +5970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="87" ht="16.5" spans="1:17">
       <c r="A87" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1031004</v>
@@ -5410,7 +6012,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="88" ht="16.5" spans="1:17">
       <c r="A88" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1031005</v>
@@ -5452,7 +6054,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="89" ht="16.5" spans="1:17">
       <c r="A89" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1031006</v>
@@ -5494,7 +6096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="90" ht="16.5" spans="1:17">
       <c r="A90" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1040001</v>
@@ -5536,7 +6138,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="91" ht="16.5" spans="1:17">
       <c r="A91" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1040002</v>
@@ -5578,7 +6180,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="92" ht="16.5" spans="1:17">
       <c r="A92" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1040003</v>
@@ -5620,7 +6222,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="93" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A93" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1039001</v>
@@ -5663,7 +6265,7 @@
       </c>
       <c r="Q93" s="16"/>
     </row>
-    <row r="94" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="94" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A94" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1039002</v>
@@ -5706,7 +6308,7 @@
       </c>
       <c r="Q94" s="16"/>
     </row>
-    <row r="95" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="95" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A95" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1039003</v>
@@ -5749,7 +6351,7 @@
       </c>
       <c r="Q95" s="16"/>
     </row>
-    <row r="96" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="96" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A96" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1016001</v>
@@ -5792,7 +6394,7 @@
       </c>
       <c r="Q96" s="16"/>
     </row>
-    <row r="97" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="97" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A97" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1016002</v>
@@ -5835,7 +6437,7 @@
       </c>
       <c r="Q97" s="16"/>
     </row>
-    <row r="98" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="98" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A98" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1016003</v>
@@ -5878,7 +6480,7 @@
       </c>
       <c r="Q98" s="16"/>
     </row>
-    <row r="99" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="99" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A99" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015001</v>
@@ -5921,7 +6523,7 @@
       </c>
       <c r="Q99" s="16"/>
     </row>
-    <row r="100" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="100" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A100" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015002</v>
@@ -5964,7 +6566,7 @@
       </c>
       <c r="Q100" s="16"/>
     </row>
-    <row r="101" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="101" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A101" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015003</v>
@@ -6007,7 +6609,7 @@
       </c>
       <c r="Q101" s="16"/>
     </row>
-    <row r="102" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="102" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A102" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015004</v>
@@ -6050,7 +6652,7 @@
       </c>
       <c r="Q102" s="16"/>
     </row>
-    <row r="103" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="103" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A103" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015005</v>
@@ -6093,7 +6695,7 @@
       </c>
       <c r="Q103" s="16"/>
     </row>
-    <row r="104" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="104" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A104" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015006</v>
@@ -6136,7 +6738,7 @@
       </c>
       <c r="Q104" s="16"/>
     </row>
-    <row r="105" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="105" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A105" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015007</v>
@@ -6179,7 +6781,7 @@
       </c>
       <c r="Q105" s="16"/>
     </row>
-    <row r="106" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="106" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A106" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1026001</v>
@@ -6222,7 +6824,7 @@
       </c>
       <c r="Q106" s="16"/>
     </row>
-    <row r="107" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="107" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A107" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1026002</v>
@@ -6265,7 +6867,7 @@
       </c>
       <c r="Q107" s="16"/>
     </row>
-    <row r="108" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="108" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A108" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1026003</v>
@@ -6308,7 +6910,7 @@
       </c>
       <c r="Q108" s="16"/>
     </row>
-    <row r="109" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="109" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A109" s="4" t="str">
         <f t="shared" ref="A109:A112" si="4">B109&amp;C109</f>
         <v>1050001</v>
@@ -6351,7 +6953,7 @@
       </c>
       <c r="Q109" s="16"/>
     </row>
-    <row r="110" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="110" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A110" s="4" t="str">
         <f t="shared" si="4"/>
         <v>1050002</v>
@@ -6394,7 +6996,7 @@
       </c>
       <c r="Q110" s="16"/>
     </row>
-    <row r="111" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="111" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A111" s="4" t="str">
         <f t="shared" si="4"/>
         <v>1050003</v>
@@ -6437,7 +7039,7 @@
       </c>
       <c r="Q111" s="16"/>
     </row>
-    <row r="112" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="112" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A112" s="4" t="str">
         <f t="shared" si="4"/>
         <v>1050004</v>
@@ -6480,7 +7082,7 @@
       </c>
       <c r="Q112" s="16"/>
     </row>
-    <row r="113" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="113" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A113" s="43">
         <v>1051001</v>
       </c>
@@ -6508,12 +7110,7 @@
       <c r="I113" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L113" s="43">
-        <v>10510001</v>
-      </c>
-      <c r="M113" s="4" t="s">
-        <v>227</v>
-      </c>
+      <c r="L113" s="43"/>
       <c r="N113" s="42">
         <v>4</v>
       </c>
@@ -6522,7 +7119,7 @@
       </c>
       <c r="Q113" s="16"/>
     </row>
-    <row r="114" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="114" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A114" s="43">
         <v>1051002</v>
       </c>
@@ -6536,7 +7133,7 @@
         <v>225</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F114" s="4">
         <v>1</v>
@@ -6550,12 +7147,7 @@
       <c r="I114" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L114" s="43">
-        <v>10510002</v>
-      </c>
-      <c r="M114" s="4" t="s">
-        <v>229</v>
-      </c>
+      <c r="L114" s="43"/>
       <c r="N114" s="42">
         <v>5</v>
       </c>
@@ -6564,7 +7156,7 @@
       </c>
       <c r="Q114" s="16"/>
     </row>
-    <row r="115" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="115" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A115" s="43">
         <v>1051003</v>
       </c>
@@ -6578,7 +7170,7 @@
         <v>225</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F115" s="4">
         <v>1</v>
@@ -6592,12 +7184,7 @@
       <c r="I115" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L115" s="43">
-        <v>10510003</v>
-      </c>
-      <c r="M115" s="4" t="s">
-        <v>231</v>
-      </c>
+      <c r="L115" s="43"/>
       <c r="N115" s="42">
         <v>6</v>
       </c>
@@ -6606,7 +7193,7 @@
       </c>
       <c r="Q115" s="16"/>
     </row>
-    <row r="116" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="116" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A116" s="43">
         <v>1051004</v>
       </c>
@@ -6620,7 +7207,7 @@
         <v>225</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F116" s="4">
         <v>1</v>
@@ -6635,10 +7222,10 @@
         <v>24</v>
       </c>
       <c r="L116" s="43">
-        <v>10510004</v>
+        <v>10510001</v>
       </c>
       <c r="M116" s="4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="N116" s="42">
         <v>4</v>
@@ -6648,7 +7235,7 @@
       </c>
       <c r="Q116" s="16"/>
     </row>
-    <row r="117" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="117" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A117" s="43">
         <v>1051005</v>
       </c>
@@ -6662,7 +7249,7 @@
         <v>225</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F117" s="4">
         <v>1</v>
@@ -6677,10 +7264,10 @@
         <v>24</v>
       </c>
       <c r="L117" s="43">
-        <v>10510005</v>
+        <v>10510002</v>
       </c>
       <c r="M117" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="N117" s="42">
         <v>5</v>
@@ -6690,7 +7277,7 @@
       </c>
       <c r="Q117" s="16"/>
     </row>
-    <row r="118" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="118" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A118" s="43">
         <v>1051006</v>
       </c>
@@ -6704,7 +7291,7 @@
         <v>225</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F118" s="4">
         <v>1</v>
@@ -6719,10 +7306,10 @@
         <v>24</v>
       </c>
       <c r="L118" s="43">
-        <v>10510006</v>
+        <v>10510003</v>
       </c>
       <c r="M118" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="N118" s="42">
         <v>6</v>
@@ -6732,7 +7319,7 @@
       </c>
       <c r="Q118" s="16"/>
     </row>
-    <row r="119" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="119" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A119" s="43">
         <v>1051007</v>
       </c>
@@ -6746,7 +7333,7 @@
         <v>225</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F119" s="4">
         <v>1</v>
@@ -6760,7 +7347,12 @@
       <c r="I119" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L119" s="43"/>
+      <c r="L119" s="43">
+        <v>10510004</v>
+      </c>
+      <c r="M119" s="4" t="s">
+        <v>236</v>
+      </c>
       <c r="N119" s="42">
         <v>4</v>
       </c>
@@ -6769,7 +7361,7 @@
       </c>
       <c r="Q119" s="16"/>
     </row>
-    <row r="120" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="120" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A120" s="43">
         <v>1051008</v>
       </c>
@@ -6783,7 +7375,7 @@
         <v>225</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F120" s="4">
         <v>1</v>
@@ -6797,7 +7389,12 @@
       <c r="I120" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L120" s="43"/>
+      <c r="L120" s="43">
+        <v>10510005</v>
+      </c>
+      <c r="M120" s="4" t="s">
+        <v>238</v>
+      </c>
       <c r="N120" s="42">
         <v>5</v>
       </c>
@@ -6806,7 +7403,7 @@
       </c>
       <c r="Q120" s="16"/>
     </row>
-    <row r="121" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="121" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A121" s="43">
         <v>1051009</v>
       </c>
@@ -6820,7 +7417,7 @@
         <v>225</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F121" s="4">
         <v>1</v>
@@ -6834,7 +7431,12 @@
       <c r="I121" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L121" s="43"/>
+      <c r="L121" s="43">
+        <v>10510006</v>
+      </c>
+      <c r="M121" s="4" t="s">
+        <v>240</v>
+      </c>
       <c r="N121" s="42">
         <v>6</v>
       </c>
@@ -6843,7 +7445,7 @@
       </c>
       <c r="Q121" s="16"/>
     </row>
-    <row r="122" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="122" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A122" s="4" t="str">
         <f t="shared" ref="A122:A136" si="5">B122&amp;C122</f>
         <v>1054001</v>
@@ -6886,7 +7488,7 @@
       </c>
       <c r="Q122" s="16"/>
     </row>
-    <row r="123" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="123" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A123" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1054002</v>
@@ -6929,7 +7531,7 @@
       </c>
       <c r="Q123" s="16"/>
     </row>
-    <row r="124" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="124" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A124" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1054003</v>
@@ -6972,7 +7574,7 @@
       </c>
       <c r="Q124" s="16"/>
     </row>
-    <row r="125" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="125" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A125" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1054004</v>
@@ -7015,7 +7617,7 @@
       </c>
       <c r="Q125" s="16"/>
     </row>
-    <row r="126" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="126" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A126" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1008001</v>
@@ -7058,7 +7660,7 @@
       </c>
       <c r="Q126" s="16"/>
     </row>
-    <row r="127" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="127" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A127" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1008002</v>
@@ -7101,7 +7703,7 @@
       </c>
       <c r="Q127" s="16"/>
     </row>
-    <row r="128" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="128" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A128" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1008003</v>
@@ -7144,7 +7746,7 @@
       </c>
       <c r="Q128" s="16"/>
     </row>
-    <row r="129" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="129" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A129" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1053001</v>
@@ -7187,7 +7789,7 @@
       </c>
       <c r="Q129" s="16"/>
     </row>
-    <row r="130" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="130" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A130" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1053002</v>
@@ -7230,7 +7832,7 @@
       </c>
       <c r="Q130" s="16"/>
     </row>
-    <row r="131" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="131" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A131" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1057001</v>
@@ -7273,7 +7875,7 @@
       </c>
       <c r="Q131" s="16"/>
     </row>
-    <row r="132" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="132" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A132" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1057002</v>
@@ -7316,7 +7918,7 @@
       </c>
       <c r="Q132" s="16"/>
     </row>
-    <row r="133" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="133" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A133" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1057003</v>
@@ -7359,7 +7961,7 @@
       </c>
       <c r="Q133" s="16"/>
     </row>
-    <row r="134" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="134" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A134" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1058001</v>
@@ -7402,7 +8004,7 @@
       </c>
       <c r="Q134" s="16"/>
     </row>
-    <row r="135" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="135" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A135" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1058002</v>
@@ -7445,7 +8047,7 @@
       </c>
       <c r="Q135" s="16"/>
     </row>
-    <row r="136" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="136" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A136" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1058003</v>
@@ -7488,7 +8090,7 @@
       </c>
       <c r="Q136" s="16"/>
     </row>
-    <row r="137" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="137" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A137" s="43">
         <v>1055001</v>
       </c>
@@ -7530,7 +8132,7 @@
       </c>
       <c r="Q137" s="16"/>
     </row>
-    <row r="138" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="138" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A138" s="43">
         <v>1055002</v>
       </c>
@@ -7572,7 +8174,7 @@
       </c>
       <c r="Q138" s="16"/>
     </row>
-    <row r="139" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="139" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A139" s="43">
         <v>1048001</v>
       </c>
@@ -7614,7 +8216,7 @@
       </c>
       <c r="Q139" s="16"/>
     </row>
-    <row r="140" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="140" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A140" s="43">
         <v>1048002</v>
       </c>
@@ -7656,7 +8258,7 @@
       </c>
       <c r="Q140" s="16"/>
     </row>
-    <row r="141" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="141" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A141" s="43">
         <v>1048003</v>
       </c>
@@ -7698,7 +8300,7 @@
       </c>
       <c r="Q141" s="16"/>
     </row>
-    <row r="142" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="142" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A142" s="43">
         <v>1055011</v>
       </c>
@@ -7740,7 +8342,7 @@
       </c>
       <c r="Q142" s="16"/>
     </row>
-    <row r="143" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="143" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A143" s="43">
         <v>1055012</v>
       </c>
@@ -7782,7 +8384,7 @@
       </c>
       <c r="Q143" s="16"/>
     </row>
-    <row r="144" spans="1:17" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="144" ht="16.5" spans="1:17">
       <c r="A144" s="43">
         <v>1055013</v>
       </c>
@@ -7826,13 +8428,13 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="J2:L2">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(MID($A2,1,4),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\slot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA47324-C04F-44D7-B0A4-9035058B6362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView xWindow="4935" yWindow="3825" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -27,13 +33,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author/>
   </authors>
   <commentList>
-    <comment ref="J1" authorId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -55,7 +61,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="1">
+    <comment ref="N1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -77,7 +83,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="1">
+    <comment ref="O1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -99,7 +105,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J2" authorId="0">
+    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -126,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="281">
   <si>
     <t>id</t>
   </si>
@@ -960,20 +966,28 @@
   </si>
   <si>
     <t>改出小游戏图标</t>
+  </si>
+  <si>
+    <t>伽罗宝石2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>多格图标模式触发</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>改出多格图标</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -999,147 +1013,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1153,8 +1030,28 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="45">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1163,31 +1060,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1211,216 +1108,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.39994506668294322"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1443,254 +1154,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1712,10 +1181,10 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1746,7 +1215,7 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1813,98 +1282,175 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 80" xfId="49"/>
+    <cellStyle name="常规 80" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
   <dxfs count="18">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.799340800195319"/>
+          <bgColor theme="8" tint="0.7993408001953185"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1915,7 +1461,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1943,154 +1489,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="7"/>
-      <tableStyleElement type="headerRow" dxfId="6"/>
-      <tableStyleElement type="totalRow" dxfId="5"/>
-      <tableStyleElement type="firstColumn" dxfId="4"/>
-      <tableStyleElement type="lastColumn" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstColumn" dxfId="14"/>
+      <tableStyleElement type="lastColumn" dxfId="13"/>
+      <tableStyleElement type="firstRowStripe" dxfId="12"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="11"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="totalRow" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
-      <tableStyleElement type="pageFieldValues" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
+      <tableStyleElement type="totalRow" dxfId="9"/>
+      <tableStyleElement type="firstRowStripe" dxfId="8"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="7"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="6"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="4"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="3"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="2"/>
+      <tableStyleElement type="pageFieldValues" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2340,14 +1772,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:S144"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S147"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
     <col min="5" max="5" width="36.375" customWidth="1"/>
@@ -2365,7 +1797,7 @@
     <col min="18" max="18" width="60.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:17">
+    <row r="1" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2403,7 +1835,7 @@
       </c>
       <c r="Q1"/>
     </row>
-    <row r="2" ht="16.5" spans="1:17">
+    <row r="2" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2439,7 +1871,7 @@
       </c>
       <c r="Q2"/>
     </row>
-    <row r="3" ht="16.5" spans="1:17">
+    <row r="3" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -2475,7 +1907,7 @@
       </c>
       <c r="Q3"/>
     </row>
-    <row r="4" ht="16.5" spans="1:17">
+    <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -2492,7 +1924,7 @@
       <c r="O4" s="15"/>
       <c r="Q4"/>
     </row>
-    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:17">
+    <row r="5" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="str">
         <f t="shared" ref="A5:A19" si="0">B5&amp;C5</f>
         <v>1001001</v>
@@ -2536,7 +1968,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="16.5" spans="1:17">
+    <row r="6" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A6" s="22" t="str">
         <f t="shared" si="0"/>
         <v>1001002</v>
@@ -2578,7 +2010,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="16.5" spans="1:17">
+    <row r="7" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="str">
         <f t="shared" si="0"/>
         <v>1001003</v>
@@ -2620,7 +2052,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="16.5" spans="1:17">
+    <row r="8" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="str">
         <f t="shared" si="0"/>
         <v>1001004</v>
@@ -2662,7 +2094,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="16.5" spans="1:17">
+    <row r="9" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="str">
         <f t="shared" si="0"/>
         <v>1001005</v>
@@ -2704,7 +2136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="16.5" spans="1:17">
+    <row r="10" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="str">
         <f t="shared" si="0"/>
         <v>1001006</v>
@@ -2746,7 +2178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="16.5" spans="1:17">
+    <row r="11" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="str">
         <f t="shared" si="0"/>
         <v>1001007</v>
@@ -2788,7 +2220,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" ht="16.5" spans="1:17">
+    <row r="12" spans="1:17" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A12" s="32" t="str">
         <f t="shared" si="0"/>
         <v>1003001</v>
@@ -2833,7 +2265,7 @@
       </c>
       <c r="Q12" s="34"/>
     </row>
-    <row r="13" s="2" customFormat="1" ht="16.5" spans="1:17">
+    <row r="13" spans="1:17" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A13" s="32" t="str">
         <f t="shared" si="0"/>
         <v>1003002</v>
@@ -2876,7 +2308,7 @@
       </c>
       <c r="Q13" s="34"/>
     </row>
-    <row r="14" s="2" customFormat="1" ht="16.5" spans="1:17">
+    <row r="14" spans="1:17" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A14" s="32" t="str">
         <f t="shared" si="0"/>
         <v>1003003</v>
@@ -2923,7 +2355,7 @@
       </c>
       <c r="Q14" s="34"/>
     </row>
-    <row r="15" ht="16.5" spans="1:17">
+    <row r="15" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A15" s="35" t="str">
         <f t="shared" si="0"/>
         <v>1007001</v>
@@ -2968,7 +2400,7 @@
       </c>
       <c r="Q15"/>
     </row>
-    <row r="16" ht="16.5" spans="1:17">
+    <row r="16" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A16" s="35" t="str">
         <f t="shared" si="0"/>
         <v>1007002</v>
@@ -3011,7 +2443,7 @@
       </c>
       <c r="Q16"/>
     </row>
-    <row r="17" s="3" customFormat="1" ht="16.5" spans="1:17">
+    <row r="17" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A17" s="38" t="str">
         <f t="shared" si="0"/>
         <v>1012001</v>
@@ -3056,7 +2488,7 @@
       </c>
       <c r="Q17" s="41"/>
     </row>
-    <row r="18" s="3" customFormat="1" ht="16.5" spans="1:17">
+    <row r="18" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A18" s="38" t="str">
         <f t="shared" si="0"/>
         <v>1012002</v>
@@ -3099,7 +2531,7 @@
       </c>
       <c r="Q18" s="41"/>
     </row>
-    <row r="19" s="3" customFormat="1" ht="16.5" spans="1:17">
+    <row r="19" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A19" s="38" t="str">
         <f t="shared" si="0"/>
         <v>1012003</v>
@@ -3144,7 +2576,7 @@
       </c>
       <c r="Q19" s="41"/>
     </row>
-    <row r="20" ht="16.5" spans="1:17">
+    <row r="20" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A20" s="32" t="str">
         <f t="shared" ref="A20:A30" si="1">B20&amp;C20</f>
         <v>1014001</v>
@@ -3188,7 +2620,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" ht="16.5" spans="1:17">
+    <row r="21" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A21" s="32" t="str">
         <f t="shared" si="1"/>
         <v>1014002</v>
@@ -3232,7 +2664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" ht="16.5" spans="1:17">
+    <row r="22" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A22" s="32" t="str">
         <f t="shared" si="1"/>
         <v>1014003</v>
@@ -3276,7 +2708,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="16.5" spans="1:17">
+    <row r="23" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A23" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024001</v>
@@ -3320,7 +2752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:17">
+    <row r="24" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A24" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024002</v>
@@ -3362,7 +2794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:17">
+    <row r="25" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024003</v>
@@ -3404,7 +2836,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="16.5" spans="1:17">
+    <row r="26" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024004</v>
@@ -3446,7 +2878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:17">
+    <row r="27" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024005</v>
@@ -3488,7 +2920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:17">
+    <row r="28" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A28" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024006</v>
@@ -3530,7 +2962,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:17">
+    <row r="29" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A29" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024007</v>
@@ -3572,7 +3004,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="30" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A30" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1017001</v>
@@ -3615,7 +3047,7 @@
       </c>
       <c r="Q30" s="16"/>
     </row>
-    <row r="31" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="31" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="str">
         <f t="shared" ref="A31:A54" si="2">B31&amp;C31</f>
         <v>1017002</v>
@@ -3658,7 +3090,7 @@
       </c>
       <c r="Q31" s="16"/>
     </row>
-    <row r="32" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="32" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A32" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1017003</v>
@@ -3701,7 +3133,7 @@
       </c>
       <c r="Q32" s="16"/>
     </row>
-    <row r="33" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="33" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A33" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1022001</v>
@@ -3744,7 +3176,7 @@
       </c>
       <c r="Q33" s="16"/>
     </row>
-    <row r="34" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="34" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A34" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1022002</v>
@@ -3787,7 +3219,7 @@
       </c>
       <c r="Q34" s="16"/>
     </row>
-    <row r="35" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="35" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A35" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1022003</v>
@@ -3830,7 +3262,7 @@
       </c>
       <c r="Q35" s="16"/>
     </row>
-    <row r="36" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="36" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A36" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1022004</v>
@@ -3870,7 +3302,7 @@
       </c>
       <c r="Q36" s="16"/>
     </row>
-    <row r="37" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="37" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A37" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1022005</v>
@@ -3911,7 +3343,7 @@
       <c r="Q37" s="16"/>
       <c r="S37" s="44"/>
     </row>
-    <row r="38" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="38" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A38" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1021001</v>
@@ -3955,7 +3387,7 @@
       <c r="Q38" s="16"/>
       <c r="S38" s="44"/>
     </row>
-    <row r="39" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="39" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A39" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1021002</v>
@@ -3999,7 +3431,7 @@
       <c r="Q39" s="16"/>
       <c r="S39" s="44"/>
     </row>
-    <row r="40" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="40" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A40" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1021003</v>
@@ -4043,7 +3475,7 @@
       <c r="Q40" s="16"/>
       <c r="S40" s="44"/>
     </row>
-    <row r="41" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="41" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A41" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1021004</v>
@@ -4087,7 +3519,7 @@
       <c r="Q41" s="16"/>
       <c r="S41" s="44"/>
     </row>
-    <row r="42" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="42" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A42" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1018001</v>
@@ -4131,7 +3563,7 @@
       <c r="Q42" s="16"/>
       <c r="S42" s="44"/>
     </row>
-    <row r="43" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="43" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1018002</v>
@@ -4173,7 +3605,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" ht="16.5" spans="1:19">
+    <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1018003</v>
@@ -4215,7 +3647,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" ht="16.5" spans="1:19">
+    <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1025001</v>
@@ -4257,7 +3689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" ht="16.5" spans="1:19">
+    <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1025002</v>
@@ -4299,7 +3731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" ht="16.5" spans="1:19">
+    <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1025003</v>
@@ -4341,7 +3773,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" ht="16.5" spans="1:19">
+    <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1023001</v>
@@ -4383,7 +3815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" ht="16.5" spans="1:16">
+    <row r="49" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1023002</v>
@@ -4425,7 +3857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" ht="16.5" spans="1:16">
+    <row r="50" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1023003</v>
@@ -4467,7 +3899,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" ht="16.5" spans="1:16">
+    <row r="51" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1034001</v>
@@ -4509,7 +3941,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" ht="16.5" spans="1:16">
+    <row r="52" spans="1:16" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1034002</v>
@@ -4548,7 +3980,7 @@
       </c>
       <c r="P52" s="45"/>
     </row>
-    <row r="53" ht="16.5" spans="1:16">
+    <row r="53" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1034003</v>
@@ -4586,7 +4018,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" ht="16.5" spans="1:16">
+    <row r="54" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1035001</v>
@@ -4628,7 +4060,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" ht="16.5" spans="1:16">
+    <row r="55" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="str">
         <f t="shared" ref="A55:A108" si="3">B55&amp;C55</f>
         <v>1035002</v>
@@ -4670,7 +4102,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" ht="16.5" spans="1:16">
+    <row r="56" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1035003</v>
@@ -4712,7 +4144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" ht="16.5" spans="1:16">
+    <row r="57" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A57" s="43">
         <v>1035011</v>
       </c>
@@ -4753,7 +4185,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" ht="16.5" spans="1:16">
+    <row r="58" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1035012</v>
@@ -4795,7 +4227,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" ht="16.5" spans="1:16">
+    <row r="59" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1035013</v>
@@ -4837,7 +4269,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" ht="16.5" spans="1:16">
+    <row r="60" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1036001</v>
@@ -4879,7 +4311,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" ht="16.5" spans="1:16">
+    <row r="61" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1036002</v>
@@ -4921,7 +4353,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" ht="16.5" spans="1:16">
+    <row r="62" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1036003</v>
@@ -4963,7 +4395,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" ht="16.5" spans="1:16">
+    <row r="63" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1028001</v>
@@ -5005,7 +4437,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" ht="16.5" spans="1:16">
+    <row r="64" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1028002</v>
@@ -5047,7 +4479,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" ht="16.5" spans="1:17">
+    <row r="65" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1028003</v>
@@ -5089,7 +4521,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" ht="16.5" spans="1:17">
+    <row r="66" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1034011</v>
@@ -5131,7 +4563,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" ht="16.5" spans="1:17">
+    <row r="67" spans="1:17" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1034012</v>
@@ -5170,7 +4602,7 @@
       </c>
       <c r="P67" s="45"/>
     </row>
-    <row r="68" s="5" customFormat="1" ht="16.5" spans="1:17">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1034013</v>
@@ -5211,7 +4643,7 @@
       </c>
       <c r="Q68" s="46"/>
     </row>
-    <row r="69" s="5" customFormat="1" ht="16.5" spans="1:17">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A69" s="47" t="str">
         <f t="shared" si="3"/>
         <v>1020001</v>
@@ -5254,7 +4686,7 @@
       </c>
       <c r="Q69" s="46"/>
     </row>
-    <row r="70" ht="16.5" spans="1:17">
+    <row r="70" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1020002</v>
@@ -5296,7 +4728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" ht="16.5" spans="1:17">
+    <row r="71" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1020003</v>
@@ -5338,7 +4770,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" s="6" customFormat="1" ht="16.5" spans="1:17">
+    <row r="72" spans="1:17" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A72" s="50" t="str">
         <f t="shared" si="3"/>
         <v>1020004</v>
@@ -5381,7 +4813,7 @@
       </c>
       <c r="Q72" s="53"/>
     </row>
-    <row r="73" ht="16.5" spans="1:17">
+    <row r="73" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1020005</v>
@@ -5423,7 +4855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" ht="16.5" spans="1:17">
+    <row r="74" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1038001</v>
@@ -5466,7 +4898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" ht="16.5" spans="1:17">
+    <row r="75" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1038002</v>
@@ -5508,7 +4940,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" ht="16.5" spans="1:17">
+    <row r="76" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1038004</v>
@@ -5550,7 +4982,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" ht="16.5" spans="1:17">
+    <row r="77" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1038003</v>
@@ -5592,7 +5024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" ht="16.5" spans="1:17">
+    <row r="78" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1027001</v>
@@ -5634,7 +5066,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" ht="16.5" spans="1:17">
+    <row r="79" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1027002</v>
@@ -5676,7 +5108,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" ht="16.5" spans="1:17">
+    <row r="80" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1027003</v>
@@ -5718,7 +5150,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" ht="16.5" spans="1:17">
+    <row r="81" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1037001</v>
@@ -5760,7 +5192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" ht="16.5" spans="1:17">
+    <row r="82" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1037002</v>
@@ -5802,7 +5234,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" ht="16.5" spans="1:17">
+    <row r="83" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1037003</v>
@@ -5844,7 +5276,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" ht="16.5" spans="1:17">
+    <row r="84" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1031001</v>
@@ -5886,7 +5318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" ht="16.5" spans="1:17">
+    <row r="85" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1031002</v>
@@ -5928,7 +5360,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" ht="16.5" spans="1:17">
+    <row r="86" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1031003</v>
@@ -5970,7 +5402,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" ht="16.5" spans="1:17">
+    <row r="87" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1031004</v>
@@ -6012,7 +5444,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" ht="16.5" spans="1:17">
+    <row r="88" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1031005</v>
@@ -6054,7 +5486,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" ht="16.5" spans="1:17">
+    <row r="89" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1031006</v>
@@ -6096,7 +5528,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" ht="16.5" spans="1:17">
+    <row r="90" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1040001</v>
@@ -6138,7 +5570,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" ht="16.5" spans="1:17">
+    <row r="91" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1040002</v>
@@ -6180,7 +5612,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" ht="16.5" spans="1:17">
+    <row r="92" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1040003</v>
@@ -6222,7 +5654,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="93" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1039001</v>
@@ -6265,7 +5697,7 @@
       </c>
       <c r="Q93" s="16"/>
     </row>
-    <row r="94" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="94" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1039002</v>
@@ -6308,7 +5740,7 @@
       </c>
       <c r="Q94" s="16"/>
     </row>
-    <row r="95" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="95" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1039003</v>
@@ -6351,7 +5783,7 @@
       </c>
       <c r="Q95" s="16"/>
     </row>
-    <row r="96" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="96" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1016001</v>
@@ -6394,7 +5826,7 @@
       </c>
       <c r="Q96" s="16"/>
     </row>
-    <row r="97" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="97" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1016002</v>
@@ -6437,7 +5869,7 @@
       </c>
       <c r="Q97" s="16"/>
     </row>
-    <row r="98" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="98" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1016003</v>
@@ -6480,7 +5912,7 @@
       </c>
       <c r="Q98" s="16"/>
     </row>
-    <row r="99" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="99" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015001</v>
@@ -6523,7 +5955,7 @@
       </c>
       <c r="Q99" s="16"/>
     </row>
-    <row r="100" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="100" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015002</v>
@@ -6566,7 +5998,7 @@
       </c>
       <c r="Q100" s="16"/>
     </row>
-    <row r="101" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="101" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015003</v>
@@ -6609,7 +6041,7 @@
       </c>
       <c r="Q101" s="16"/>
     </row>
-    <row r="102" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="102" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015004</v>
@@ -6652,7 +6084,7 @@
       </c>
       <c r="Q102" s="16"/>
     </row>
-    <row r="103" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="103" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015005</v>
@@ -6695,7 +6127,7 @@
       </c>
       <c r="Q103" s="16"/>
     </row>
-    <row r="104" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="104" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015006</v>
@@ -6738,7 +6170,7 @@
       </c>
       <c r="Q104" s="16"/>
     </row>
-    <row r="105" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="105" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015007</v>
@@ -6781,7 +6213,7 @@
       </c>
       <c r="Q105" s="16"/>
     </row>
-    <row r="106" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="106" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1026001</v>
@@ -6824,7 +6256,7 @@
       </c>
       <c r="Q106" s="16"/>
     </row>
-    <row r="107" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="107" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1026002</v>
@@ -6867,7 +6299,7 @@
       </c>
       <c r="Q107" s="16"/>
     </row>
-    <row r="108" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="108" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1026003</v>
@@ -6910,7 +6342,7 @@
       </c>
       <c r="Q108" s="16"/>
     </row>
-    <row r="109" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="109" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="str">
         <f t="shared" ref="A109:A112" si="4">B109&amp;C109</f>
         <v>1050001</v>
@@ -6953,7 +6385,7 @@
       </c>
       <c r="Q109" s="16"/>
     </row>
-    <row r="110" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="110" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="str">
         <f t="shared" si="4"/>
         <v>1050002</v>
@@ -6996,7 +6428,7 @@
       </c>
       <c r="Q110" s="16"/>
     </row>
-    <row r="111" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="111" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="str">
         <f t="shared" si="4"/>
         <v>1050003</v>
@@ -7039,7 +6471,7 @@
       </c>
       <c r="Q111" s="16"/>
     </row>
-    <row r="112" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="112" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="str">
         <f t="shared" si="4"/>
         <v>1050004</v>
@@ -7082,7 +6514,7 @@
       </c>
       <c r="Q112" s="16"/>
     </row>
-    <row r="113" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="113" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A113" s="43">
         <v>1051001</v>
       </c>
@@ -7119,7 +6551,7 @@
       </c>
       <c r="Q113" s="16"/>
     </row>
-    <row r="114" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="114" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A114" s="43">
         <v>1051002</v>
       </c>
@@ -7156,7 +6588,7 @@
       </c>
       <c r="Q114" s="16"/>
     </row>
-    <row r="115" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="115" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A115" s="43">
         <v>1051003</v>
       </c>
@@ -7193,7 +6625,7 @@
       </c>
       <c r="Q115" s="16"/>
     </row>
-    <row r="116" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="116" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A116" s="43">
         <v>1051004</v>
       </c>
@@ -7235,7 +6667,7 @@
       </c>
       <c r="Q116" s="16"/>
     </row>
-    <row r="117" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="117" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A117" s="43">
         <v>1051005</v>
       </c>
@@ -7277,7 +6709,7 @@
       </c>
       <c r="Q117" s="16"/>
     </row>
-    <row r="118" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="118" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A118" s="43">
         <v>1051006</v>
       </c>
@@ -7319,7 +6751,7 @@
       </c>
       <c r="Q118" s="16"/>
     </row>
-    <row r="119" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="119" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A119" s="43">
         <v>1051007</v>
       </c>
@@ -7361,7 +6793,7 @@
       </c>
       <c r="Q119" s="16"/>
     </row>
-    <row r="120" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="120" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A120" s="43">
         <v>1051008</v>
       </c>
@@ -7403,7 +6835,7 @@
       </c>
       <c r="Q120" s="16"/>
     </row>
-    <row r="121" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="121" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A121" s="43">
         <v>1051009</v>
       </c>
@@ -7445,7 +6877,7 @@
       </c>
       <c r="Q121" s="16"/>
     </row>
-    <row r="122" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="122" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="str">
         <f t="shared" ref="A122:A136" si="5">B122&amp;C122</f>
         <v>1054001</v>
@@ -7488,7 +6920,7 @@
       </c>
       <c r="Q122" s="16"/>
     </row>
-    <row r="123" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="123" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1054002</v>
@@ -7531,7 +6963,7 @@
       </c>
       <c r="Q123" s="16"/>
     </row>
-    <row r="124" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="124" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1054003</v>
@@ -7574,7 +7006,7 @@
       </c>
       <c r="Q124" s="16"/>
     </row>
-    <row r="125" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="125" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1054004</v>
@@ -7617,7 +7049,7 @@
       </c>
       <c r="Q125" s="16"/>
     </row>
-    <row r="126" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="126" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1008001</v>
@@ -7660,7 +7092,7 @@
       </c>
       <c r="Q126" s="16"/>
     </row>
-    <row r="127" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="127" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1008002</v>
@@ -7703,7 +7135,7 @@
       </c>
       <c r="Q127" s="16"/>
     </row>
-    <row r="128" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="128" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1008003</v>
@@ -7746,7 +7178,7 @@
       </c>
       <c r="Q128" s="16"/>
     </row>
-    <row r="129" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="129" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1053001</v>
@@ -7789,7 +7221,7 @@
       </c>
       <c r="Q129" s="16"/>
     </row>
-    <row r="130" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="130" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1053002</v>
@@ -7832,7 +7264,7 @@
       </c>
       <c r="Q130" s="16"/>
     </row>
-    <row r="131" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="131" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1057001</v>
@@ -7875,7 +7307,7 @@
       </c>
       <c r="Q131" s="16"/>
     </row>
-    <row r="132" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="132" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1057002</v>
@@ -7918,7 +7350,7 @@
       </c>
       <c r="Q132" s="16"/>
     </row>
-    <row r="133" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="133" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1057003</v>
@@ -7961,7 +7393,7 @@
       </c>
       <c r="Q133" s="16"/>
     </row>
-    <row r="134" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="134" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1058001</v>
@@ -8004,7 +7436,7 @@
       </c>
       <c r="Q134" s="16"/>
     </row>
-    <row r="135" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="135" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1058002</v>
@@ -8047,7 +7479,7 @@
       </c>
       <c r="Q135" s="16"/>
     </row>
-    <row r="136" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="136" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1058003</v>
@@ -8090,7 +7522,7 @@
       </c>
       <c r="Q136" s="16"/>
     </row>
-    <row r="137" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="137" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A137" s="43">
         <v>1055001</v>
       </c>
@@ -8132,7 +7564,7 @@
       </c>
       <c r="Q137" s="16"/>
     </row>
-    <row r="138" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="138" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A138" s="43">
         <v>1055002</v>
       </c>
@@ -8174,7 +7606,7 @@
       </c>
       <c r="Q138" s="16"/>
     </row>
-    <row r="139" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="139" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A139" s="43">
         <v>1048001</v>
       </c>
@@ -8216,7 +7648,7 @@
       </c>
       <c r="Q139" s="16"/>
     </row>
-    <row r="140" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="140" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A140" s="43">
         <v>1048002</v>
       </c>
@@ -8258,7 +7690,7 @@
       </c>
       <c r="Q140" s="16"/>
     </row>
-    <row r="141" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="141" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A141" s="43">
         <v>1048003</v>
       </c>
@@ -8300,7 +7732,7 @@
       </c>
       <c r="Q141" s="16"/>
     </row>
-    <row r="142" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="142" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A142" s="43">
         <v>1055011</v>
       </c>
@@ -8342,7 +7774,7 @@
       </c>
       <c r="Q142" s="16"/>
     </row>
-    <row r="143" s="4" customFormat="1" ht="16.5" spans="1:17">
+    <row r="143" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A143" s="43">
         <v>1055012</v>
       </c>
@@ -8384,7 +7816,7 @@
       </c>
       <c r="Q143" s="16"/>
     </row>
-    <row r="144" ht="16.5" spans="1:17">
+    <row r="144" spans="1:17" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A144" s="43">
         <v>1055013</v>
       </c>
@@ -8427,14 +7859,139 @@
         <v>4</v>
       </c>
     </row>
+    <row r="145" spans="1:17" s="57" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A145" s="56">
+        <v>1055021</v>
+      </c>
+      <c r="B145" s="57">
+        <v>105502</v>
+      </c>
+      <c r="C145" s="57">
+        <v>1</v>
+      </c>
+      <c r="D145" s="57" t="s">
+        <v>278</v>
+      </c>
+      <c r="E145" s="57" t="s">
+        <v>22</v>
+      </c>
+      <c r="F145" s="57">
+        <v>1</v>
+      </c>
+      <c r="G145" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="H145" s="57">
+        <v>2055021</v>
+      </c>
+      <c r="I145" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="L145" s="56">
+        <v>10550202</v>
+      </c>
+      <c r="M145" s="57" t="s">
+        <v>108</v>
+      </c>
+      <c r="N145" s="58">
+        <v>3</v>
+      </c>
+      <c r="O145" s="58">
+        <v>4</v>
+      </c>
+      <c r="Q145" s="59"/>
+    </row>
+    <row r="146" spans="1:17" s="57" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A146" s="56">
+        <v>1055022</v>
+      </c>
+      <c r="B146" s="57">
+        <v>105502</v>
+      </c>
+      <c r="C146" s="57">
+        <v>2</v>
+      </c>
+      <c r="D146" s="57" t="s">
+        <v>278</v>
+      </c>
+      <c r="E146" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="F146" s="57">
+        <v>1</v>
+      </c>
+      <c r="G146" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="H146" s="57">
+        <v>2055021</v>
+      </c>
+      <c r="I146" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="L146" s="56">
+        <v>10550201</v>
+      </c>
+      <c r="M146" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="N146" s="58">
+        <v>3</v>
+      </c>
+      <c r="O146" s="58">
+        <v>4</v>
+      </c>
+      <c r="Q146" s="59"/>
+    </row>
+    <row r="147" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A147" s="56">
+        <v>1055023</v>
+      </c>
+      <c r="B147" s="57">
+        <v>105502</v>
+      </c>
+      <c r="C147" s="57">
+        <v>3</v>
+      </c>
+      <c r="D147" s="57" t="s">
+        <v>278</v>
+      </c>
+      <c r="E147" s="57" t="s">
+        <v>279</v>
+      </c>
+      <c r="F147" s="57">
+        <v>1</v>
+      </c>
+      <c r="G147" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="H147" s="57">
+        <v>2055021</v>
+      </c>
+      <c r="I147" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="L147" s="56">
+        <v>10550203</v>
+      </c>
+      <c r="M147" s="57" t="s">
+        <v>280</v>
+      </c>
+      <c r="N147" s="58">
+        <v>3</v>
+      </c>
+      <c r="O147" s="58">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="J2:L2">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(MID($A2,1,4),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\slot\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA47324-C04F-44D7-B0A4-9035058B6362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4935" yWindow="3825" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="14460" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -33,13 +27,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author/>
   </authors>
   <commentList>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -61,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="N1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -83,7 +77,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="O1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -105,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="J2" authorId="0">
       <text>
         <r>
           <rPr>
@@ -132,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="290">
   <si>
     <t>id</t>
   </si>
@@ -969,31 +963,65 @@
   </si>
   <si>
     <t>伽罗宝石2</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>多格图标模式触发</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>改出多格图标</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗨到底</t>
+  </si>
+  <si>
+    <t>10410001|10410003</t>
+  </si>
+  <si>
+    <t>概率改出wild符号+概率改出scatter符号</t>
+  </si>
+  <si>
+    <t>改出3个scatter符号</t>
+  </si>
+  <si>
+    <t>10410005|10410004</t>
+  </si>
+  <si>
+    <t>概率改出2个SCATTER+改出奖池符号</t>
+  </si>
+  <si>
+    <t>狂野沙滩</t>
+  </si>
+  <si>
+    <t>10420001|10420003</t>
+  </si>
+  <si>
+    <t>10420005|10420004</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1013,10 +1041,147 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1030,28 +1195,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="14">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1060,31 +1205,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79995117038483843"/>
+        <fgColor theme="7" tint="0.799951170384838"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79995117038483843"/>
+        <fgColor theme="5" tint="0.799951170384838"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79995117038483843"/>
+        <fgColor theme="4" tint="0.799951170384838"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1108,30 +1253,216 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79995117038483843"/>
+        <fgColor theme="8" tint="0.799951170384838"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79995117038483843"/>
+        <fgColor theme="9" tint="0.799951170384838"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39994506668294322"/>
+        <fgColor theme="8" tint="0.399945066682943"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79995117038483843"/>
+        <fgColor theme="6" tint="0.799951170384838"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1154,12 +1485,254 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1167,6 +1740,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1178,13 +1752,13 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1215,7 +1789,7 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1259,7 +1833,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1282,175 +1856,115 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 80" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 80" xfId="49"/>
   </cellStyles>
   <dxfs count="18">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
+          <bgColor theme="8" tint="0.799340800195319"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -1461,7 +1975,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1489,40 +2003,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="17"/>
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstColumn" dxfId="14"/>
-      <tableStyleElement type="lastColumn" dxfId="13"/>
-      <tableStyleElement type="firstRowStripe" dxfId="12"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="11"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="10"/>
-      <tableStyleElement type="totalRow" dxfId="9"/>
-      <tableStyleElement type="firstRowStripe" dxfId="8"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="7"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="6"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="4"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="3"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="2"/>
-      <tableStyleElement type="pageFieldValues" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1772,14 +2400,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S147"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:S153"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
     <col min="5" max="5" width="36.375" customWidth="1"/>
@@ -1791,13 +2419,13 @@
     <col min="11" max="11" width="16.75" customWidth="1"/>
     <col min="12" max="12" width="53.25" customWidth="1"/>
     <col min="13" max="13" width="21.625" customWidth="1"/>
-    <col min="14" max="15" width="9" style="7"/>
+    <col min="14" max="15" width="9" style="8"/>
     <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="23.75" style="8" customWidth="1"/>
+    <col min="17" max="17" width="23.75" style="9" customWidth="1"/>
     <col min="18" max="18" width="60.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" ht="16.5" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1809,33 +2437,33 @@
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="4"/>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="4"/>
-      <c r="J1" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="10"/>
-      <c r="L1" s="11" t="s">
+      <c r="J1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="11"/>
+      <c r="L1" s="12" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="13" t="s">
         <v>9</v>
       </c>
       <c r="Q1"/>
     </row>
-    <row r="2" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="2" ht="16.5" spans="1:17">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1847,1165 +2475,1165 @@
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="4"/>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="10" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="4"/>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="14" t="s">
+      <c r="K2" s="14"/>
+      <c r="L2" s="15" t="s">
         <v>12</v>
       </c>
       <c r="M2" s="4"/>
-      <c r="N2" s="15" t="s">
+      <c r="N2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="15" t="s">
+      <c r="O2" s="16" t="s">
         <v>10</v>
       </c>
       <c r="Q2"/>
     </row>
-    <row r="3" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="3" ht="16.5" spans="1:17">
       <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="17" t="s">
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="18" t="s">
+      <c r="G3" s="17"/>
+      <c r="H3" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="16"/>
-      <c r="J3" s="19" t="s">
+      <c r="I3" s="17"/>
+      <c r="J3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="19"/>
-      <c r="L3" s="20" t="s">
+      <c r="K3" s="20"/>
+      <c r="L3" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="16"/>
-      <c r="N3" s="15" t="s">
+      <c r="M3" s="17"/>
+      <c r="N3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="15" t="s">
+      <c r="O3" s="16" t="s">
         <v>20</v>
       </c>
       <c r="Q3"/>
     </row>
-    <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="4" ht="16.5" spans="1:17">
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="9"/>
+      <c r="F4" s="10"/>
       <c r="G4" s="4"/>
-      <c r="H4" s="9"/>
+      <c r="H4" s="10"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="11"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="12"/>
       <c r="M4" s="4"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
       <c r="Q4"/>
     </row>
-    <row r="5" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="22" t="str">
+    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A5" s="23" t="str">
         <f t="shared" ref="A5:A19" si="0">B5&amp;C5</f>
         <v>1001001</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="24">
         <v>100100</v>
       </c>
-      <c r="C5" s="23">
-        <v>1</v>
-      </c>
-      <c r="D5" s="23" t="s">
+      <c r="C5" s="24">
+        <v>1</v>
+      </c>
+      <c r="D5" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="23">
-        <v>1</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="22">
+      <c r="F5" s="24">
+        <v>1</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="23">
         <v>2001001</v>
       </c>
-      <c r="I5" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="25" t="s">
+      <c r="I5" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="22" t="s">
+      <c r="M5" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="15">
+      <c r="N5" s="16">
         <v>4</v>
       </c>
-      <c r="O5" s="15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="22" t="str">
+      <c r="O5" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A6" s="23" t="str">
         <f t="shared" si="0"/>
         <v>1001002</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="24">
         <v>100100</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="24">
         <v>2</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="26" t="s">
+      <c r="D6" s="24"/>
+      <c r="E6" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="23">
-        <v>1</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="22">
+      <c r="F6" s="24">
+        <v>1</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="23">
         <v>2001001</v>
       </c>
-      <c r="I6" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="27" t="s">
+      <c r="I6" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="22" t="s">
+      <c r="M6" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="15">
+      <c r="N6" s="16">
         <v>4</v>
       </c>
-      <c r="O6" s="15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="22" t="str">
+      <c r="O6" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A7" s="23" t="str">
         <f t="shared" si="0"/>
         <v>1001003</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="24">
         <v>100100</v>
       </c>
-      <c r="C7" s="23">
-        <v>3</v>
-      </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="28" t="s">
+      <c r="C7" s="24">
+        <v>3</v>
+      </c>
+      <c r="D7" s="24"/>
+      <c r="E7" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="23">
-        <v>1</v>
-      </c>
-      <c r="G7" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="22">
+      <c r="F7" s="24">
+        <v>1</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="23">
         <v>2001001</v>
       </c>
-      <c r="I7" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="25" t="s">
+      <c r="I7" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="M7" s="22" t="s">
+      <c r="M7" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="15">
+      <c r="N7" s="16">
         <v>4</v>
       </c>
-      <c r="O7" s="15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="22" t="str">
+      <c r="O7" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A8" s="23" t="str">
         <f t="shared" si="0"/>
         <v>1001004</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="24">
         <v>100100</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="24">
         <v>4</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="29" t="s">
+      <c r="D8" s="24"/>
+      <c r="E8" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="30">
-        <v>1</v>
-      </c>
-      <c r="G8" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="22">
+      <c r="F8" s="31">
+        <v>1</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="23">
         <v>2001001</v>
       </c>
-      <c r="I8" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="25">
+      <c r="I8" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="26">
         <v>10010041</v>
       </c>
-      <c r="M8" s="22" t="s">
+      <c r="M8" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="15">
+      <c r="N8" s="16">
         <v>4</v>
       </c>
-      <c r="O8" s="15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="22" t="str">
+      <c r="O8" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A9" s="23" t="str">
         <f t="shared" si="0"/>
         <v>1001005</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="24">
         <v>100100</v>
       </c>
-      <c r="C9" s="23">
-        <v>5</v>
-      </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="31" t="s">
+      <c r="C9" s="24">
+        <v>5</v>
+      </c>
+      <c r="D9" s="24"/>
+      <c r="E9" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="30">
-        <v>1</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="22">
+      <c r="F9" s="31">
+        <v>1</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="23">
         <v>2001001</v>
       </c>
-      <c r="I9" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="25" t="s">
+      <c r="I9" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="22" t="s">
+      <c r="M9" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="N9" s="15">
+      <c r="N9" s="16">
         <v>4</v>
       </c>
-      <c r="O9" s="15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="22" t="str">
+      <c r="O9" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A10" s="23" t="str">
         <f t="shared" si="0"/>
         <v>1001006</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="24">
         <v>100100</v>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="24">
         <v>6</v>
       </c>
-      <c r="D10" s="23"/>
-      <c r="E10" s="31" t="s">
+      <c r="D10" s="24"/>
+      <c r="E10" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="30">
-        <v>1</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="22">
+      <c r="F10" s="31">
+        <v>1</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="23">
         <v>2001001</v>
       </c>
-      <c r="I10" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="25">
+      <c r="I10" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="26">
         <v>10010061</v>
       </c>
-      <c r="M10" s="22" t="s">
+      <c r="M10" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="15">
+      <c r="N10" s="16">
         <v>4</v>
       </c>
-      <c r="O10" s="15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="22" t="str">
+      <c r="O10" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A11" s="23" t="str">
         <f t="shared" si="0"/>
         <v>1001007</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="24">
         <v>100100</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="24">
         <v>7</v>
       </c>
-      <c r="D11" s="23"/>
-      <c r="E11" s="26" t="s">
+      <c r="D11" s="24"/>
+      <c r="E11" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="23">
-        <v>1</v>
-      </c>
-      <c r="G11" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="22">
+      <c r="F11" s="24">
+        <v>1</v>
+      </c>
+      <c r="G11" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="23">
         <v>2001001</v>
       </c>
-      <c r="I11" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="27" t="s">
+      <c r="I11" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="M11" s="22" t="s">
+      <c r="M11" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="N11" s="15">
+      <c r="N11" s="16">
         <v>4</v>
       </c>
-      <c r="O11" s="15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="32" t="str">
+      <c r="O11" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A12" s="33" t="str">
         <f t="shared" si="0"/>
         <v>1003001</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="25">
         <v>100300</v>
       </c>
-      <c r="C12" s="24">
-        <v>1</v>
-      </c>
-      <c r="D12" s="24" t="s">
+      <c r="C12" s="25">
+        <v>1</v>
+      </c>
+      <c r="D12" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="24">
-        <v>1</v>
-      </c>
-      <c r="G12" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="32">
+      <c r="F12" s="25">
+        <v>1</v>
+      </c>
+      <c r="G12" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="33">
         <v>2003001</v>
       </c>
-      <c r="I12" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="33">
+      <c r="I12" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="34">
         <v>10030022</v>
       </c>
-      <c r="M12" s="32" t="s">
+      <c r="M12" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="N12" s="24">
-        <v>3</v>
-      </c>
-      <c r="O12" s="24">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="34"/>
-    </row>
-    <row r="13" spans="1:17" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="32" t="str">
+      <c r="N12" s="25">
+        <v>3</v>
+      </c>
+      <c r="O12" s="25">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="35"/>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A13" s="33" t="str">
         <f t="shared" si="0"/>
         <v>1003002</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="25">
         <v>100300</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="25">
         <v>2</v>
       </c>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24" t="s">
+      <c r="D13" s="25"/>
+      <c r="E13" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="24">
-        <v>1</v>
-      </c>
-      <c r="G13" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="32">
+      <c r="F13" s="25">
+        <v>1</v>
+      </c>
+      <c r="G13" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="33">
         <v>2003001</v>
       </c>
-      <c r="I13" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="33" t="s">
+      <c r="I13" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="32" t="s">
+      <c r="M13" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="N13" s="24">
-        <v>3</v>
-      </c>
-      <c r="O13" s="24">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="34"/>
-    </row>
-    <row r="14" spans="1:17" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="32" t="str">
+      <c r="N13" s="25">
+        <v>3</v>
+      </c>
+      <c r="O13" s="25">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="35"/>
+    </row>
+    <row r="14" s="2" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A14" s="33" t="str">
         <f t="shared" si="0"/>
         <v>1003003</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="25">
         <v>100300</v>
       </c>
-      <c r="C14" s="24">
-        <v>3</v>
-      </c>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24" t="s">
+      <c r="C14" s="25">
+        <v>3</v>
+      </c>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="24">
-        <v>1</v>
-      </c>
-      <c r="G14" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="32">
+      <c r="F14" s="25">
+        <v>1</v>
+      </c>
+      <c r="G14" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="33">
         <v>2003002</v>
       </c>
-      <c r="I14" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="32" t="s">
+      <c r="I14" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="32" t="s">
+      <c r="K14" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="33" t="s">
+      <c r="L14" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="32" t="s">
+      <c r="M14" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="24">
-        <v>3</v>
-      </c>
-      <c r="O14" s="24">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="34"/>
-    </row>
-    <row r="15" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="35" t="str">
+      <c r="N14" s="25">
+        <v>3</v>
+      </c>
+      <c r="O14" s="25">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="35"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:17">
+      <c r="A15" s="36" t="str">
         <f t="shared" si="0"/>
         <v>1007001</v>
       </c>
-      <c r="B15" s="36">
+      <c r="B15" s="37">
         <v>100700</v>
       </c>
-      <c r="C15" s="36">
-        <v>1</v>
-      </c>
-      <c r="D15" s="36" t="s">
+      <c r="C15" s="37">
+        <v>1</v>
+      </c>
+      <c r="D15" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="36" t="s">
+      <c r="E15" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="36">
-        <v>1</v>
-      </c>
-      <c r="G15" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="35">
+      <c r="F15" s="37">
+        <v>1</v>
+      </c>
+      <c r="G15" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="36">
         <v>2007001</v>
       </c>
-      <c r="I15" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="35"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="37" t="s">
+      <c r="I15" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="36"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="M15" s="35" t="s">
+      <c r="M15" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="N15" s="15">
+      <c r="N15" s="16">
         <v>4</v>
       </c>
-      <c r="O15" s="15">
+      <c r="O15" s="16">
         <v>5</v>
       </c>
       <c r="Q15"/>
     </row>
-    <row r="16" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="35" t="str">
+    <row r="16" ht="16.5" spans="1:17">
+      <c r="A16" s="36" t="str">
         <f t="shared" si="0"/>
         <v>1007002</v>
       </c>
-      <c r="B16" s="36">
+      <c r="B16" s="37">
         <v>100700</v>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="37">
         <v>2</v>
       </c>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36" t="s">
+      <c r="D16" s="37"/>
+      <c r="E16" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="36">
-        <v>1</v>
-      </c>
-      <c r="G16" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="35">
+      <c r="F16" s="37">
+        <v>1</v>
+      </c>
+      <c r="G16" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="36">
         <v>2007001</v>
       </c>
-      <c r="I16" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="37" t="s">
+      <c r="I16" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="36"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="35" t="s">
+      <c r="M16" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="15">
+      <c r="N16" s="16">
         <v>4</v>
       </c>
-      <c r="O16" s="15">
+      <c r="O16" s="16">
         <v>5</v>
       </c>
       <c r="Q16"/>
     </row>
-    <row r="17" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="38" t="str">
+    <row r="17" s="3" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A17" s="39" t="str">
         <f t="shared" si="0"/>
         <v>1012001</v>
       </c>
-      <c r="B17" s="39">
+      <c r="B17" s="40">
         <v>101200</v>
       </c>
-      <c r="C17" s="39">
-        <v>1</v>
-      </c>
-      <c r="D17" s="39" t="s">
+      <c r="C17" s="40">
+        <v>1</v>
+      </c>
+      <c r="D17" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E17" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="39">
-        <v>1</v>
-      </c>
-      <c r="G17" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="38">
+      <c r="F17" s="40">
+        <v>1</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="39">
         <v>2012001</v>
       </c>
-      <c r="I17" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="40">
+      <c r="I17" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="41">
         <v>10120011</v>
       </c>
-      <c r="M17" s="38" t="s">
+      <c r="M17" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="N17" s="39">
-        <v>3</v>
-      </c>
-      <c r="O17" s="39">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="41"/>
-    </row>
-    <row r="18" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="38" t="str">
+      <c r="N17" s="40">
+        <v>3</v>
+      </c>
+      <c r="O17" s="40">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="42"/>
+    </row>
+    <row r="18" s="3" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A18" s="39" t="str">
         <f t="shared" si="0"/>
         <v>1012002</v>
       </c>
-      <c r="B18" s="39">
+      <c r="B18" s="40">
         <v>101200</v>
       </c>
-      <c r="C18" s="39">
+      <c r="C18" s="40">
         <v>2</v>
       </c>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39" t="s">
+      <c r="D18" s="40"/>
+      <c r="E18" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="39">
-        <v>1</v>
-      </c>
-      <c r="G18" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="38">
+      <c r="F18" s="40">
+        <v>1</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="39">
         <v>2012001</v>
       </c>
-      <c r="I18" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="38"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="40">
+      <c r="I18" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="39"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="41">
         <v>10120021</v>
       </c>
-      <c r="M18" s="38" t="s">
+      <c r="M18" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="N18" s="39">
-        <v>3</v>
-      </c>
-      <c r="O18" s="39">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="41"/>
-    </row>
-    <row r="19" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="38" t="str">
+      <c r="N18" s="40">
+        <v>3</v>
+      </c>
+      <c r="O18" s="40">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="42"/>
+    </row>
+    <row r="19" s="3" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A19" s="39" t="str">
         <f t="shared" si="0"/>
         <v>1012003</v>
       </c>
-      <c r="B19" s="39">
+      <c r="B19" s="40">
         <v>101200</v>
       </c>
-      <c r="C19" s="39">
-        <v>3</v>
-      </c>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39" t="s">
+      <c r="C19" s="40">
+        <v>3</v>
+      </c>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="39">
-        <v>1</v>
-      </c>
-      <c r="G19" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" s="38">
+      <c r="F19" s="40">
+        <v>1</v>
+      </c>
+      <c r="G19" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="39">
         <v>2012001</v>
       </c>
-      <c r="I19" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="38" t="s">
+      <c r="I19" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="K19" s="38" t="s">
+      <c r="K19" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="L19" s="40"/>
-      <c r="M19" s="38" t="s">
+      <c r="L19" s="41"/>
+      <c r="M19" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="N19" s="39">
-        <v>3</v>
-      </c>
-      <c r="O19" s="39">
-        <v>5</v>
-      </c>
-      <c r="Q19" s="41"/>
-    </row>
-    <row r="20" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="32" t="str">
+      <c r="N19" s="40">
+        <v>3</v>
+      </c>
+      <c r="O19" s="40">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="42"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:17">
+      <c r="A20" s="33" t="str">
         <f t="shared" ref="A20:A30" si="1">B20&amp;C20</f>
         <v>1014001</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="25">
         <v>101400</v>
       </c>
-      <c r="C20" s="24">
-        <v>1</v>
-      </c>
-      <c r="D20" s="24" t="s">
+      <c r="C20" s="25">
+        <v>1</v>
+      </c>
+      <c r="D20" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="24">
-        <v>1</v>
-      </c>
-      <c r="G20" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="32">
+      <c r="F20" s="25">
+        <v>1</v>
+      </c>
+      <c r="G20" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="33">
         <v>2014001</v>
       </c>
-      <c r="I20" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="33" t="s">
+      <c r="I20" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="M20" s="32" t="s">
+      <c r="M20" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="N20" s="15">
+      <c r="N20" s="16">
         <v>4</v>
       </c>
-      <c r="O20" s="15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="32" t="str">
+      <c r="O20" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:17">
+      <c r="A21" s="33" t="str">
         <f t="shared" si="1"/>
         <v>1014002</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B21" s="25">
         <v>101400</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="25">
         <v>2</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="24">
-        <v>1</v>
-      </c>
-      <c r="G21" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="32">
+      <c r="F21" s="25">
+        <v>1</v>
+      </c>
+      <c r="G21" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="33">
         <v>2014001</v>
       </c>
-      <c r="I21" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="33" t="s">
+      <c r="I21" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="32" t="s">
+      <c r="M21" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="N21" s="15">
+      <c r="N21" s="16">
         <v>4</v>
       </c>
-      <c r="O21" s="15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="32" t="str">
+      <c r="O21" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:17">
+      <c r="A22" s="33" t="str">
         <f t="shared" si="1"/>
         <v>1014003</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B22" s="25">
         <v>101400</v>
       </c>
-      <c r="C22" s="24">
-        <v>3</v>
-      </c>
-      <c r="D22" s="24" t="s">
+      <c r="C22" s="25">
+        <v>3</v>
+      </c>
+      <c r="D22" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="24">
-        <v>1</v>
-      </c>
-      <c r="G22" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="32">
+      <c r="F22" s="25">
+        <v>1</v>
+      </c>
+      <c r="G22" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="33">
         <v>2014001</v>
       </c>
-      <c r="I22" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="33">
+      <c r="I22" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="34">
         <v>10140021</v>
       </c>
-      <c r="M22" s="32" t="s">
+      <c r="M22" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="N22" s="15">
+      <c r="N22" s="16">
         <v>4</v>
       </c>
-      <c r="O22" s="15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="22" t="str">
+      <c r="O22" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A23" s="23" t="str">
         <f t="shared" si="1"/>
         <v>1024001</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="24">
         <v>102400</v>
       </c>
-      <c r="C23" s="23">
-        <v>1</v>
-      </c>
-      <c r="D23" s="23" t="s">
+      <c r="C23" s="24">
+        <v>1</v>
+      </c>
+      <c r="D23" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="23">
-        <v>1</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="22">
+      <c r="F23" s="24">
+        <v>1</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="23">
         <v>2024001</v>
       </c>
-      <c r="I23" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="25" t="s">
+      <c r="I23" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="M23" s="22" t="s">
+      <c r="M23" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="N23" s="15">
+      <c r="N23" s="16">
         <v>4</v>
       </c>
-      <c r="O23" s="15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="22" t="str">
+      <c r="O23" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A24" s="23" t="str">
         <f t="shared" si="1"/>
         <v>1024002</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B24" s="24">
         <v>102400</v>
       </c>
-      <c r="C24" s="23">
+      <c r="C24" s="24">
         <v>2</v>
       </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="26" t="s">
+      <c r="D24" s="24"/>
+      <c r="E24" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="23">
-        <v>1</v>
-      </c>
-      <c r="G24" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="22">
+      <c r="F24" s="24">
+        <v>1</v>
+      </c>
+      <c r="G24" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="23">
         <v>2024001</v>
       </c>
-      <c r="I24" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="27" t="s">
+      <c r="I24" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="M24" s="22" t="s">
+      <c r="M24" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="N24" s="15">
+      <c r="N24" s="16">
         <v>4</v>
       </c>
-      <c r="O24" s="15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="22" t="str">
+      <c r="O24" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A25" s="23" t="str">
         <f t="shared" si="1"/>
         <v>1024003</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B25" s="24">
         <v>102400</v>
       </c>
-      <c r="C25" s="23">
-        <v>3</v>
-      </c>
-      <c r="D25" s="23"/>
-      <c r="E25" s="28" t="s">
+      <c r="C25" s="24">
+        <v>3</v>
+      </c>
+      <c r="D25" s="24"/>
+      <c r="E25" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="23">
-        <v>1</v>
-      </c>
-      <c r="G25" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="22">
+      <c r="F25" s="24">
+        <v>1</v>
+      </c>
+      <c r="G25" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="23">
         <v>2024001</v>
       </c>
-      <c r="I25" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="25" t="s">
+      <c r="I25" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="M25" s="22" t="s">
+      <c r="M25" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="N25" s="15">
+      <c r="N25" s="16">
         <v>4</v>
       </c>
-      <c r="O25" s="15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="22" t="str">
+      <c r="O25" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A26" s="23" t="str">
         <f t="shared" si="1"/>
         <v>1024004</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B26" s="24">
         <v>102400</v>
       </c>
-      <c r="C26" s="23">
+      <c r="C26" s="24">
         <v>4</v>
       </c>
-      <c r="D26" s="23"/>
-      <c r="E26" s="29" t="s">
+      <c r="D26" s="24"/>
+      <c r="E26" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="30">
-        <v>1</v>
-      </c>
-      <c r="G26" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="22">
+      <c r="F26" s="31">
+        <v>1</v>
+      </c>
+      <c r="G26" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="23">
         <v>2024001</v>
       </c>
-      <c r="I26" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="25">
+      <c r="I26" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="26">
         <v>10240041</v>
       </c>
-      <c r="M26" s="22" t="s">
+      <c r="M26" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="N26" s="15">
+      <c r="N26" s="16">
         <v>4</v>
       </c>
-      <c r="O26" s="15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="22" t="str">
+      <c r="O26" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A27" s="23" t="str">
         <f t="shared" si="1"/>
         <v>1024005</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B27" s="24">
         <v>102400</v>
       </c>
-      <c r="C27" s="23">
-        <v>5</v>
-      </c>
-      <c r="D27" s="23"/>
-      <c r="E27" s="31" t="s">
+      <c r="C27" s="24">
+        <v>5</v>
+      </c>
+      <c r="D27" s="24"/>
+      <c r="E27" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="F27" s="30">
-        <v>1</v>
-      </c>
-      <c r="G27" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="22">
+      <c r="F27" s="31">
+        <v>1</v>
+      </c>
+      <c r="G27" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="23">
         <v>2024001</v>
       </c>
-      <c r="I27" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="25" t="s">
+      <c r="I27" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="M27" s="22" t="s">
+      <c r="M27" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="N27" s="15">
+      <c r="N27" s="16">
         <v>4</v>
       </c>
-      <c r="O27" s="15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="22" t="str">
+      <c r="O27" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A28" s="23" t="str">
         <f t="shared" si="1"/>
         <v>1024006</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B28" s="24">
         <v>102400</v>
       </c>
-      <c r="C28" s="23">
+      <c r="C28" s="24">
         <v>6</v>
       </c>
-      <c r="D28" s="23"/>
-      <c r="E28" s="31" t="s">
+      <c r="D28" s="24"/>
+      <c r="E28" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="30">
-        <v>1</v>
-      </c>
-      <c r="G28" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="22">
+      <c r="F28" s="31">
+        <v>1</v>
+      </c>
+      <c r="G28" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="23">
         <v>2024001</v>
       </c>
-      <c r="I28" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="25">
+      <c r="I28" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="26">
         <v>10240061</v>
       </c>
-      <c r="M28" s="22" t="s">
+      <c r="M28" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="N28" s="15">
+      <c r="N28" s="16">
         <v>4</v>
       </c>
-      <c r="O28" s="15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="22" t="str">
+      <c r="O28" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A29" s="23" t="str">
         <f t="shared" si="1"/>
         <v>1024007</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B29" s="24">
         <v>102400</v>
       </c>
-      <c r="C29" s="23">
+      <c r="C29" s="24">
         <v>7</v>
       </c>
-      <c r="D29" s="23"/>
-      <c r="E29" s="26" t="s">
+      <c r="D29" s="24"/>
+      <c r="E29" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="23">
-        <v>1</v>
-      </c>
-      <c r="G29" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="22">
+      <c r="F29" s="24">
+        <v>1</v>
+      </c>
+      <c r="G29" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="23">
         <v>2024001</v>
       </c>
-      <c r="I29" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="27" t="s">
+      <c r="I29" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="23"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="M29" s="22" t="s">
+      <c r="M29" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="N29" s="15">
+      <c r="N29" s="16">
         <v>4</v>
       </c>
-      <c r="O29" s="15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="22" t="str">
+      <c r="O29" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A30" s="23" t="str">
         <f t="shared" si="1"/>
         <v>1017001</v>
       </c>
@@ -3039,16 +3667,16 @@
       <c r="M30" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="N30" s="42">
+      <c r="N30" s="43">
         <v>4</v>
       </c>
-      <c r="O30" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q30" s="16"/>
-    </row>
-    <row r="31" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="22" t="str">
+      <c r="O30" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q30" s="17"/>
+    </row>
+    <row r="31" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A31" s="23" t="str">
         <f t="shared" ref="A31:A54" si="2">B31&amp;C31</f>
         <v>1017002</v>
       </c>
@@ -3082,16 +3710,16 @@
       <c r="M31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="N31" s="42">
+      <c r="N31" s="43">
         <v>4</v>
       </c>
-      <c r="O31" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q31" s="16"/>
-    </row>
-    <row r="32" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="22" t="str">
+      <c r="O31" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="17"/>
+    </row>
+    <row r="32" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A32" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1017003</v>
       </c>
@@ -3125,16 +3753,16 @@
       <c r="M32" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="N32" s="42">
+      <c r="N32" s="43">
         <v>4</v>
       </c>
-      <c r="O32" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="16"/>
-    </row>
-    <row r="33" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="22" t="str">
+      <c r="O32" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="17"/>
+    </row>
+    <row r="33" s="4" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A33" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1022001</v>
       </c>
@@ -3162,22 +3790,22 @@
       <c r="I33" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="43" t="s">
+      <c r="L33" s="44" t="s">
         <v>85</v>
       </c>
       <c r="M33" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="N33" s="42">
-        <v>3</v>
-      </c>
-      <c r="O33" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="16"/>
-    </row>
-    <row r="34" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="22" t="str">
+      <c r="N33" s="43">
+        <v>3</v>
+      </c>
+      <c r="O33" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="17"/>
+    </row>
+    <row r="34" s="4" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A34" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1022002</v>
       </c>
@@ -3193,7 +3821,7 @@
       <c r="E34" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="16">
         <v>1</v>
       </c>
       <c r="G34" s="4" t="s">
@@ -3205,22 +3833,22 @@
       <c r="I34" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L34" s="43">
+      <c r="L34" s="44">
         <v>10220033</v>
       </c>
       <c r="M34" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="N34" s="42">
-        <v>3</v>
-      </c>
-      <c r="O34" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q34" s="16"/>
-    </row>
-    <row r="35" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="22" t="str">
+      <c r="N34" s="43">
+        <v>3</v>
+      </c>
+      <c r="O34" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q34" s="17"/>
+    </row>
+    <row r="35" s="4" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A35" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1022003</v>
       </c>
@@ -3248,22 +3876,22 @@
       <c r="I35" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="43" t="s">
+      <c r="L35" s="44" t="s">
         <v>89</v>
       </c>
       <c r="M35" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="N35" s="42">
-        <v>3</v>
-      </c>
-      <c r="O35" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="16"/>
-    </row>
-    <row r="36" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="22" t="str">
+      <c r="N35" s="43">
+        <v>3</v>
+      </c>
+      <c r="O35" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="17"/>
+    </row>
+    <row r="36" s="4" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A36" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1022004</v>
       </c>
@@ -3279,7 +3907,7 @@
       <c r="E36" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F36" s="15">
+      <c r="F36" s="16">
         <v>1</v>
       </c>
       <c r="G36" s="4" t="s">
@@ -3291,19 +3919,19 @@
       <c r="I36" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L36" s="43">
+      <c r="L36" s="44">
         <v>10220020</v>
       </c>
-      <c r="N36" s="42">
-        <v>3</v>
-      </c>
-      <c r="O36" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q36" s="16"/>
-    </row>
-    <row r="37" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="22" t="str">
+      <c r="N36" s="43">
+        <v>3</v>
+      </c>
+      <c r="O36" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="17"/>
+    </row>
+    <row r="37" s="4" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A37" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1022005</v>
       </c>
@@ -3331,20 +3959,20 @@
       <c r="I37" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L37" s="43">
+      <c r="L37" s="44">
         <v>10220019</v>
       </c>
-      <c r="N37" s="42">
-        <v>3</v>
-      </c>
-      <c r="O37" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q37" s="16"/>
-      <c r="S37" s="44"/>
-    </row>
-    <row r="38" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="22" t="str">
+      <c r="N37" s="43">
+        <v>3</v>
+      </c>
+      <c r="O37" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q37" s="17"/>
+      <c r="S37" s="45"/>
+    </row>
+    <row r="38" s="4" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A38" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1021001</v>
       </c>
@@ -3372,23 +4000,23 @@
       <c r="I38" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L38" s="43" t="s">
+      <c r="L38" s="44" t="s">
         <v>93</v>
       </c>
       <c r="M38" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="N38" s="42">
-        <v>3</v>
-      </c>
-      <c r="O38" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q38" s="16"/>
-      <c r="S38" s="44"/>
-    </row>
-    <row r="39" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="22" t="str">
+      <c r="N38" s="43">
+        <v>3</v>
+      </c>
+      <c r="O38" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="17"/>
+      <c r="S38" s="45"/>
+    </row>
+    <row r="39" s="4" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A39" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1021002</v>
       </c>
@@ -3416,23 +4044,23 @@
       <c r="I39" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="43">
+      <c r="L39" s="44">
         <v>10210031</v>
       </c>
       <c r="M39" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="N39" s="42">
-        <v>3</v>
-      </c>
-      <c r="O39" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q39" s="16"/>
-      <c r="S39" s="44"/>
-    </row>
-    <row r="40" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="22" t="str">
+      <c r="N39" s="43">
+        <v>3</v>
+      </c>
+      <c r="O39" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q39" s="17"/>
+      <c r="S39" s="45"/>
+    </row>
+    <row r="40" s="4" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A40" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1021003</v>
       </c>
@@ -3460,23 +4088,23 @@
       <c r="I40" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L40" s="43">
+      <c r="L40" s="44">
         <v>10210041</v>
       </c>
       <c r="M40" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="N40" s="42">
-        <v>3</v>
-      </c>
-      <c r="O40" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q40" s="16"/>
-      <c r="S40" s="44"/>
-    </row>
-    <row r="41" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="22" t="str">
+      <c r="N40" s="43">
+        <v>3</v>
+      </c>
+      <c r="O40" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q40" s="17"/>
+      <c r="S40" s="45"/>
+    </row>
+    <row r="41" s="4" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A41" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1021004</v>
       </c>
@@ -3504,23 +4132,23 @@
       <c r="I41" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L41" s="43" t="s">
+      <c r="L41" s="44" t="s">
         <v>96</v>
       </c>
       <c r="M41" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="N41" s="42">
-        <v>3</v>
-      </c>
-      <c r="O41" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q41" s="16"/>
-      <c r="S41" s="44"/>
-    </row>
-    <row r="42" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="22" t="str">
+      <c r="N41" s="43">
+        <v>3</v>
+      </c>
+      <c r="O41" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q41" s="17"/>
+      <c r="S41" s="45"/>
+    </row>
+    <row r="42" s="4" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A42" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1018001</v>
       </c>
@@ -3548,22 +4176,22 @@
       <c r="I42" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L42" s="43" t="s">
+      <c r="L42" s="44" t="s">
         <v>98</v>
       </c>
       <c r="M42" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="N42" s="42">
+      <c r="N42" s="43">
         <v>4</v>
       </c>
-      <c r="O42" s="42">
+      <c r="O42" s="43">
         <v>6</v>
       </c>
-      <c r="Q42" s="16"/>
-      <c r="S42" s="44"/>
-    </row>
-    <row r="43" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q42" s="17"/>
+      <c r="S42" s="45"/>
+    </row>
+    <row r="43" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A43" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1018002</v>
@@ -3592,20 +4220,20 @@
       <c r="I43" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L43" s="43">
+      <c r="L43" s="44">
         <v>10180031</v>
       </c>
       <c r="M43" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="N43" s="42">
+      <c r="N43" s="43">
         <v>4</v>
       </c>
-      <c r="O43" s="42">
+      <c r="O43" s="43">
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="44" ht="16.5" spans="1:19">
       <c r="A44" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1018003</v>
@@ -3634,20 +4262,20 @@
       <c r="I44" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L44" s="43" t="s">
+      <c r="L44" s="44" t="s">
         <v>99</v>
       </c>
       <c r="M44" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="N44" s="42">
+      <c r="N44" s="43">
         <v>4</v>
       </c>
-      <c r="O44" s="42">
+      <c r="O44" s="43">
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="45" ht="16.5" spans="1:19">
       <c r="A45" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1025001</v>
@@ -3676,20 +4304,20 @@
       <c r="I45" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="43" t="s">
+      <c r="L45" s="44" t="s">
         <v>101</v>
       </c>
       <c r="M45" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="N45" s="42">
-        <v>3</v>
-      </c>
-      <c r="O45" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N45" s="43">
+        <v>3</v>
+      </c>
+      <c r="O45" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="1:19">
       <c r="A46" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1025002</v>
@@ -3718,20 +4346,20 @@
       <c r="I46" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L46" s="43">
+      <c r="L46" s="44">
         <v>10250031</v>
       </c>
       <c r="M46" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="N46" s="42">
-        <v>3</v>
-      </c>
-      <c r="O46" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N46" s="43">
+        <v>3</v>
+      </c>
+      <c r="O46" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="1:19">
       <c r="A47" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1025003</v>
@@ -3760,20 +4388,20 @@
       <c r="I47" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L47" s="43" t="s">
+      <c r="L47" s="44" t="s">
         <v>103</v>
       </c>
       <c r="M47" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="N47" s="42">
-        <v>3</v>
-      </c>
-      <c r="O47" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N47" s="43">
+        <v>3</v>
+      </c>
+      <c r="O47" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="1:19">
       <c r="A48" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1023001</v>
@@ -3802,20 +4430,20 @@
       <c r="I48" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L48" s="43" t="s">
+      <c r="L48" s="44" t="s">
         <v>105</v>
       </c>
       <c r="M48" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="N48" s="42">
+      <c r="N48" s="43">
         <v>4</v>
       </c>
-      <c r="O48" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O48" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="1:16">
       <c r="A49" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1023002</v>
@@ -3844,20 +4472,20 @@
       <c r="I49" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L49" s="43">
+      <c r="L49" s="44">
         <v>10230003</v>
       </c>
       <c r="M49" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="N49" s="42">
+      <c r="N49" s="43">
         <v>4</v>
       </c>
-      <c r="O49" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O49" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="1:16">
       <c r="A50" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1023003</v>
@@ -3886,20 +4514,20 @@
       <c r="I50" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="43" t="s">
+      <c r="L50" s="44" t="s">
         <v>106</v>
       </c>
       <c r="M50" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="N50" s="42">
+      <c r="N50" s="43">
         <v>4</v>
       </c>
-      <c r="O50" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O50" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="1:16">
       <c r="A51" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1034001</v>
@@ -3928,20 +4556,20 @@
       <c r="I51" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L51" s="43">
+      <c r="L51" s="44">
         <v>10340007</v>
       </c>
       <c r="M51" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="N51" s="42">
-        <v>3</v>
-      </c>
-      <c r="O51" s="42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="N51" s="43">
+        <v>3</v>
+      </c>
+      <c r="O51" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" spans="1:16">
       <c r="A52" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1034002</v>
@@ -3970,17 +4598,17 @@
       <c r="I52" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L52" s="43"/>
+      <c r="L52" s="44"/>
       <c r="M52" s="4"/>
-      <c r="N52" s="42">
-        <v>3</v>
-      </c>
-      <c r="O52" s="42">
-        <v>3</v>
-      </c>
-      <c r="P52" s="45"/>
-    </row>
-    <row r="53" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N52" s="43">
+        <v>3</v>
+      </c>
+      <c r="O52" s="43">
+        <v>3</v>
+      </c>
+      <c r="P52" s="46"/>
+    </row>
+    <row r="53" ht="16.5" spans="1:16">
       <c r="A53" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1034003</v>
@@ -4009,16 +4637,16 @@
       <c r="I53" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L53" s="43"/>
+      <c r="L53" s="44"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="42">
-        <v>3</v>
-      </c>
-      <c r="O53" s="42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N53" s="43">
+        <v>3</v>
+      </c>
+      <c r="O53" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" spans="1:16">
       <c r="A54" s="4" t="str">
         <f t="shared" si="2"/>
         <v>1035001</v>
@@ -4047,20 +4675,20 @@
       <c r="I54" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L54" s="43" t="s">
+      <c r="L54" s="44" t="s">
         <v>112</v>
       </c>
       <c r="M54" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="N54" s="42">
+      <c r="N54" s="43">
         <v>4</v>
       </c>
-      <c r="O54" s="42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O54" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" spans="1:16">
       <c r="A55" s="4" t="str">
         <f t="shared" ref="A55:A108" si="3">B55&amp;C55</f>
         <v>1035002</v>
@@ -4089,20 +4717,20 @@
       <c r="I55" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="43" t="s">
+      <c r="L55" s="44" t="s">
         <v>115</v>
       </c>
       <c r="M55" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="N55" s="42">
+      <c r="N55" s="43">
         <v>4</v>
       </c>
-      <c r="O55" s="42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O55" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" ht="16.5" spans="1:16">
       <c r="A56" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1035003</v>
@@ -4131,21 +4759,21 @@
       <c r="I56" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L56" s="43" t="s">
+      <c r="L56" s="44" t="s">
         <v>117</v>
       </c>
       <c r="M56" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="N56" s="42">
+      <c r="N56" s="43">
         <v>4</v>
       </c>
-      <c r="O56" s="42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="43">
+      <c r="O56" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" spans="1:16">
+      <c r="A57" s="44">
         <v>1035011</v>
       </c>
       <c r="B57" s="4">
@@ -4172,20 +4800,20 @@
       <c r="I57" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L57" s="43" t="s">
+      <c r="L57" s="44" t="s">
         <v>120</v>
       </c>
       <c r="M57" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="N57" s="42">
+      <c r="N57" s="43">
         <v>4</v>
       </c>
-      <c r="O57" s="42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O57" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" spans="1:16">
       <c r="A58" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1035012</v>
@@ -4214,20 +4842,20 @@
       <c r="I58" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L58" s="43" t="s">
+      <c r="L58" s="44" t="s">
         <v>121</v>
       </c>
       <c r="M58" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="N58" s="42">
+      <c r="N58" s="43">
         <v>4</v>
       </c>
-      <c r="O58" s="42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O58" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" ht="16.5" spans="1:16">
       <c r="A59" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1035013</v>
@@ -4256,20 +4884,20 @@
       <c r="I59" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="43" t="s">
+      <c r="L59" s="44" t="s">
         <v>122</v>
       </c>
       <c r="M59" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="N59" s="42">
+      <c r="N59" s="43">
         <v>4</v>
       </c>
-      <c r="O59" s="42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O59" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" ht="16.5" spans="1:16">
       <c r="A60" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1036001</v>
@@ -4298,20 +4926,20 @@
       <c r="I60" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L60" s="43" t="s">
+      <c r="L60" s="44" t="s">
         <v>124</v>
       </c>
       <c r="M60" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="N60" s="42">
-        <v>3</v>
-      </c>
-      <c r="O60" s="42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N60" s="43">
+        <v>3</v>
+      </c>
+      <c r="O60" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" ht="16.5" spans="1:16">
       <c r="A61" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1036002</v>
@@ -4340,20 +4968,20 @@
       <c r="I61" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L61" s="43">
+      <c r="L61" s="44">
         <v>10360004</v>
       </c>
       <c r="M61" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="N61" s="42">
-        <v>3</v>
-      </c>
-      <c r="O61" s="42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N61" s="43">
+        <v>3</v>
+      </c>
+      <c r="O61" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" ht="16.5" spans="1:16">
       <c r="A62" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1036003</v>
@@ -4382,20 +5010,20 @@
       <c r="I62" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L62" s="43">
+      <c r="L62" s="44">
         <v>10360002</v>
       </c>
       <c r="M62" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="N62" s="42">
-        <v>3</v>
-      </c>
-      <c r="O62" s="42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N62" s="43">
+        <v>3</v>
+      </c>
+      <c r="O62" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" spans="1:16">
       <c r="A63" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1028001</v>
@@ -4424,20 +5052,20 @@
       <c r="I63" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L63" s="43" t="s">
+      <c r="L63" s="44" t="s">
         <v>130</v>
       </c>
       <c r="M63" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="N63" s="42">
-        <v>5</v>
-      </c>
-      <c r="O63" s="42">
+      <c r="N63" s="43">
+        <v>5</v>
+      </c>
+      <c r="O63" s="43">
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="64" ht="16.5" spans="1:16">
       <c r="A64" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1028002</v>
@@ -4466,20 +5094,20 @@
       <c r="I64" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L64" s="43">
+      <c r="L64" s="44">
         <v>10280002</v>
       </c>
       <c r="M64" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="N64" s="42">
-        <v>5</v>
-      </c>
-      <c r="O64" s="42">
+      <c r="N64" s="43">
+        <v>5</v>
+      </c>
+      <c r="O64" s="43">
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="65" ht="16.5" spans="1:17">
       <c r="A65" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1028003</v>
@@ -4508,20 +5136,20 @@
       <c r="I65" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L65" s="43" t="s">
+      <c r="L65" s="44" t="s">
         <v>133</v>
       </c>
       <c r="M65" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="N65" s="42">
-        <v>5</v>
-      </c>
-      <c r="O65" s="42">
+      <c r="N65" s="43">
+        <v>5</v>
+      </c>
+      <c r="O65" s="43">
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="66" ht="16.5" spans="1:17">
       <c r="A66" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1034011</v>
@@ -4550,20 +5178,20 @@
       <c r="I66" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L66" s="43">
+      <c r="L66" s="44">
         <v>10340101</v>
       </c>
       <c r="M66" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="N66" s="42">
-        <v>3</v>
-      </c>
-      <c r="O66" s="42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="N66" s="43">
+        <v>3</v>
+      </c>
+      <c r="O66" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" ht="16.5" spans="1:17">
       <c r="A67" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1034012</v>
@@ -4592,17 +5220,17 @@
       <c r="I67" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L67" s="43"/>
+      <c r="L67" s="44"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="42">
-        <v>3</v>
-      </c>
-      <c r="O67" s="42">
-        <v>3</v>
-      </c>
-      <c r="P67" s="45"/>
-    </row>
-    <row r="68" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N67" s="43">
+        <v>3</v>
+      </c>
+      <c r="O67" s="43">
+        <v>3</v>
+      </c>
+      <c r="P67" s="46"/>
+    </row>
+    <row r="68" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A68" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1034013</v>
@@ -4633,60 +5261,60 @@
       </c>
       <c r="J68"/>
       <c r="K68"/>
-      <c r="L68" s="43"/>
+      <c r="L68" s="44"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="42">
-        <v>3</v>
-      </c>
-      <c r="O68" s="42">
-        <v>3</v>
-      </c>
-      <c r="Q68" s="46"/>
-    </row>
-    <row r="69" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A69" s="47" t="str">
+      <c r="N68" s="43">
+        <v>3</v>
+      </c>
+      <c r="O68" s="43">
+        <v>3</v>
+      </c>
+      <c r="Q68" s="47"/>
+    </row>
+    <row r="69" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A69" s="48" t="str">
         <f t="shared" si="3"/>
         <v>1020001</v>
       </c>
-      <c r="B69" s="47">
+      <c r="B69" s="48">
         <v>102000</v>
       </c>
-      <c r="C69" s="47">
-        <v>1</v>
-      </c>
-      <c r="D69" s="47" t="s">
+      <c r="C69" s="48">
+        <v>1</v>
+      </c>
+      <c r="D69" s="48" t="s">
         <v>136</v>
       </c>
-      <c r="E69" s="47" t="s">
+      <c r="E69" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="F69" s="47">
-        <v>1</v>
-      </c>
-      <c r="G69" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="H69" s="47">
+      <c r="F69" s="48">
+        <v>1</v>
+      </c>
+      <c r="G69" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="H69" s="48">
         <v>2020001</v>
       </c>
-      <c r="I69" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="L69" s="48" t="s">
+      <c r="I69" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69" s="49" t="s">
         <v>137</v>
       </c>
-      <c r="M69" s="47" t="s">
+      <c r="M69" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="N69" s="49">
-        <v>5</v>
-      </c>
-      <c r="O69" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q69" s="46"/>
-    </row>
-    <row r="70" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N69" s="50">
+        <v>5</v>
+      </c>
+      <c r="O69" s="50">
+        <v>5</v>
+      </c>
+      <c r="Q69" s="47"/>
+    </row>
+    <row r="70" ht="16.5" spans="1:17">
       <c r="A70" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1020002</v>
@@ -4715,20 +5343,20 @@
       <c r="I70" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L70" s="43" t="s">
+      <c r="L70" s="44" t="s">
         <v>139</v>
       </c>
       <c r="M70" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="N70" s="42">
-        <v>5</v>
-      </c>
-      <c r="O70" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N70" s="43">
+        <v>5</v>
+      </c>
+      <c r="O70" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" ht="16.5" spans="1:17">
       <c r="A71" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1020003</v>
@@ -4757,63 +5385,63 @@
       <c r="I71" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L71" s="43" t="s">
+      <c r="L71" s="44" t="s">
         <v>141</v>
       </c>
       <c r="M71" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="N71" s="42">
-        <v>5</v>
-      </c>
-      <c r="O71" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A72" s="50" t="str">
+      <c r="N71" s="43">
+        <v>5</v>
+      </c>
+      <c r="O71" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" s="6" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A72" s="51" t="str">
         <f t="shared" si="3"/>
         <v>1020004</v>
       </c>
-      <c r="B72" s="50">
+      <c r="B72" s="51">
         <v>102000</v>
       </c>
-      <c r="C72" s="50">
+      <c r="C72" s="51">
         <v>4</v>
       </c>
-      <c r="D72" s="50" t="s">
+      <c r="D72" s="51" t="s">
         <v>136</v>
       </c>
-      <c r="E72" s="50" t="s">
+      <c r="E72" s="51" t="s">
         <v>143</v>
       </c>
-      <c r="F72" s="50">
-        <v>1</v>
-      </c>
-      <c r="G72" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="H72" s="50">
+      <c r="F72" s="51">
+        <v>1</v>
+      </c>
+      <c r="G72" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="H72" s="51">
         <v>2020002</v>
       </c>
-      <c r="I72" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="L72" s="51">
+      <c r="I72" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72" s="52">
         <v>10200016</v>
       </c>
-      <c r="M72" s="50" t="s">
+      <c r="M72" s="51" t="s">
         <v>144</v>
       </c>
-      <c r="N72" s="52">
-        <v>5</v>
-      </c>
-      <c r="O72" s="52">
-        <v>5</v>
-      </c>
-      <c r="Q72" s="53"/>
-    </row>
-    <row r="73" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N72" s="53">
+        <v>5</v>
+      </c>
+      <c r="O72" s="53">
+        <v>5</v>
+      </c>
+      <c r="Q72" s="54"/>
+    </row>
+    <row r="73" ht="16.5" spans="1:17">
       <c r="A73" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1020005</v>
@@ -4842,20 +5470,20 @@
       <c r="I73" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L73" s="43">
+      <c r="L73" s="44">
         <v>10200021</v>
       </c>
       <c r="M73" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="N73" s="42">
-        <v>5</v>
-      </c>
-      <c r="O73" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N73" s="43">
+        <v>5</v>
+      </c>
+      <c r="O73" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" ht="16.5" spans="1:17">
       <c r="A74" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1038001</v>
@@ -4887,18 +5515,18 @@
       <c r="J74" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="L74" s="43"/>
+      <c r="L74" s="44"/>
       <c r="M74" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="N74" s="42">
-        <v>3</v>
-      </c>
-      <c r="O74" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N74" s="43">
+        <v>3</v>
+      </c>
+      <c r="O74" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" ht="16.5" spans="1:17">
       <c r="A75" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1038002</v>
@@ -4927,20 +5555,20 @@
       <c r="I75" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L75" s="43">
+      <c r="L75" s="44">
         <v>10380002</v>
       </c>
       <c r="M75" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="N75" s="42">
-        <v>3</v>
-      </c>
-      <c r="O75" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N75" s="43">
+        <v>3</v>
+      </c>
+      <c r="O75" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" ht="16.5" spans="1:17">
       <c r="A76" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1038004</v>
@@ -4969,20 +5597,20 @@
       <c r="I76" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L76" s="43" t="s">
+      <c r="L76" s="44" t="s">
         <v>152</v>
       </c>
       <c r="M76" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="N76" s="42">
-        <v>3</v>
-      </c>
-      <c r="O76" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N76" s="43">
+        <v>3</v>
+      </c>
+      <c r="O76" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" ht="16.5" spans="1:17">
       <c r="A77" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1038003</v>
@@ -5011,20 +5639,20 @@
       <c r="I77" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L77" s="43" t="s">
+      <c r="L77" s="44" t="s">
         <v>154</v>
       </c>
       <c r="M77" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="N77" s="42">
-        <v>3</v>
-      </c>
-      <c r="O77" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N77" s="43">
+        <v>3</v>
+      </c>
+      <c r="O77" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" ht="16.5" spans="1:17">
       <c r="A78" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1027001</v>
@@ -5053,20 +5681,20 @@
       <c r="I78" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L78" s="43" t="s">
+      <c r="L78" s="44" t="s">
         <v>157</v>
       </c>
       <c r="M78" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="N78" s="42">
-        <v>3</v>
-      </c>
-      <c r="O78" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N78" s="43">
+        <v>3</v>
+      </c>
+      <c r="O78" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" ht="16.5" spans="1:17">
       <c r="A79" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1027002</v>
@@ -5095,20 +5723,20 @@
       <c r="I79" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L79" s="43">
+      <c r="L79" s="44">
         <v>10270003</v>
       </c>
       <c r="M79" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="N79" s="42">
-        <v>3</v>
-      </c>
-      <c r="O79" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N79" s="43">
+        <v>3</v>
+      </c>
+      <c r="O79" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" ht="16.5" spans="1:17">
       <c r="A80" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1027003</v>
@@ -5137,20 +5765,20 @@
       <c r="I80" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L80" s="43" t="s">
+      <c r="L80" s="44" t="s">
         <v>160</v>
       </c>
       <c r="M80" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="N80" s="42">
-        <v>3</v>
-      </c>
-      <c r="O80" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N80" s="43">
+        <v>3</v>
+      </c>
+      <c r="O80" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" ht="16.5" spans="1:17">
       <c r="A81" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1037001</v>
@@ -5179,20 +5807,20 @@
       <c r="I81" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L81" s="43" t="s">
+      <c r="L81" s="44" t="s">
         <v>163</v>
       </c>
       <c r="M81" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="N81" s="42">
+      <c r="N81" s="43">
         <v>4</v>
       </c>
-      <c r="O81" s="42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O81" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" ht="16.5" spans="1:17">
       <c r="A82" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1037002</v>
@@ -5221,20 +5849,20 @@
       <c r="I82" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L82" s="43" t="s">
+      <c r="L82" s="44" t="s">
         <v>166</v>
       </c>
       <c r="M82" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="N82" s="42">
+      <c r="N82" s="43">
         <v>4</v>
       </c>
-      <c r="O82" s="42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O82" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" ht="16.5" spans="1:17">
       <c r="A83" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1037003</v>
@@ -5263,20 +5891,20 @@
       <c r="I83" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L83" s="43">
+      <c r="L83" s="44">
         <v>10370003</v>
       </c>
       <c r="M83" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="N83" s="42">
+      <c r="N83" s="43">
         <v>4</v>
       </c>
-      <c r="O83" s="42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O83" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" ht="16.5" spans="1:17">
       <c r="A84" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1031001</v>
@@ -5305,20 +5933,20 @@
       <c r="I84" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L84" s="43" t="s">
+      <c r="L84" s="44" t="s">
         <v>169</v>
       </c>
       <c r="M84" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="N84" s="42">
-        <v>3</v>
-      </c>
-      <c r="O84" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N84" s="43">
+        <v>3</v>
+      </c>
+      <c r="O84" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" ht="16.5" spans="1:17">
       <c r="A85" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1031002</v>
@@ -5347,20 +5975,20 @@
       <c r="I85" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L85" s="43">
+      <c r="L85" s="44">
         <v>10310008</v>
       </c>
       <c r="M85" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="N85" s="42">
-        <v>3</v>
-      </c>
-      <c r="O85" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N85" s="43">
+        <v>3</v>
+      </c>
+      <c r="O85" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" ht="16.5" spans="1:17">
       <c r="A86" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1031003</v>
@@ -5389,20 +6017,20 @@
       <c r="I86" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L86" s="43" t="s">
+      <c r="L86" s="44" t="s">
         <v>172</v>
       </c>
       <c r="M86" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="N86" s="42">
-        <v>3</v>
-      </c>
-      <c r="O86" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N86" s="43">
+        <v>3</v>
+      </c>
+      <c r="O86" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" ht="16.5" spans="1:17">
       <c r="A87" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1031004</v>
@@ -5431,20 +6059,20 @@
       <c r="I87" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L87" s="43" t="s">
+      <c r="L87" s="44" t="s">
         <v>174</v>
       </c>
       <c r="M87" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="N87" s="42">
-        <v>3</v>
-      </c>
-      <c r="O87" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N87" s="43">
+        <v>3</v>
+      </c>
+      <c r="O87" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" ht="16.5" spans="1:17">
       <c r="A88" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1031005</v>
@@ -5473,20 +6101,20 @@
       <c r="I88" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L88" s="43">
+      <c r="L88" s="44">
         <v>10310003</v>
       </c>
       <c r="M88" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="N88" s="42">
-        <v>3</v>
-      </c>
-      <c r="O88" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N88" s="43">
+        <v>3</v>
+      </c>
+      <c r="O88" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" ht="16.5" spans="1:17">
       <c r="A89" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1031006</v>
@@ -5515,20 +6143,20 @@
       <c r="I89" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L89" s="43" t="s">
+      <c r="L89" s="44" t="s">
         <v>179</v>
       </c>
       <c r="M89" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="N89" s="42">
-        <v>3</v>
-      </c>
-      <c r="O89" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N89" s="43">
+        <v>3</v>
+      </c>
+      <c r="O89" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" ht="16.5" spans="1:17">
       <c r="A90" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1040001</v>
@@ -5557,20 +6185,20 @@
       <c r="I90" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L90" s="43" t="s">
+      <c r="L90" s="44" t="s">
         <v>182</v>
       </c>
       <c r="M90" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="N90" s="42">
-        <v>3</v>
-      </c>
-      <c r="O90" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N90" s="43">
+        <v>3</v>
+      </c>
+      <c r="O90" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" ht="16.5" spans="1:17">
       <c r="A91" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1040002</v>
@@ -5599,20 +6227,20 @@
       <c r="I91" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L91" s="43" t="s">
+      <c r="L91" s="44" t="s">
         <v>184</v>
       </c>
       <c r="M91" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="N91" s="42">
-        <v>3</v>
-      </c>
-      <c r="O91" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N91" s="43">
+        <v>3</v>
+      </c>
+      <c r="O91" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" ht="16.5" spans="1:17">
       <c r="A92" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1040003</v>
@@ -5641,20 +6269,20 @@
       <c r="I92" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L92" s="43" t="s">
+      <c r="L92" s="44" t="s">
         <v>186</v>
       </c>
       <c r="M92" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="N92" s="42">
-        <v>3</v>
-      </c>
-      <c r="O92" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N92" s="43">
+        <v>3</v>
+      </c>
+      <c r="O92" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A93" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1039001</v>
@@ -5689,15 +6317,15 @@
       <c r="M93" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="N93" s="42">
-        <v>3</v>
-      </c>
-      <c r="O93" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q93" s="16"/>
-    </row>
-    <row r="94" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N93" s="43">
+        <v>3</v>
+      </c>
+      <c r="O93" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q93" s="17"/>
+    </row>
+    <row r="94" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A94" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1039002</v>
@@ -5726,21 +6354,21 @@
       <c r="I94" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L94" s="43">
+      <c r="L94" s="44">
         <v>10390003</v>
       </c>
       <c r="M94" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="N94" s="42">
-        <v>3</v>
-      </c>
-      <c r="O94" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="16"/>
-    </row>
-    <row r="95" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N94" s="43">
+        <v>3</v>
+      </c>
+      <c r="O94" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="17"/>
+    </row>
+    <row r="95" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A95" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1039003</v>
@@ -5775,15 +6403,15 @@
       <c r="M95" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="N95" s="42">
-        <v>3</v>
-      </c>
-      <c r="O95" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q95" s="16"/>
-    </row>
-    <row r="96" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N95" s="43">
+        <v>3</v>
+      </c>
+      <c r="O95" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q95" s="17"/>
+    </row>
+    <row r="96" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A96" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1016001</v>
@@ -5818,15 +6446,15 @@
       <c r="M96" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="N96" s="42">
+      <c r="N96" s="43">
         <v>6</v>
       </c>
-      <c r="O96" s="42">
+      <c r="O96" s="43">
         <v>6</v>
       </c>
-      <c r="Q96" s="16"/>
-    </row>
-    <row r="97" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q96" s="17"/>
+    </row>
+    <row r="97" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A97" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1016002</v>
@@ -5855,21 +6483,21 @@
       <c r="I97" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L97" s="43">
+      <c r="L97" s="44">
         <v>10160002</v>
       </c>
       <c r="M97" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="N97" s="42">
+      <c r="N97" s="43">
         <v>6</v>
       </c>
-      <c r="O97" s="42">
+      <c r="O97" s="43">
         <v>6</v>
       </c>
-      <c r="Q97" s="16"/>
-    </row>
-    <row r="98" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q97" s="17"/>
+    </row>
+    <row r="98" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A98" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1016003</v>
@@ -5904,15 +6532,15 @@
       <c r="M98" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="N98" s="42">
+      <c r="N98" s="43">
         <v>6</v>
       </c>
-      <c r="O98" s="42">
+      <c r="O98" s="43">
         <v>6</v>
       </c>
-      <c r="Q98" s="16"/>
-    </row>
-    <row r="99" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q98" s="17"/>
+    </row>
+    <row r="99" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A99" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015001</v>
@@ -5947,15 +6575,15 @@
       <c r="M99" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="N99" s="42">
-        <v>3</v>
-      </c>
-      <c r="O99" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q99" s="16"/>
-    </row>
-    <row r="100" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N99" s="43">
+        <v>3</v>
+      </c>
+      <c r="O99" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q99" s="17"/>
+    </row>
+    <row r="100" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A100" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015002</v>
@@ -5990,15 +6618,15 @@
       <c r="M100" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="N100" s="42">
-        <v>3</v>
-      </c>
-      <c r="O100" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="16"/>
-    </row>
-    <row r="101" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N100" s="43">
+        <v>3</v>
+      </c>
+      <c r="O100" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="17"/>
+    </row>
+    <row r="101" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A101" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015003</v>
@@ -6027,21 +6655,21 @@
       <c r="I101" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L101" s="43">
+      <c r="L101" s="44">
         <v>10150002</v>
       </c>
       <c r="M101" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="N101" s="42">
-        <v>3</v>
-      </c>
-      <c r="O101" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="16"/>
-    </row>
-    <row r="102" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N101" s="43">
+        <v>3</v>
+      </c>
+      <c r="O101" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="17"/>
+    </row>
+    <row r="102" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A102" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015004</v>
@@ -6076,15 +6704,15 @@
       <c r="M102" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="N102" s="42">
-        <v>3</v>
-      </c>
-      <c r="O102" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="16"/>
-    </row>
-    <row r="103" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N102" s="43">
+        <v>3</v>
+      </c>
+      <c r="O102" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="17"/>
+    </row>
+    <row r="103" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A103" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015005</v>
@@ -6113,21 +6741,21 @@
       <c r="I103" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L103" s="43">
+      <c r="L103" s="44">
         <v>10150005</v>
       </c>
       <c r="M103" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="N103" s="42">
-        <v>3</v>
-      </c>
-      <c r="O103" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q103" s="16"/>
-    </row>
-    <row r="104" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N103" s="43">
+        <v>3</v>
+      </c>
+      <c r="O103" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q103" s="17"/>
+    </row>
+    <row r="104" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A104" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015006</v>
@@ -6156,21 +6784,21 @@
       <c r="I104" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L104" s="43">
+      <c r="L104" s="44">
         <v>10150006</v>
       </c>
       <c r="M104" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="N104" s="42">
-        <v>3</v>
-      </c>
-      <c r="O104" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q104" s="16"/>
-    </row>
-    <row r="105" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N104" s="43">
+        <v>3</v>
+      </c>
+      <c r="O104" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q104" s="17"/>
+    </row>
+    <row r="105" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A105" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1015007</v>
@@ -6199,21 +6827,21 @@
       <c r="I105" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L105" s="43">
+      <c r="L105" s="44">
         <v>10150007</v>
       </c>
       <c r="M105" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="N105" s="42">
-        <v>3</v>
-      </c>
-      <c r="O105" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q105" s="16"/>
-    </row>
-    <row r="106" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N105" s="43">
+        <v>3</v>
+      </c>
+      <c r="O105" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q105" s="17"/>
+    </row>
+    <row r="106" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A106" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1026001</v>
@@ -6242,21 +6870,21 @@
       <c r="I106" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L106" s="43" t="s">
+      <c r="L106" s="44" t="s">
         <v>211</v>
       </c>
       <c r="M106" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="N106" s="42">
+      <c r="N106" s="43">
         <v>6</v>
       </c>
-      <c r="O106" s="42">
+      <c r="O106" s="43">
         <v>6</v>
       </c>
-      <c r="Q106" s="16"/>
-    </row>
-    <row r="107" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q106" s="17"/>
+    </row>
+    <row r="107" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A107" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1026002</v>
@@ -6285,21 +6913,21 @@
       <c r="I107" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L107" s="43" t="s">
+      <c r="L107" s="44" t="s">
         <v>213</v>
       </c>
       <c r="M107" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="N107" s="42">
+      <c r="N107" s="43">
         <v>6</v>
       </c>
-      <c r="O107" s="42">
+      <c r="O107" s="43">
         <v>6</v>
       </c>
-      <c r="Q107" s="16"/>
-    </row>
-    <row r="108" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q107" s="17"/>
+    </row>
+    <row r="108" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A108" s="4" t="str">
         <f t="shared" si="3"/>
         <v>1026003</v>
@@ -6328,21 +6956,21 @@
       <c r="I108" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L108" s="43" t="s">
+      <c r="L108" s="44" t="s">
         <v>214</v>
       </c>
       <c r="M108" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="N108" s="42">
+      <c r="N108" s="43">
         <v>6</v>
       </c>
-      <c r="O108" s="42">
+      <c r="O108" s="43">
         <v>6</v>
       </c>
-      <c r="Q108" s="16"/>
-    </row>
-    <row r="109" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q108" s="17"/>
+    </row>
+    <row r="109" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A109" s="4" t="str">
         <f t="shared" ref="A109:A112" si="4">B109&amp;C109</f>
         <v>1050001</v>
@@ -6371,21 +6999,21 @@
       <c r="I109" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L109" s="43" t="s">
+      <c r="L109" s="44" t="s">
         <v>216</v>
       </c>
       <c r="M109" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="N109" s="42">
+      <c r="N109" s="43">
         <v>6</v>
       </c>
-      <c r="O109" s="42">
+      <c r="O109" s="43">
         <v>6</v>
       </c>
-      <c r="Q109" s="16"/>
-    </row>
-    <row r="110" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q109" s="17"/>
+    </row>
+    <row r="110" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A110" s="4" t="str">
         <f t="shared" si="4"/>
         <v>1050002</v>
@@ -6414,21 +7042,21 @@
       <c r="I110" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L110" s="43" t="s">
+      <c r="L110" s="44" t="s">
         <v>218</v>
       </c>
       <c r="M110" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="N110" s="42">
+      <c r="N110" s="43">
         <v>6</v>
       </c>
-      <c r="O110" s="42">
+      <c r="O110" s="43">
         <v>6</v>
       </c>
-      <c r="Q110" s="16"/>
-    </row>
-    <row r="111" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q110" s="17"/>
+    </row>
+    <row r="111" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A111" s="4" t="str">
         <f t="shared" si="4"/>
         <v>1050003</v>
@@ -6457,21 +7085,21 @@
       <c r="I111" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L111" s="43" t="s">
+      <c r="L111" s="44" t="s">
         <v>220</v>
       </c>
       <c r="M111" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="N111" s="42">
+      <c r="N111" s="43">
         <v>6</v>
       </c>
-      <c r="O111" s="42">
+      <c r="O111" s="43">
         <v>6</v>
       </c>
-      <c r="Q111" s="16"/>
-    </row>
-    <row r="112" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q111" s="17"/>
+    </row>
+    <row r="112" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A112" s="4" t="str">
         <f t="shared" si="4"/>
         <v>1050004</v>
@@ -6500,22 +7128,22 @@
       <c r="I112" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L112" s="43" t="s">
+      <c r="L112" s="44" t="s">
         <v>223</v>
       </c>
       <c r="M112" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="N112" s="42">
+      <c r="N112" s="43">
         <v>6</v>
       </c>
-      <c r="O112" s="42">
+      <c r="O112" s="43">
         <v>6</v>
       </c>
-      <c r="Q112" s="16"/>
-    </row>
-    <row r="113" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A113" s="43">
+      <c r="Q112" s="17"/>
+    </row>
+    <row r="113" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A113" s="44">
         <v>1051001</v>
       </c>
       <c r="B113" s="4">
@@ -6542,17 +7170,17 @@
       <c r="I113" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L113" s="43"/>
-      <c r="N113" s="42">
+      <c r="L113" s="44"/>
+      <c r="N113" s="43">
         <v>4</v>
       </c>
-      <c r="O113" s="42">
+      <c r="O113" s="43">
         <v>4</v>
       </c>
-      <c r="Q113" s="16"/>
-    </row>
-    <row r="114" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A114" s="43">
+      <c r="Q113" s="17"/>
+    </row>
+    <row r="114" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A114" s="44">
         <v>1051002</v>
       </c>
       <c r="B114" s="4">
@@ -6579,17 +7207,17 @@
       <c r="I114" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L114" s="43"/>
-      <c r="N114" s="42">
-        <v>5</v>
-      </c>
-      <c r="O114" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q114" s="16"/>
-    </row>
-    <row r="115" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A115" s="43">
+      <c r="L114" s="44"/>
+      <c r="N114" s="43">
+        <v>5</v>
+      </c>
+      <c r="O114" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q114" s="17"/>
+    </row>
+    <row r="115" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A115" s="44">
         <v>1051003</v>
       </c>
       <c r="B115" s="4">
@@ -6616,17 +7244,17 @@
       <c r="I115" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L115" s="43"/>
-      <c r="N115" s="42">
+      <c r="L115" s="44"/>
+      <c r="N115" s="43">
         <v>6</v>
       </c>
-      <c r="O115" s="42">
+      <c r="O115" s="43">
         <v>6</v>
       </c>
-      <c r="Q115" s="16"/>
-    </row>
-    <row r="116" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A116" s="43">
+      <c r="Q115" s="17"/>
+    </row>
+    <row r="116" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A116" s="44">
         <v>1051004</v>
       </c>
       <c r="B116" s="4">
@@ -6653,22 +7281,22 @@
       <c r="I116" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L116" s="43">
+      <c r="L116" s="44">
         <v>10510001</v>
       </c>
       <c r="M116" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="N116" s="42">
+      <c r="N116" s="43">
         <v>4</v>
       </c>
-      <c r="O116" s="42">
+      <c r="O116" s="43">
         <v>4</v>
       </c>
-      <c r="Q116" s="16"/>
-    </row>
-    <row r="117" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A117" s="43">
+      <c r="Q116" s="17"/>
+    </row>
+    <row r="117" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A117" s="44">
         <v>1051005</v>
       </c>
       <c r="B117" s="4">
@@ -6695,22 +7323,22 @@
       <c r="I117" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L117" s="43">
+      <c r="L117" s="44">
         <v>10510002</v>
       </c>
       <c r="M117" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="N117" s="42">
-        <v>5</v>
-      </c>
-      <c r="O117" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q117" s="16"/>
-    </row>
-    <row r="118" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A118" s="43">
+      <c r="N117" s="43">
+        <v>5</v>
+      </c>
+      <c r="O117" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q117" s="17"/>
+    </row>
+    <row r="118" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A118" s="44">
         <v>1051006</v>
       </c>
       <c r="B118" s="4">
@@ -6737,22 +7365,22 @@
       <c r="I118" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L118" s="43">
+      <c r="L118" s="44">
         <v>10510003</v>
       </c>
       <c r="M118" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="N118" s="42">
+      <c r="N118" s="43">
         <v>6</v>
       </c>
-      <c r="O118" s="42">
+      <c r="O118" s="43">
         <v>6</v>
       </c>
-      <c r="Q118" s="16"/>
-    </row>
-    <row r="119" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A119" s="43">
+      <c r="Q118" s="17"/>
+    </row>
+    <row r="119" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A119" s="44">
         <v>1051007</v>
       </c>
       <c r="B119" s="4">
@@ -6779,22 +7407,22 @@
       <c r="I119" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L119" s="43">
+      <c r="L119" s="44">
         <v>10510004</v>
       </c>
       <c r="M119" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="N119" s="42">
+      <c r="N119" s="43">
         <v>4</v>
       </c>
-      <c r="O119" s="42">
+      <c r="O119" s="43">
         <v>4</v>
       </c>
-      <c r="Q119" s="16"/>
-    </row>
-    <row r="120" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A120" s="43">
+      <c r="Q119" s="17"/>
+    </row>
+    <row r="120" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A120" s="44">
         <v>1051008</v>
       </c>
       <c r="B120" s="4">
@@ -6821,22 +7449,22 @@
       <c r="I120" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L120" s="43">
+      <c r="L120" s="44">
         <v>10510005</v>
       </c>
       <c r="M120" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="N120" s="42">
-        <v>5</v>
-      </c>
-      <c r="O120" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q120" s="16"/>
-    </row>
-    <row r="121" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A121" s="43">
+      <c r="N120" s="43">
+        <v>5</v>
+      </c>
+      <c r="O120" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q120" s="17"/>
+    </row>
+    <row r="121" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A121" s="44">
         <v>1051009</v>
       </c>
       <c r="B121" s="4">
@@ -6863,21 +7491,21 @@
       <c r="I121" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L121" s="43">
+      <c r="L121" s="44">
         <v>10510006</v>
       </c>
       <c r="M121" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="N121" s="42">
+      <c r="N121" s="43">
         <v>6</v>
       </c>
-      <c r="O121" s="42">
+      <c r="O121" s="43">
         <v>6</v>
       </c>
-      <c r="Q121" s="16"/>
-    </row>
-    <row r="122" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q121" s="17"/>
+    </row>
+    <row r="122" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A122" s="4" t="str">
         <f t="shared" ref="A122:A136" si="5">B122&amp;C122</f>
         <v>1054001</v>
@@ -6906,21 +7534,21 @@
       <c r="I122" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L122" s="43" t="s">
+      <c r="L122" s="44" t="s">
         <v>242</v>
       </c>
       <c r="M122" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="N122" s="42">
+      <c r="N122" s="43">
         <v>6</v>
       </c>
-      <c r="O122" s="42">
+      <c r="O122" s="43">
         <v>6</v>
       </c>
-      <c r="Q122" s="16"/>
-    </row>
-    <row r="123" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q122" s="17"/>
+    </row>
+    <row r="123" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A123" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1054002</v>
@@ -6949,21 +7577,21 @@
       <c r="I123" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L123" s="43" t="s">
+      <c r="L123" s="44" t="s">
         <v>244</v>
       </c>
       <c r="M123" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="N123" s="42">
+      <c r="N123" s="43">
         <v>6</v>
       </c>
-      <c r="O123" s="42">
+      <c r="O123" s="43">
         <v>6</v>
       </c>
-      <c r="Q123" s="16"/>
-    </row>
-    <row r="124" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q123" s="17"/>
+    </row>
+    <row r="124" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A124" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1054003</v>
@@ -6992,21 +7620,21 @@
       <c r="I124" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L124" s="43" t="s">
+      <c r="L124" s="44" t="s">
         <v>246</v>
       </c>
       <c r="M124" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="N124" s="42">
+      <c r="N124" s="43">
         <v>6</v>
       </c>
-      <c r="O124" s="42">
+      <c r="O124" s="43">
         <v>6</v>
       </c>
-      <c r="Q124" s="16"/>
-    </row>
-    <row r="125" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q124" s="17"/>
+    </row>
+    <row r="125" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A125" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1054004</v>
@@ -7035,21 +7663,21 @@
       <c r="I125" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L125" s="43" t="s">
+      <c r="L125" s="44" t="s">
         <v>248</v>
       </c>
       <c r="M125" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="N125" s="42">
+      <c r="N125" s="43">
         <v>6</v>
       </c>
-      <c r="O125" s="42">
+      <c r="O125" s="43">
         <v>6</v>
       </c>
-      <c r="Q125" s="16"/>
-    </row>
-    <row r="126" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q125" s="17"/>
+    </row>
+    <row r="126" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A126" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1008001</v>
@@ -7078,21 +7706,21 @@
       <c r="I126" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L126" s="43" t="s">
+      <c r="L126" s="44" t="s">
         <v>250</v>
       </c>
       <c r="M126" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="N126" s="42">
+      <c r="N126" s="43">
         <v>6</v>
       </c>
-      <c r="O126" s="42">
+      <c r="O126" s="43">
         <v>6</v>
       </c>
-      <c r="Q126" s="16"/>
-    </row>
-    <row r="127" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q126" s="17"/>
+    </row>
+    <row r="127" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A127" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1008002</v>
@@ -7121,21 +7749,21 @@
       <c r="I127" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L127" s="43" t="s">
+      <c r="L127" s="44" t="s">
         <v>252</v>
       </c>
       <c r="M127" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="N127" s="42">
+      <c r="N127" s="43">
         <v>6</v>
       </c>
-      <c r="O127" s="42">
+      <c r="O127" s="43">
         <v>6</v>
       </c>
-      <c r="Q127" s="16"/>
-    </row>
-    <row r="128" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q127" s="17"/>
+    </row>
+    <row r="128" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A128" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1008003</v>
@@ -7164,21 +7792,21 @@
       <c r="I128" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L128" s="43" t="s">
+      <c r="L128" s="44" t="s">
         <v>253</v>
       </c>
       <c r="M128" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="N128" s="42">
+      <c r="N128" s="43">
         <v>6</v>
       </c>
-      <c r="O128" s="42">
+      <c r="O128" s="43">
         <v>6</v>
       </c>
-      <c r="Q128" s="16"/>
-    </row>
-    <row r="129" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q128" s="17"/>
+    </row>
+    <row r="129" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A129" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1053001</v>
@@ -7207,21 +7835,21 @@
       <c r="I129" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L129" s="43" t="s">
+      <c r="L129" s="44" t="s">
         <v>255</v>
       </c>
       <c r="M129" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="N129" s="42">
-        <v>5</v>
-      </c>
-      <c r="O129" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q129" s="16"/>
-    </row>
-    <row r="130" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N129" s="43">
+        <v>5</v>
+      </c>
+      <c r="O129" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q129" s="17"/>
+    </row>
+    <row r="130" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A130" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1053002</v>
@@ -7250,21 +7878,21 @@
       <c r="I130" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L130" s="43" t="s">
+      <c r="L130" s="44" t="s">
         <v>257</v>
       </c>
       <c r="M130" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="N130" s="42">
-        <v>5</v>
-      </c>
-      <c r="O130" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q130" s="16"/>
-    </row>
-    <row r="131" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N130" s="43">
+        <v>5</v>
+      </c>
+      <c r="O130" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q130" s="17"/>
+    </row>
+    <row r="131" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A131" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1057001</v>
@@ -7293,21 +7921,21 @@
       <c r="I131" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L131" s="43" t="s">
+      <c r="L131" s="44" t="s">
         <v>260</v>
       </c>
       <c r="M131" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="N131" s="42">
+      <c r="N131" s="43">
         <v>6</v>
       </c>
-      <c r="O131" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q131" s="16"/>
-    </row>
-    <row r="132" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O131" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q131" s="17"/>
+    </row>
+    <row r="132" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A132" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1057002</v>
@@ -7336,21 +7964,21 @@
       <c r="I132" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L132" s="43" t="s">
+      <c r="L132" s="44" t="s">
         <v>262</v>
       </c>
       <c r="M132" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="N132" s="42">
+      <c r="N132" s="43">
         <v>6</v>
       </c>
-      <c r="O132" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q132" s="16"/>
-    </row>
-    <row r="133" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O132" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q132" s="17"/>
+    </row>
+    <row r="133" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A133" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1057003</v>
@@ -7379,21 +8007,21 @@
       <c r="I133" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L133" s="43" t="s">
+      <c r="L133" s="44" t="s">
         <v>264</v>
       </c>
       <c r="M133" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="N133" s="42">
+      <c r="N133" s="43">
         <v>6</v>
       </c>
-      <c r="O133" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q133" s="16"/>
-    </row>
-    <row r="134" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O133" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q133" s="17"/>
+    </row>
+    <row r="134" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A134" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1058001</v>
@@ -7422,21 +8050,21 @@
       <c r="I134" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L134" s="43">
+      <c r="L134" s="44">
         <v>10580003</v>
       </c>
       <c r="M134" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="N134" s="42">
+      <c r="N134" s="43">
         <v>7</v>
       </c>
-      <c r="O134" s="42">
+      <c r="O134" s="43">
         <v>7</v>
       </c>
-      <c r="Q134" s="16"/>
-    </row>
-    <row r="135" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q134" s="17"/>
+    </row>
+    <row r="135" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A135" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1058002</v>
@@ -7465,21 +8093,21 @@
       <c r="I135" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L135" s="43">
+      <c r="L135" s="44">
         <v>10580002</v>
       </c>
       <c r="M135" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="N135" s="42">
+      <c r="N135" s="43">
         <v>7</v>
       </c>
-      <c r="O135" s="42">
+      <c r="O135" s="43">
         <v>7</v>
       </c>
-      <c r="Q135" s="16"/>
-    </row>
-    <row r="136" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q135" s="17"/>
+    </row>
+    <row r="136" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A136" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1058003</v>
@@ -7508,22 +8136,22 @@
       <c r="I136" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L136" s="43" t="s">
+      <c r="L136" s="44" t="s">
         <v>268</v>
       </c>
       <c r="M136" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="N136" s="42">
+      <c r="N136" s="43">
         <v>7</v>
       </c>
-      <c r="O136" s="42">
+      <c r="O136" s="43">
         <v>7</v>
       </c>
-      <c r="Q136" s="16"/>
-    </row>
-    <row r="137" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A137" s="43">
+      <c r="Q136" s="17"/>
+    </row>
+    <row r="137" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A137" s="44">
         <v>1055001</v>
       </c>
       <c r="B137" s="4">
@@ -7550,22 +8178,22 @@
       <c r="I137" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L137" s="43">
+      <c r="L137" s="44">
         <v>10550002</v>
       </c>
       <c r="M137" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="N137" s="42">
-        <v>3</v>
-      </c>
-      <c r="O137" s="42">
+      <c r="N137" s="43">
+        <v>3</v>
+      </c>
+      <c r="O137" s="43">
         <v>4</v>
       </c>
-      <c r="Q137" s="16"/>
-    </row>
-    <row r="138" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A138" s="43">
+      <c r="Q137" s="17"/>
+    </row>
+    <row r="138" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A138" s="44">
         <v>1055002</v>
       </c>
       <c r="B138" s="4">
@@ -7592,22 +8220,22 @@
       <c r="I138" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L138" s="43">
+      <c r="L138" s="44">
         <v>10550001</v>
       </c>
       <c r="M138" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="N138" s="42">
-        <v>3</v>
-      </c>
-      <c r="O138" s="42">
+      <c r="N138" s="43">
+        <v>3</v>
+      </c>
+      <c r="O138" s="43">
         <v>4</v>
       </c>
-      <c r="Q138" s="16"/>
-    </row>
-    <row r="139" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A139" s="43">
+      <c r="Q138" s="17"/>
+    </row>
+    <row r="139" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A139" s="44">
         <v>1048001</v>
       </c>
       <c r="B139" s="4">
@@ -7619,16 +8247,16 @@
       <c r="D139" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="E139" s="54" t="s">
+      <c r="E139" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="F139" s="15">
+      <c r="F139" s="16">
         <v>1</v>
       </c>
       <c r="G139" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H139" s="55">
+      <c r="H139" s="56">
         <v>2048001</v>
       </c>
       <c r="I139" s="4" t="s">
@@ -7640,16 +8268,16 @@
       <c r="M139" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="N139" s="42">
+      <c r="N139" s="43">
         <v>6</v>
       </c>
-      <c r="O139" s="42">
+      <c r="O139" s="43">
         <v>6</v>
       </c>
-      <c r="Q139" s="16"/>
-    </row>
-    <row r="140" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A140" s="43">
+      <c r="Q139" s="17"/>
+    </row>
+    <row r="140" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A140" s="44">
         <v>1048002</v>
       </c>
       <c r="B140" s="4">
@@ -7661,37 +8289,37 @@
       <c r="D140" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="E140" s="54" t="s">
+      <c r="E140" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="F140" s="15">
+      <c r="F140" s="16">
         <v>1</v>
       </c>
       <c r="G140" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H140" s="55">
+      <c r="H140" s="56">
         <v>2048001</v>
       </c>
       <c r="I140" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L140" s="43">
+      <c r="L140" s="44">
         <v>10480002</v>
       </c>
       <c r="M140" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="N140" s="42">
+      <c r="N140" s="43">
         <v>6</v>
       </c>
-      <c r="O140" s="42">
+      <c r="O140" s="43">
         <v>6</v>
       </c>
-      <c r="Q140" s="16"/>
-    </row>
-    <row r="141" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A141" s="43">
+      <c r="Q140" s="17"/>
+    </row>
+    <row r="141" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A141" s="44">
         <v>1048003</v>
       </c>
       <c r="B141" s="4">
@@ -7706,34 +8334,34 @@
       <c r="E141" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F141" s="15">
+      <c r="F141" s="16">
         <v>1</v>
       </c>
       <c r="G141" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H141" s="55">
+      <c r="H141" s="56">
         <v>2048001</v>
       </c>
       <c r="I141" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L141" s="43" t="s">
+      <c r="L141" s="44" t="s">
         <v>274</v>
       </c>
       <c r="M141" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="N141" s="42">
+      <c r="N141" s="43">
         <v>6</v>
       </c>
-      <c r="O141" s="42">
+      <c r="O141" s="43">
         <v>6</v>
       </c>
-      <c r="Q141" s="16"/>
-    </row>
-    <row r="142" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A142" s="43">
+      <c r="Q141" s="17"/>
+    </row>
+    <row r="142" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A142" s="44">
         <v>1055011</v>
       </c>
       <c r="B142" s="4">
@@ -7760,22 +8388,22 @@
       <c r="I142" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L142" s="43">
+      <c r="L142" s="44">
         <v>10550102</v>
       </c>
       <c r="M142" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="N142" s="42">
-        <v>3</v>
-      </c>
-      <c r="O142" s="42">
+      <c r="N142" s="43">
+        <v>3</v>
+      </c>
+      <c r="O142" s="43">
         <v>4</v>
       </c>
-      <c r="Q142" s="16"/>
-    </row>
-    <row r="143" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A143" s="43">
+      <c r="Q142" s="17"/>
+    </row>
+    <row r="143" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A143" s="44">
         <v>1055012</v>
       </c>
       <c r="B143" s="4">
@@ -7802,22 +8430,22 @@
       <c r="I143" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L143" s="43">
+      <c r="L143" s="44">
         <v>10550101</v>
       </c>
       <c r="M143" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="N143" s="42">
-        <v>3</v>
-      </c>
-      <c r="O143" s="42">
+      <c r="N143" s="43">
+        <v>3</v>
+      </c>
+      <c r="O143" s="43">
         <v>4</v>
       </c>
-      <c r="Q143" s="16"/>
-    </row>
-    <row r="144" spans="1:17" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="A144" s="43">
+      <c r="Q143" s="17"/>
+    </row>
+    <row r="144" ht="16.5" spans="1:17">
+      <c r="A144" s="44">
         <v>1055013</v>
       </c>
       <c r="B144" s="4">
@@ -7829,7 +8457,7 @@
       <c r="D144" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="E144" s="45" t="s">
+      <c r="E144" s="46" t="s">
         <v>276</v>
       </c>
       <c r="F144" s="4">
@@ -7846,51 +8474,51 @@
       </c>
       <c r="J144" s="4"/>
       <c r="K144" s="4"/>
-      <c r="L144" s="43">
+      <c r="L144" s="44">
         <v>10550103</v>
       </c>
       <c r="M144" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="N144" s="42">
-        <v>3</v>
-      </c>
-      <c r="O144" s="42">
+      <c r="N144" s="43">
+        <v>3</v>
+      </c>
+      <c r="O144" s="43">
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:17" s="57" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A145" s="56">
+    <row r="145" s="7" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A145" s="57">
         <v>1055021</v>
       </c>
-      <c r="B145" s="57">
+      <c r="B145" s="7">
         <v>105502</v>
       </c>
-      <c r="C145" s="57">
-        <v>1</v>
-      </c>
-      <c r="D145" s="57" t="s">
+      <c r="C145" s="7">
+        <v>1</v>
+      </c>
+      <c r="D145" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="E145" s="57" t="s">
+      <c r="E145" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F145" s="57">
-        <v>1</v>
-      </c>
-      <c r="G145" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="H145" s="57">
+      <c r="F145" s="7">
+        <v>1</v>
+      </c>
+      <c r="G145" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H145" s="7">
         <v>2055021</v>
       </c>
-      <c r="I145" s="57" t="s">
-        <v>24</v>
-      </c>
-      <c r="L145" s="56">
+      <c r="I145" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L145" s="57">
         <v>10550202</v>
       </c>
-      <c r="M145" s="57" t="s">
+      <c r="M145" s="7" t="s">
         <v>108</v>
       </c>
       <c r="N145" s="58">
@@ -7901,38 +8529,38 @@
       </c>
       <c r="Q145" s="59"/>
     </row>
-    <row r="146" spans="1:17" s="57" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A146" s="56">
+    <row r="146" s="7" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A146" s="57">
         <v>1055022</v>
       </c>
-      <c r="B146" s="57">
+      <c r="B146" s="7">
         <v>105502</v>
       </c>
-      <c r="C146" s="57">
+      <c r="C146" s="7">
         <v>2</v>
       </c>
-      <c r="D146" s="57" t="s">
+      <c r="D146" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="E146" s="57" t="s">
+      <c r="E146" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="F146" s="57">
-        <v>1</v>
-      </c>
-      <c r="G146" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="H146" s="57">
+      <c r="F146" s="7">
+        <v>1</v>
+      </c>
+      <c r="G146" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H146" s="7">
         <v>2055021</v>
       </c>
-      <c r="I146" s="57" t="s">
-        <v>24</v>
-      </c>
-      <c r="L146" s="56">
+      <c r="I146" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L146" s="57">
         <v>10550201</v>
       </c>
-      <c r="M146" s="57" t="s">
+      <c r="M146" s="7" t="s">
         <v>118</v>
       </c>
       <c r="N146" s="58">
@@ -7943,38 +8571,38 @@
       </c>
       <c r="Q146" s="59"/>
     </row>
-    <row r="147" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A147" s="56">
+    <row r="147" ht="16.5" spans="1:17">
+      <c r="A147" s="57">
         <v>1055023</v>
       </c>
-      <c r="B147" s="57">
+      <c r="B147" s="7">
         <v>105502</v>
       </c>
-      <c r="C147" s="57">
-        <v>3</v>
-      </c>
-      <c r="D147" s="57" t="s">
+      <c r="C147" s="7">
+        <v>3</v>
+      </c>
+      <c r="D147" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="E147" s="57" t="s">
+      <c r="E147" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="F147" s="57">
-        <v>1</v>
-      </c>
-      <c r="G147" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="H147" s="57">
+      <c r="F147" s="7">
+        <v>1</v>
+      </c>
+      <c r="G147" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H147" s="7">
         <v>2055021</v>
       </c>
-      <c r="I147" s="57" t="s">
-        <v>24</v>
-      </c>
-      <c r="L147" s="56">
+      <c r="I147" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L147" s="57">
         <v>10550203</v>
       </c>
-      <c r="M147" s="57" t="s">
+      <c r="M147" s="7" t="s">
         <v>280</v>
       </c>
       <c r="N147" s="58">
@@ -7984,14 +8612,266 @@
         <v>4</v>
       </c>
     </row>
+    <row r="148" s="4" customFormat="1" ht="15" customHeight="1" spans="1:17">
+      <c r="A148" s="44">
+        <v>1041001</v>
+      </c>
+      <c r="B148" s="4">
+        <v>104100</v>
+      </c>
+      <c r="C148" s="4">
+        <v>1</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F148" s="4">
+        <v>1</v>
+      </c>
+      <c r="G148" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="H148" s="56">
+        <v>2041001</v>
+      </c>
+      <c r="I148" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L148" s="44" t="s">
+        <v>282</v>
+      </c>
+      <c r="M148" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="N148" s="61">
+        <v>3</v>
+      </c>
+      <c r="O148" s="61">
+        <v>5</v>
+      </c>
+      <c r="Q148" s="17"/>
+    </row>
+    <row r="149" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A149" s="44">
+        <v>1041002</v>
+      </c>
+      <c r="B149" s="4">
+        <v>104100</v>
+      </c>
+      <c r="C149" s="4">
+        <v>2</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E149" s="62" t="s">
+        <v>55</v>
+      </c>
+      <c r="F149" s="63">
+        <v>1</v>
+      </c>
+      <c r="G149" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="H149" s="56">
+        <v>2041001</v>
+      </c>
+      <c r="I149" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L149" s="44">
+        <v>10410002</v>
+      </c>
+      <c r="M149" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="N149" s="61">
+        <v>3</v>
+      </c>
+      <c r="O149" s="61">
+        <v>5</v>
+      </c>
+      <c r="Q149" s="17"/>
+    </row>
+    <row r="150" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A150" s="44">
+        <v>1041003</v>
+      </c>
+      <c r="B150" s="4">
+        <v>104100</v>
+      </c>
+      <c r="C150" s="4">
+        <v>3</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E150" s="62" t="s">
+        <v>81</v>
+      </c>
+      <c r="F150" s="63">
+        <v>1</v>
+      </c>
+      <c r="G150" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="H150" s="56">
+        <v>2041001</v>
+      </c>
+      <c r="I150" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="L150" s="44" t="s">
+        <v>285</v>
+      </c>
+      <c r="M150" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="N150" s="61">
+        <v>3</v>
+      </c>
+      <c r="O150" s="61">
+        <v>5</v>
+      </c>
+      <c r="Q150" s="17"/>
+    </row>
+    <row r="151" s="4" customFormat="1" ht="15" customHeight="1" spans="1:17">
+      <c r="A151" s="44">
+        <v>1042001</v>
+      </c>
+      <c r="B151" s="4">
+        <v>104200</v>
+      </c>
+      <c r="C151" s="4">
+        <v>1</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F151" s="4">
+        <v>1</v>
+      </c>
+      <c r="G151" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="H151" s="56">
+        <v>2042001</v>
+      </c>
+      <c r="I151" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L151" s="44" t="s">
+        <v>288</v>
+      </c>
+      <c r="M151" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="N151" s="61">
+        <v>3</v>
+      </c>
+      <c r="O151" s="61">
+        <v>5</v>
+      </c>
+      <c r="Q151" s="17"/>
+    </row>
+    <row r="152" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A152" s="44">
+        <v>1042002</v>
+      </c>
+      <c r="B152" s="4">
+        <v>104200</v>
+      </c>
+      <c r="C152" s="4">
+        <v>2</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="E152" s="62" t="s">
+        <v>55</v>
+      </c>
+      <c r="F152" s="63">
+        <v>1</v>
+      </c>
+      <c r="G152" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="H152" s="56">
+        <v>2042001</v>
+      </c>
+      <c r="I152" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L152" s="44">
+        <v>10420002</v>
+      </c>
+      <c r="M152" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="N152" s="61">
+        <v>3</v>
+      </c>
+      <c r="O152" s="61">
+        <v>5</v>
+      </c>
+      <c r="Q152" s="9"/>
+    </row>
+    <row r="153" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A153" s="44">
+        <v>1042003</v>
+      </c>
+      <c r="B153" s="4">
+        <v>104200</v>
+      </c>
+      <c r="C153" s="4">
+        <v>3</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="E153" s="62" t="s">
+        <v>81</v>
+      </c>
+      <c r="F153" s="63">
+        <v>1</v>
+      </c>
+      <c r="G153" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="H153" s="56">
+        <v>2042001</v>
+      </c>
+      <c r="I153" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="L153" s="44" t="s">
+        <v>289</v>
+      </c>
+      <c r="M153" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="N153" s="61">
+        <v>3</v>
+      </c>
+      <c r="O153" s="61">
+        <v>5</v>
+      </c>
+      <c r="Q153" s="9"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="J2:L2">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(MID($A2,1,4),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14460" windowHeight="11655"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -551,7 +551,7 @@
     <t>第1轴改出1个scatter+第3轴改出1个scatter+第1轴改出5个scatter</t>
   </si>
   <si>
-    <t>10200006|10200007|10200015</t>
+    <t>10200006|10200007|10200011</t>
   </si>
   <si>
     <t>第1轴改出1个scatter+第3轴改出1个scatter+第5轴改出奖池符号</t>
@@ -572,7 +572,7 @@
     <t>恶魔之子</t>
   </si>
   <si>
-    <t>10380001_1|10380004_1|10380005_1</t>
+    <t>10380001_10|10380004_1|10380005_1</t>
   </si>
   <si>
     <t>概率改出wild+概率改出奖金符号+改出奖池符号</t>
@@ -953,7 +953,7 @@
     <t>10480004|10480008</t>
   </si>
   <si>
-    <t>伽罗宝石1</t>
+    <t>伽罗宝石2</t>
   </si>
   <si>
     <t>小游戏—触发</t>
@@ -962,7 +962,7 @@
     <t>改出小游戏图标</t>
   </si>
   <si>
-    <t>伽罗宝石2</t>
+    <t>伽罗宝石3</t>
   </si>
   <si>
     <t>多格图标模式触发</t>
@@ -1009,19 +1009,13 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1185,18 +1179,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="45">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1379,12 +1373,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1422,12 +1410,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1601,13 +1583,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1616,103 +1601,106 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1721,18 +1709,12 @@
     <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1740,7 +1722,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1752,7 +1733,7 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1833,7 +1814,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1841,6 +1822,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1856,13 +1843,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2419,9 +2399,9 @@
     <col min="11" max="11" width="16.75" customWidth="1"/>
     <col min="12" max="12" width="53.25" customWidth="1"/>
     <col min="13" max="13" width="21.625" customWidth="1"/>
-    <col min="14" max="15" width="9" style="8"/>
+    <col min="14" max="15" width="9" style="7"/>
     <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="23.75" style="9" customWidth="1"/>
+    <col min="17" max="17" width="23.75" style="8" customWidth="1"/>
     <col min="18" max="18" width="60.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2437,28 +2417,28 @@
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="4"/>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="4"/>
-      <c r="J1" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="11"/>
-      <c r="L1" s="12" t="s">
+      <c r="J1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="10"/>
+      <c r="L1" s="11" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="12" t="s">
         <v>9</v>
       </c>
       <c r="Q1"/>
@@ -2475,26 +2455,26 @@
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="4"/>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="4"/>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="14"/>
-      <c r="L2" s="15" t="s">
+      <c r="K2" s="13"/>
+      <c r="L2" s="14" t="s">
         <v>12</v>
       </c>
       <c r="M2" s="4"/>
-      <c r="N2" s="16" t="s">
+      <c r="N2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="O2" s="15" t="s">
         <v>10</v>
       </c>
       <c r="Q2"/>
@@ -2503,34 +2483,34 @@
       <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18" t="s">
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="17"/>
-      <c r="H3" s="19" t="s">
+      <c r="G3" s="16"/>
+      <c r="H3" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="20" t="s">
+      <c r="I3" s="16"/>
+      <c r="J3" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="20"/>
-      <c r="L3" s="21" t="s">
+      <c r="K3" s="19"/>
+      <c r="L3" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="17"/>
-      <c r="N3" s="16" t="s">
+      <c r="M3" s="16"/>
+      <c r="N3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="O3" s="15" t="s">
         <v>20</v>
       </c>
       <c r="Q3"/>
@@ -2540,1100 +2520,1100 @@
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="10"/>
+      <c r="F4" s="9"/>
       <c r="G4" s="4"/>
-      <c r="H4" s="10"/>
+      <c r="H4" s="9"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="12"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="11"/>
       <c r="M4" s="4"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
       <c r="Q4"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A5" s="23" t="str">
+      <c r="A5" s="22" t="str">
         <f t="shared" ref="A5:A19" si="0">B5&amp;C5</f>
         <v>1001001</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="23">
         <v>100100</v>
       </c>
-      <c r="C5" s="24">
-        <v>1</v>
-      </c>
-      <c r="D5" s="24" t="s">
+      <c r="C5" s="23">
+        <v>1</v>
+      </c>
+      <c r="D5" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="24">
-        <v>1</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="23">
+      <c r="F5" s="23">
+        <v>1</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="22">
         <v>2001001</v>
       </c>
-      <c r="I5" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="26" t="s">
+      <c r="I5" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="23" t="s">
+      <c r="M5" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="16">
+      <c r="N5" s="15">
         <v>4</v>
       </c>
-      <c r="O5" s="16">
+      <c r="O5" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A6" s="23" t="str">
+      <c r="A6" s="22" t="str">
         <f t="shared" si="0"/>
         <v>1001002</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="23">
         <v>100100</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="23">
         <v>2</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="27" t="s">
+      <c r="D6" s="23"/>
+      <c r="E6" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="24">
-        <v>1</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="23">
+      <c r="F6" s="23">
+        <v>1</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="22">
         <v>2001001</v>
       </c>
-      <c r="I6" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="28" t="s">
+      <c r="I6" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="23" t="s">
+      <c r="M6" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="16">
+      <c r="N6" s="15">
         <v>4</v>
       </c>
-      <c r="O6" s="16">
+      <c r="O6" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A7" s="23" t="str">
+      <c r="A7" s="22" t="str">
         <f t="shared" si="0"/>
         <v>1001003</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="23">
         <v>100100</v>
       </c>
-      <c r="C7" s="24">
-        <v>3</v>
-      </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="29" t="s">
+      <c r="C7" s="23">
+        <v>3</v>
+      </c>
+      <c r="D7" s="23"/>
+      <c r="E7" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="24">
-        <v>1</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="23">
+      <c r="F7" s="23">
+        <v>1</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="22">
         <v>2001001</v>
       </c>
-      <c r="I7" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="26" t="s">
+      <c r="I7" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="M7" s="23" t="s">
+      <c r="M7" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="16">
+      <c r="N7" s="15">
         <v>4</v>
       </c>
-      <c r="O7" s="16">
+      <c r="O7" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A8" s="23" t="str">
+      <c r="A8" s="22" t="str">
         <f t="shared" si="0"/>
         <v>1001004</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="23">
         <v>100100</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="23">
         <v>4</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="30" t="s">
+      <c r="D8" s="23"/>
+      <c r="E8" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="31">
-        <v>1</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="23">
+      <c r="F8" s="30">
+        <v>1</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="22">
         <v>2001001</v>
       </c>
-      <c r="I8" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="26">
+      <c r="I8" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="25">
         <v>10010041</v>
       </c>
-      <c r="M8" s="23" t="s">
+      <c r="M8" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="16">
+      <c r="N8" s="15">
         <v>4</v>
       </c>
-      <c r="O8" s="16">
+      <c r="O8" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A9" s="23" t="str">
+      <c r="A9" s="22" t="str">
         <f t="shared" si="0"/>
         <v>1001005</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="23">
         <v>100100</v>
       </c>
-      <c r="C9" s="24">
-        <v>5</v>
-      </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="32" t="s">
+      <c r="C9" s="23">
+        <v>5</v>
+      </c>
+      <c r="D9" s="23"/>
+      <c r="E9" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="31">
-        <v>1</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="23">
+      <c r="F9" s="30">
+        <v>1</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="22">
         <v>2001001</v>
       </c>
-      <c r="I9" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="26" t="s">
+      <c r="I9" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="23" t="s">
+      <c r="M9" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="N9" s="16">
+      <c r="N9" s="15">
         <v>4</v>
       </c>
-      <c r="O9" s="16">
+      <c r="O9" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A10" s="23" t="str">
+      <c r="A10" s="22" t="str">
         <f t="shared" si="0"/>
         <v>1001006</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="23">
         <v>100100</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="23">
         <v>6</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="32" t="s">
+      <c r="D10" s="23"/>
+      <c r="E10" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="31">
-        <v>1</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="23">
+      <c r="F10" s="30">
+        <v>1</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="22">
         <v>2001001</v>
       </c>
-      <c r="I10" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="26">
+      <c r="I10" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="25">
         <v>10010061</v>
       </c>
-      <c r="M10" s="23" t="s">
+      <c r="M10" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="16">
+      <c r="N10" s="15">
         <v>4</v>
       </c>
-      <c r="O10" s="16">
+      <c r="O10" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A11" s="23" t="str">
+      <c r="A11" s="22" t="str">
         <f t="shared" si="0"/>
         <v>1001007</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="23">
         <v>100100</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="23">
         <v>7</v>
       </c>
-      <c r="D11" s="24"/>
-      <c r="E11" s="27" t="s">
+      <c r="D11" s="23"/>
+      <c r="E11" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="24">
-        <v>1</v>
-      </c>
-      <c r="G11" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="23">
+      <c r="F11" s="23">
+        <v>1</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="22">
         <v>2001001</v>
       </c>
-      <c r="I11" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="28" t="s">
+      <c r="I11" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="M11" s="23" t="s">
+      <c r="M11" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="N11" s="16">
+      <c r="N11" s="15">
         <v>4</v>
       </c>
-      <c r="O11" s="16">
+      <c r="O11" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A12" s="33" t="str">
+      <c r="A12" s="32" t="str">
         <f t="shared" si="0"/>
         <v>1003001</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="24">
         <v>100300</v>
       </c>
-      <c r="C12" s="25">
-        <v>1</v>
-      </c>
-      <c r="D12" s="25" t="s">
+      <c r="C12" s="24">
+        <v>1</v>
+      </c>
+      <c r="D12" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="25">
-        <v>1</v>
-      </c>
-      <c r="G12" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="33">
+      <c r="F12" s="24">
+        <v>1</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="32">
         <v>2003001</v>
       </c>
-      <c r="I12" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="34">
+      <c r="I12" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="33">
         <v>10030022</v>
       </c>
-      <c r="M12" s="33" t="s">
+      <c r="M12" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="N12" s="25">
-        <v>3</v>
-      </c>
-      <c r="O12" s="25">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="35"/>
+      <c r="N12" s="24">
+        <v>3</v>
+      </c>
+      <c r="O12" s="24">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="34"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A13" s="33" t="str">
+      <c r="A13" s="32" t="str">
         <f t="shared" si="0"/>
         <v>1003002</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="24">
         <v>100300</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="24">
         <v>2</v>
       </c>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25" t="s">
+      <c r="D13" s="24"/>
+      <c r="E13" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="25">
-        <v>1</v>
-      </c>
-      <c r="G13" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="33">
+      <c r="F13" s="24">
+        <v>1</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="32">
         <v>2003001</v>
       </c>
-      <c r="I13" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="34" t="s">
+      <c r="I13" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="33" t="s">
+      <c r="M13" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="N13" s="25">
-        <v>3</v>
-      </c>
-      <c r="O13" s="25">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="35"/>
+      <c r="N13" s="24">
+        <v>3</v>
+      </c>
+      <c r="O13" s="24">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="34"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A14" s="33" t="str">
+      <c r="A14" s="32" t="str">
         <f t="shared" si="0"/>
         <v>1003003</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="24">
         <v>100300</v>
       </c>
-      <c r="C14" s="25">
-        <v>3</v>
-      </c>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25" t="s">
+      <c r="C14" s="24">
+        <v>3</v>
+      </c>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="25">
-        <v>1</v>
-      </c>
-      <c r="G14" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="33">
+      <c r="F14" s="24">
+        <v>1</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="32">
         <v>2003002</v>
       </c>
-      <c r="I14" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="33" t="s">
+      <c r="I14" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="33" t="s">
+      <c r="K14" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="34" t="s">
+      <c r="L14" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="33" t="s">
+      <c r="M14" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="25">
-        <v>3</v>
-      </c>
-      <c r="O14" s="25">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="35"/>
+      <c r="N14" s="24">
+        <v>3</v>
+      </c>
+      <c r="O14" s="24">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="34"/>
     </row>
     <row r="15" ht="16.5" spans="1:17">
-      <c r="A15" s="36" t="str">
+      <c r="A15" s="35" t="str">
         <f t="shared" si="0"/>
         <v>1007001</v>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="36">
         <v>100700</v>
       </c>
-      <c r="C15" s="37">
-        <v>1</v>
-      </c>
-      <c r="D15" s="37" t="s">
+      <c r="C15" s="36">
+        <v>1</v>
+      </c>
+      <c r="D15" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="37">
-        <v>1</v>
-      </c>
-      <c r="G15" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="36">
+      <c r="F15" s="36">
+        <v>1</v>
+      </c>
+      <c r="G15" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="35">
         <v>2007001</v>
       </c>
-      <c r="I15" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="36"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="38" t="s">
+      <c r="I15" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="M15" s="36" t="s">
+      <c r="M15" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="N15" s="16">
+      <c r="N15" s="15">
         <v>4</v>
       </c>
-      <c r="O15" s="16">
+      <c r="O15" s="15">
         <v>5</v>
       </c>
       <c r="Q15"/>
     </row>
     <row r="16" ht="16.5" spans="1:17">
-      <c r="A16" s="36" t="str">
+      <c r="A16" s="35" t="str">
         <f t="shared" si="0"/>
         <v>1007002</v>
       </c>
-      <c r="B16" s="37">
+      <c r="B16" s="36">
         <v>100700</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="36">
         <v>2</v>
       </c>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37" t="s">
+      <c r="D16" s="36"/>
+      <c r="E16" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="37">
-        <v>1</v>
-      </c>
-      <c r="G16" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="36">
+      <c r="F16" s="36">
+        <v>1</v>
+      </c>
+      <c r="G16" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="35">
         <v>2007001</v>
       </c>
-      <c r="I16" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="38" t="s">
+      <c r="I16" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="36" t="s">
+      <c r="M16" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="16">
+      <c r="N16" s="15">
         <v>4</v>
       </c>
-      <c r="O16" s="16">
+      <c r="O16" s="15">
         <v>5</v>
       </c>
       <c r="Q16"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A17" s="39" t="str">
+      <c r="A17" s="38" t="str">
         <f t="shared" si="0"/>
         <v>1012001</v>
       </c>
-      <c r="B17" s="40">
+      <c r="B17" s="39">
         <v>101200</v>
       </c>
-      <c r="C17" s="40">
-        <v>1</v>
-      </c>
-      <c r="D17" s="40" t="s">
+      <c r="C17" s="39">
+        <v>1</v>
+      </c>
+      <c r="D17" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="40" t="s">
+      <c r="E17" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="40">
-        <v>1</v>
-      </c>
-      <c r="G17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="39">
+      <c r="F17" s="39">
+        <v>1</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="38">
         <v>2012001</v>
       </c>
-      <c r="I17" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="41">
+      <c r="I17" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="40">
         <v>10120011</v>
       </c>
-      <c r="M17" s="39" t="s">
+      <c r="M17" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="N17" s="40">
-        <v>3</v>
-      </c>
-      <c r="O17" s="40">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="42"/>
+      <c r="N17" s="39">
+        <v>3</v>
+      </c>
+      <c r="O17" s="39">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="41"/>
     </row>
     <row r="18" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A18" s="39" t="str">
+      <c r="A18" s="38" t="str">
         <f t="shared" si="0"/>
         <v>1012002</v>
       </c>
-      <c r="B18" s="40">
+      <c r="B18" s="39">
         <v>101200</v>
       </c>
-      <c r="C18" s="40">
+      <c r="C18" s="39">
         <v>2</v>
       </c>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40" t="s">
+      <c r="D18" s="39"/>
+      <c r="E18" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="40">
-        <v>1</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="39">
+      <c r="F18" s="39">
+        <v>1</v>
+      </c>
+      <c r="G18" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="38">
         <v>2012001</v>
       </c>
-      <c r="I18" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="41">
+      <c r="I18" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="40">
         <v>10120021</v>
       </c>
-      <c r="M18" s="39" t="s">
+      <c r="M18" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="N18" s="40">
-        <v>3</v>
-      </c>
-      <c r="O18" s="40">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="42"/>
+      <c r="N18" s="39">
+        <v>3</v>
+      </c>
+      <c r="O18" s="39">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="41"/>
     </row>
     <row r="19" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A19" s="39" t="str">
+      <c r="A19" s="38" t="str">
         <f t="shared" si="0"/>
         <v>1012003</v>
       </c>
-      <c r="B19" s="40">
+      <c r="B19" s="39">
         <v>101200</v>
       </c>
-      <c r="C19" s="40">
-        <v>3</v>
-      </c>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40" t="s">
+      <c r="C19" s="39">
+        <v>3</v>
+      </c>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="40">
-        <v>1</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" s="39">
+      <c r="F19" s="39">
+        <v>1</v>
+      </c>
+      <c r="G19" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="38">
         <v>2012001</v>
       </c>
-      <c r="I19" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="39" t="s">
+      <c r="I19" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="K19" s="39" t="s">
+      <c r="K19" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="L19" s="41"/>
-      <c r="M19" s="39" t="s">
+      <c r="L19" s="40"/>
+      <c r="M19" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="N19" s="40">
-        <v>3</v>
-      </c>
-      <c r="O19" s="40">
-        <v>5</v>
-      </c>
-      <c r="Q19" s="42"/>
+      <c r="N19" s="39">
+        <v>3</v>
+      </c>
+      <c r="O19" s="39">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="41"/>
     </row>
     <row r="20" ht="16.5" spans="1:17">
-      <c r="A20" s="33" t="str">
+      <c r="A20" s="32" t="str">
         <f t="shared" ref="A20:A30" si="1">B20&amp;C20</f>
         <v>1014001</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="24">
         <v>101400</v>
       </c>
-      <c r="C20" s="25">
-        <v>1</v>
-      </c>
-      <c r="D20" s="25" t="s">
+      <c r="C20" s="24">
+        <v>1</v>
+      </c>
+      <c r="D20" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="25" t="s">
+      <c r="E20" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="25">
-        <v>1</v>
-      </c>
-      <c r="G20" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="33">
+      <c r="F20" s="24">
+        <v>1</v>
+      </c>
+      <c r="G20" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="32">
         <v>2014001</v>
       </c>
-      <c r="I20" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="34" t="s">
+      <c r="I20" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="M20" s="33" t="s">
+      <c r="M20" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="N20" s="16">
+      <c r="N20" s="15">
         <v>4</v>
       </c>
-      <c r="O20" s="16">
+      <c r="O20" s="15">
         <v>3</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:17">
-      <c r="A21" s="33" t="str">
+      <c r="A21" s="32" t="str">
         <f t="shared" si="1"/>
         <v>1014002</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="24">
         <v>101400</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="24">
         <v>2</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="25">
-        <v>1</v>
-      </c>
-      <c r="G21" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="33">
+      <c r="F21" s="24">
+        <v>1</v>
+      </c>
+      <c r="G21" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="32">
         <v>2014001</v>
       </c>
-      <c r="I21" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="34" t="s">
+      <c r="I21" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="33" t="s">
+      <c r="M21" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="N21" s="16">
+      <c r="N21" s="15">
         <v>4</v>
       </c>
-      <c r="O21" s="16">
+      <c r="O21" s="15">
         <v>3</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:17">
-      <c r="A22" s="33" t="str">
+      <c r="A22" s="32" t="str">
         <f t="shared" si="1"/>
         <v>1014003</v>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="24">
         <v>101400</v>
       </c>
-      <c r="C22" s="25">
-        <v>3</v>
-      </c>
-      <c r="D22" s="25" t="s">
+      <c r="C22" s="24">
+        <v>3</v>
+      </c>
+      <c r="D22" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="25" t="s">
+      <c r="E22" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="25">
-        <v>1</v>
-      </c>
-      <c r="G22" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="33">
+      <c r="F22" s="24">
+        <v>1</v>
+      </c>
+      <c r="G22" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="32">
         <v>2014001</v>
       </c>
-      <c r="I22" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="34">
+      <c r="I22" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="33">
         <v>10140021</v>
       </c>
-      <c r="M22" s="33" t="s">
+      <c r="M22" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="N22" s="16">
+      <c r="N22" s="15">
         <v>4</v>
       </c>
-      <c r="O22" s="16">
+      <c r="O22" s="15">
         <v>3</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A23" s="23" t="str">
+      <c r="A23" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024001</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="23">
         <v>102400</v>
       </c>
-      <c r="C23" s="24">
-        <v>1</v>
-      </c>
-      <c r="D23" s="24" t="s">
+      <c r="C23" s="23">
+        <v>1</v>
+      </c>
+      <c r="D23" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="25" t="s">
+      <c r="E23" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="24">
-        <v>1</v>
-      </c>
-      <c r="G23" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="23">
+      <c r="F23" s="23">
+        <v>1</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="22">
         <v>2024001</v>
       </c>
-      <c r="I23" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="26" t="s">
+      <c r="I23" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="M23" s="23" t="s">
+      <c r="M23" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="N23" s="16">
+      <c r="N23" s="15">
         <v>4</v>
       </c>
-      <c r="O23" s="16">
+      <c r="O23" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A24" s="23" t="str">
+      <c r="A24" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024002</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="23">
         <v>102400</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="23">
         <v>2</v>
       </c>
-      <c r="D24" s="24"/>
-      <c r="E24" s="27" t="s">
+      <c r="D24" s="23"/>
+      <c r="E24" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="24">
-        <v>1</v>
-      </c>
-      <c r="G24" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="23">
+      <c r="F24" s="23">
+        <v>1</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="22">
         <v>2024001</v>
       </c>
-      <c r="I24" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="28" t="s">
+      <c r="I24" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="M24" s="23" t="s">
+      <c r="M24" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="N24" s="16">
+      <c r="N24" s="15">
         <v>4</v>
       </c>
-      <c r="O24" s="16">
+      <c r="O24" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A25" s="23" t="str">
+      <c r="A25" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024003</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B25" s="23">
         <v>102400</v>
       </c>
-      <c r="C25" s="24">
-        <v>3</v>
-      </c>
-      <c r="D25" s="24"/>
-      <c r="E25" s="29" t="s">
+      <c r="C25" s="23">
+        <v>3</v>
+      </c>
+      <c r="D25" s="23"/>
+      <c r="E25" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="24">
-        <v>1</v>
-      </c>
-      <c r="G25" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="23">
+      <c r="F25" s="23">
+        <v>1</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="22">
         <v>2024001</v>
       </c>
-      <c r="I25" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="26" t="s">
+      <c r="I25" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="M25" s="23" t="s">
+      <c r="M25" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="N25" s="16">
+      <c r="N25" s="15">
         <v>4</v>
       </c>
-      <c r="O25" s="16">
+      <c r="O25" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A26" s="23" t="str">
+      <c r="A26" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024004</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B26" s="23">
         <v>102400</v>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="23">
         <v>4</v>
       </c>
-      <c r="D26" s="24"/>
-      <c r="E26" s="30" t="s">
+      <c r="D26" s="23"/>
+      <c r="E26" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="31">
-        <v>1</v>
-      </c>
-      <c r="G26" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="23">
+      <c r="F26" s="30">
+        <v>1</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="22">
         <v>2024001</v>
       </c>
-      <c r="I26" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="26">
+      <c r="I26" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="25">
         <v>10240041</v>
       </c>
-      <c r="M26" s="23" t="s">
+      <c r="M26" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="N26" s="16">
+      <c r="N26" s="15">
         <v>4</v>
       </c>
-      <c r="O26" s="16">
+      <c r="O26" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A27" s="23" t="str">
+      <c r="A27" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024005</v>
       </c>
-      <c r="B27" s="24">
+      <c r="B27" s="23">
         <v>102400</v>
       </c>
-      <c r="C27" s="24">
-        <v>5</v>
-      </c>
-      <c r="D27" s="24"/>
-      <c r="E27" s="32" t="s">
+      <c r="C27" s="23">
+        <v>5</v>
+      </c>
+      <c r="D27" s="23"/>
+      <c r="E27" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="F27" s="31">
-        <v>1</v>
-      </c>
-      <c r="G27" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="23">
+      <c r="F27" s="30">
+        <v>1</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="22">
         <v>2024001</v>
       </c>
-      <c r="I27" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="26" t="s">
+      <c r="I27" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="M27" s="23" t="s">
+      <c r="M27" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="N27" s="16">
+      <c r="N27" s="15">
         <v>4</v>
       </c>
-      <c r="O27" s="16">
+      <c r="O27" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A28" s="23" t="str">
+      <c r="A28" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024006</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B28" s="23">
         <v>102400</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="23">
         <v>6</v>
       </c>
-      <c r="D28" s="24"/>
-      <c r="E28" s="32" t="s">
+      <c r="D28" s="23"/>
+      <c r="E28" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="31">
-        <v>1</v>
-      </c>
-      <c r="G28" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="23">
+      <c r="F28" s="30">
+        <v>1</v>
+      </c>
+      <c r="G28" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="22">
         <v>2024001</v>
       </c>
-      <c r="I28" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="26">
+      <c r="I28" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="25">
         <v>10240061</v>
       </c>
-      <c r="M28" s="23" t="s">
+      <c r="M28" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="N28" s="16">
+      <c r="N28" s="15">
         <v>4</v>
       </c>
-      <c r="O28" s="16">
+      <c r="O28" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A29" s="23" t="str">
+      <c r="A29" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1024007</v>
       </c>
-      <c r="B29" s="24">
+      <c r="B29" s="23">
         <v>102400</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="23">
         <v>7</v>
       </c>
-      <c r="D29" s="24"/>
-      <c r="E29" s="27" t="s">
+      <c r="D29" s="23"/>
+      <c r="E29" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="24">
-        <v>1</v>
-      </c>
-      <c r="G29" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="23">
+      <c r="F29" s="23">
+        <v>1</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="22">
         <v>2024001</v>
       </c>
-      <c r="I29" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="28" t="s">
+      <c r="I29" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="M29" s="23" t="s">
+      <c r="M29" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="N29" s="16">
+      <c r="N29" s="15">
         <v>4</v>
       </c>
-      <c r="O29" s="16">
+      <c r="O29" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="30" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A30" s="23" t="str">
+      <c r="A30" s="22" t="str">
         <f t="shared" si="1"/>
         <v>1017001</v>
       </c>
@@ -3667,16 +3647,16 @@
       <c r="M30" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="N30" s="43">
+      <c r="N30" s="42">
         <v>4</v>
       </c>
-      <c r="O30" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q30" s="17"/>
+      <c r="O30" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q30" s="16"/>
     </row>
     <row r="31" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A31" s="23" t="str">
+      <c r="A31" s="22" t="str">
         <f t="shared" ref="A31:A54" si="2">B31&amp;C31</f>
         <v>1017002</v>
       </c>
@@ -3710,16 +3690,16 @@
       <c r="M31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="N31" s="43">
+      <c r="N31" s="42">
         <v>4</v>
       </c>
-      <c r="O31" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q31" s="17"/>
+      <c r="O31" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="16"/>
     </row>
     <row r="32" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A32" s="23" t="str">
+      <c r="A32" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1017003</v>
       </c>
@@ -3753,16 +3733,16 @@
       <c r="M32" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="N32" s="43">
+      <c r="N32" s="42">
         <v>4</v>
       </c>
-      <c r="O32" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="17"/>
+      <c r="O32" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="16"/>
     </row>
     <row r="33" s="4" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A33" s="23" t="str">
+      <c r="A33" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1022001</v>
       </c>
@@ -3790,22 +3770,22 @@
       <c r="I33" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="44" t="s">
+      <c r="L33" s="43" t="s">
         <v>85</v>
       </c>
       <c r="M33" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="N33" s="43">
-        <v>3</v>
-      </c>
-      <c r="O33" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="17"/>
+      <c r="N33" s="42">
+        <v>3</v>
+      </c>
+      <c r="O33" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="16"/>
     </row>
     <row r="34" s="4" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A34" s="23" t="str">
+      <c r="A34" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1022002</v>
       </c>
@@ -3821,7 +3801,7 @@
       <c r="E34" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="15">
         <v>1</v>
       </c>
       <c r="G34" s="4" t="s">
@@ -3833,22 +3813,22 @@
       <c r="I34" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L34" s="44">
+      <c r="L34" s="43">
         <v>10220033</v>
       </c>
       <c r="M34" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="N34" s="43">
-        <v>3</v>
-      </c>
-      <c r="O34" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q34" s="17"/>
+      <c r="N34" s="42">
+        <v>3</v>
+      </c>
+      <c r="O34" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q34" s="16"/>
     </row>
     <row r="35" s="4" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A35" s="23" t="str">
+      <c r="A35" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1022003</v>
       </c>
@@ -3876,22 +3856,22 @@
       <c r="I35" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="44" t="s">
+      <c r="L35" s="43" t="s">
         <v>89</v>
       </c>
       <c r="M35" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="N35" s="43">
-        <v>3</v>
-      </c>
-      <c r="O35" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="17"/>
+      <c r="N35" s="42">
+        <v>3</v>
+      </c>
+      <c r="O35" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="16"/>
     </row>
     <row r="36" s="4" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A36" s="23" t="str">
+      <c r="A36" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1022004</v>
       </c>
@@ -3907,7 +3887,7 @@
       <c r="E36" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="15">
         <v>1</v>
       </c>
       <c r="G36" s="4" t="s">
@@ -3919,19 +3899,19 @@
       <c r="I36" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L36" s="44">
+      <c r="L36" s="43">
         <v>10220020</v>
       </c>
-      <c r="N36" s="43">
-        <v>3</v>
-      </c>
-      <c r="O36" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q36" s="17"/>
+      <c r="N36" s="42">
+        <v>3</v>
+      </c>
+      <c r="O36" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="16"/>
     </row>
     <row r="37" s="4" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A37" s="23" t="str">
+      <c r="A37" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1022005</v>
       </c>
@@ -3959,20 +3939,20 @@
       <c r="I37" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L37" s="44">
+      <c r="L37" s="43">
         <v>10220019</v>
       </c>
-      <c r="N37" s="43">
-        <v>3</v>
-      </c>
-      <c r="O37" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q37" s="17"/>
-      <c r="S37" s="45"/>
+      <c r="N37" s="42">
+        <v>3</v>
+      </c>
+      <c r="O37" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q37" s="16"/>
+      <c r="S37" s="44"/>
     </row>
     <row r="38" s="4" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A38" s="23" t="str">
+      <c r="A38" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1021001</v>
       </c>
@@ -4000,23 +3980,23 @@
       <c r="I38" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L38" s="44" t="s">
+      <c r="L38" s="43" t="s">
         <v>93</v>
       </c>
       <c r="M38" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="N38" s="43">
-        <v>3</v>
-      </c>
-      <c r="O38" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q38" s="17"/>
-      <c r="S38" s="45"/>
+      <c r="N38" s="42">
+        <v>3</v>
+      </c>
+      <c r="O38" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="16"/>
+      <c r="S38" s="44"/>
     </row>
     <row r="39" s="4" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A39" s="23" t="str">
+      <c r="A39" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1021002</v>
       </c>
@@ -4044,23 +4024,23 @@
       <c r="I39" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="44">
+      <c r="L39" s="43">
         <v>10210031</v>
       </c>
       <c r="M39" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="N39" s="43">
-        <v>3</v>
-      </c>
-      <c r="O39" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q39" s="17"/>
-      <c r="S39" s="45"/>
+      <c r="N39" s="42">
+        <v>3</v>
+      </c>
+      <c r="O39" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q39" s="16"/>
+      <c r="S39" s="44"/>
     </row>
     <row r="40" s="4" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A40" s="23" t="str">
+      <c r="A40" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1021003</v>
       </c>
@@ -4088,23 +4068,23 @@
       <c r="I40" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L40" s="44">
+      <c r="L40" s="43">
         <v>10210041</v>
       </c>
       <c r="M40" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="N40" s="43">
-        <v>3</v>
-      </c>
-      <c r="O40" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q40" s="17"/>
-      <c r="S40" s="45"/>
+      <c r="N40" s="42">
+        <v>3</v>
+      </c>
+      <c r="O40" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q40" s="16"/>
+      <c r="S40" s="44"/>
     </row>
     <row r="41" s="4" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A41" s="23" t="str">
+      <c r="A41" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1021004</v>
       </c>
@@ -4132,23 +4112,23 @@
       <c r="I41" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L41" s="44" t="s">
+      <c r="L41" s="43" t="s">
         <v>96</v>
       </c>
       <c r="M41" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="N41" s="43">
-        <v>3</v>
-      </c>
-      <c r="O41" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q41" s="17"/>
-      <c r="S41" s="45"/>
+      <c r="N41" s="42">
+        <v>3</v>
+      </c>
+      <c r="O41" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q41" s="16"/>
+      <c r="S41" s="44"/>
     </row>
     <row r="42" s="4" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A42" s="23" t="str">
+      <c r="A42" s="22" t="str">
         <f t="shared" si="2"/>
         <v>1018001</v>
       </c>
@@ -4176,20 +4156,20 @@
       <c r="I42" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L42" s="44" t="s">
+      <c r="L42" s="43" t="s">
         <v>98</v>
       </c>
       <c r="M42" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="N42" s="43">
+      <c r="N42" s="42">
         <v>4</v>
       </c>
-      <c r="O42" s="43">
+      <c r="O42" s="42">
         <v>6</v>
       </c>
-      <c r="Q42" s="17"/>
-      <c r="S42" s="45"/>
+      <c r="Q42" s="16"/>
+      <c r="S42" s="44"/>
     </row>
     <row r="43" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A43" s="4" t="str">
@@ -4220,16 +4200,16 @@
       <c r="I43" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L43" s="44">
+      <c r="L43" s="43">
         <v>10180031</v>
       </c>
       <c r="M43" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="N43" s="43">
+      <c r="N43" s="42">
         <v>4</v>
       </c>
-      <c r="O43" s="43">
+      <c r="O43" s="42">
         <v>6</v>
       </c>
     </row>
@@ -4262,16 +4242,16 @@
       <c r="I44" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L44" s="44" t="s">
+      <c r="L44" s="43" t="s">
         <v>99</v>
       </c>
       <c r="M44" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="N44" s="43">
+      <c r="N44" s="42">
         <v>4</v>
       </c>
-      <c r="O44" s="43">
+      <c r="O44" s="42">
         <v>6</v>
       </c>
     </row>
@@ -4304,16 +4284,16 @@
       <c r="I45" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="44" t="s">
+      <c r="L45" s="43" t="s">
         <v>101</v>
       </c>
       <c r="M45" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="N45" s="43">
-        <v>3</v>
-      </c>
-      <c r="O45" s="43">
+      <c r="N45" s="42">
+        <v>3</v>
+      </c>
+      <c r="O45" s="42">
         <v>5</v>
       </c>
     </row>
@@ -4346,16 +4326,16 @@
       <c r="I46" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L46" s="44">
+      <c r="L46" s="43">
         <v>10250031</v>
       </c>
       <c r="M46" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="N46" s="43">
-        <v>3</v>
-      </c>
-      <c r="O46" s="43">
+      <c r="N46" s="42">
+        <v>3</v>
+      </c>
+      <c r="O46" s="42">
         <v>5</v>
       </c>
     </row>
@@ -4388,16 +4368,16 @@
       <c r="I47" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L47" s="44" t="s">
+      <c r="L47" s="43" t="s">
         <v>103</v>
       </c>
       <c r="M47" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="N47" s="43">
-        <v>3</v>
-      </c>
-      <c r="O47" s="43">
+      <c r="N47" s="42">
+        <v>3</v>
+      </c>
+      <c r="O47" s="42">
         <v>5</v>
       </c>
     </row>
@@ -4430,16 +4410,16 @@
       <c r="I48" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L48" s="44" t="s">
+      <c r="L48" s="43" t="s">
         <v>105</v>
       </c>
       <c r="M48" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="N48" s="43">
+      <c r="N48" s="42">
         <v>4</v>
       </c>
-      <c r="O48" s="43">
+      <c r="O48" s="42">
         <v>5</v>
       </c>
     </row>
@@ -4472,16 +4452,16 @@
       <c r="I49" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L49" s="44">
+      <c r="L49" s="43">
         <v>10230003</v>
       </c>
       <c r="M49" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="N49" s="43">
+      <c r="N49" s="42">
         <v>4</v>
       </c>
-      <c r="O49" s="43">
+      <c r="O49" s="42">
         <v>5</v>
       </c>
     </row>
@@ -4514,16 +4494,16 @@
       <c r="I50" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="44" t="s">
+      <c r="L50" s="43" t="s">
         <v>106</v>
       </c>
       <c r="M50" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="N50" s="43">
+      <c r="N50" s="42">
         <v>4</v>
       </c>
-      <c r="O50" s="43">
+      <c r="O50" s="42">
         <v>5</v>
       </c>
     </row>
@@ -4556,16 +4536,16 @@
       <c r="I51" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L51" s="44">
+      <c r="L51" s="43">
         <v>10340007</v>
       </c>
       <c r="M51" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="N51" s="43">
-        <v>3</v>
-      </c>
-      <c r="O51" s="43">
+      <c r="N51" s="42">
+        <v>3</v>
+      </c>
+      <c r="O51" s="42">
         <v>3</v>
       </c>
     </row>
@@ -4598,15 +4578,15 @@
       <c r="I52" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L52" s="44"/>
+      <c r="L52" s="43"/>
       <c r="M52" s="4"/>
-      <c r="N52" s="43">
-        <v>3</v>
-      </c>
-      <c r="O52" s="43">
-        <v>3</v>
-      </c>
-      <c r="P52" s="46"/>
+      <c r="N52" s="42">
+        <v>3</v>
+      </c>
+      <c r="O52" s="42">
+        <v>3</v>
+      </c>
+      <c r="P52" s="45"/>
     </row>
     <row r="53" ht="16.5" spans="1:16">
       <c r="A53" s="4" t="str">
@@ -4637,12 +4617,12 @@
       <c r="I53" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L53" s="44"/>
+      <c r="L53" s="43"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="43">
-        <v>3</v>
-      </c>
-      <c r="O53" s="43">
+      <c r="N53" s="42">
+        <v>3</v>
+      </c>
+      <c r="O53" s="42">
         <v>3</v>
       </c>
     </row>
@@ -4675,16 +4655,16 @@
       <c r="I54" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L54" s="44" t="s">
+      <c r="L54" s="43" t="s">
         <v>112</v>
       </c>
       <c r="M54" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="N54" s="43">
+      <c r="N54" s="42">
         <v>4</v>
       </c>
-      <c r="O54" s="43">
+      <c r="O54" s="42">
         <v>3</v>
       </c>
     </row>
@@ -4717,16 +4697,16 @@
       <c r="I55" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="44" t="s">
+      <c r="L55" s="43" t="s">
         <v>115</v>
       </c>
       <c r="M55" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="N55" s="43">
+      <c r="N55" s="42">
         <v>4</v>
       </c>
-      <c r="O55" s="43">
+      <c r="O55" s="42">
         <v>3</v>
       </c>
     </row>
@@ -4759,21 +4739,21 @@
       <c r="I56" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L56" s="44" t="s">
+      <c r="L56" s="43" t="s">
         <v>117</v>
       </c>
       <c r="M56" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="N56" s="43">
+      <c r="N56" s="42">
         <v>4</v>
       </c>
-      <c r="O56" s="43">
+      <c r="O56" s="42">
         <v>3</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:16">
-      <c r="A57" s="44">
+      <c r="A57" s="43">
         <v>1035011</v>
       </c>
       <c r="B57" s="4">
@@ -4800,16 +4780,16 @@
       <c r="I57" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L57" s="44" t="s">
+      <c r="L57" s="43" t="s">
         <v>120</v>
       </c>
       <c r="M57" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="N57" s="43">
+      <c r="N57" s="42">
         <v>4</v>
       </c>
-      <c r="O57" s="43">
+      <c r="O57" s="42">
         <v>3</v>
       </c>
     </row>
@@ -4842,16 +4822,16 @@
       <c r="I58" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L58" s="44" t="s">
+      <c r="L58" s="43" t="s">
         <v>121</v>
       </c>
       <c r="M58" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="N58" s="43">
+      <c r="N58" s="42">
         <v>4</v>
       </c>
-      <c r="O58" s="43">
+      <c r="O58" s="42">
         <v>3</v>
       </c>
     </row>
@@ -4884,16 +4864,16 @@
       <c r="I59" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="44" t="s">
+      <c r="L59" s="43" t="s">
         <v>122</v>
       </c>
       <c r="M59" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="N59" s="43">
+      <c r="N59" s="42">
         <v>4</v>
       </c>
-      <c r="O59" s="43">
+      <c r="O59" s="42">
         <v>3</v>
       </c>
     </row>
@@ -4926,16 +4906,16 @@
       <c r="I60" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L60" s="44" t="s">
+      <c r="L60" s="43" t="s">
         <v>124</v>
       </c>
       <c r="M60" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="N60" s="43">
-        <v>3</v>
-      </c>
-      <c r="O60" s="43">
+      <c r="N60" s="42">
+        <v>3</v>
+      </c>
+      <c r="O60" s="42">
         <v>3</v>
       </c>
     </row>
@@ -4968,16 +4948,16 @@
       <c r="I61" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L61" s="44">
+      <c r="L61" s="43">
         <v>10360004</v>
       </c>
       <c r="M61" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="N61" s="43">
-        <v>3</v>
-      </c>
-      <c r="O61" s="43">
+      <c r="N61" s="42">
+        <v>3</v>
+      </c>
+      <c r="O61" s="42">
         <v>3</v>
       </c>
     </row>
@@ -5010,16 +4990,16 @@
       <c r="I62" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L62" s="44">
+      <c r="L62" s="43">
         <v>10360002</v>
       </c>
       <c r="M62" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="N62" s="43">
-        <v>3</v>
-      </c>
-      <c r="O62" s="43">
+      <c r="N62" s="42">
+        <v>3</v>
+      </c>
+      <c r="O62" s="42">
         <v>3</v>
       </c>
     </row>
@@ -5052,16 +5032,16 @@
       <c r="I63" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L63" s="44" t="s">
+      <c r="L63" s="43" t="s">
         <v>130</v>
       </c>
       <c r="M63" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="N63" s="43">
-        <v>5</v>
-      </c>
-      <c r="O63" s="43">
+      <c r="N63" s="42">
+        <v>5</v>
+      </c>
+      <c r="O63" s="42">
         <v>6</v>
       </c>
     </row>
@@ -5094,16 +5074,16 @@
       <c r="I64" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L64" s="44">
+      <c r="L64" s="43">
         <v>10280002</v>
       </c>
       <c r="M64" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="N64" s="43">
-        <v>5</v>
-      </c>
-      <c r="O64" s="43">
+      <c r="N64" s="42">
+        <v>5</v>
+      </c>
+      <c r="O64" s="42">
         <v>6</v>
       </c>
     </row>
@@ -5136,16 +5116,16 @@
       <c r="I65" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L65" s="44" t="s">
+      <c r="L65" s="43" t="s">
         <v>133</v>
       </c>
       <c r="M65" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="N65" s="43">
-        <v>5</v>
-      </c>
-      <c r="O65" s="43">
+      <c r="N65" s="42">
+        <v>5</v>
+      </c>
+      <c r="O65" s="42">
         <v>6</v>
       </c>
     </row>
@@ -5178,16 +5158,16 @@
       <c r="I66" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L66" s="44">
+      <c r="L66" s="43">
         <v>10340101</v>
       </c>
       <c r="M66" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="N66" s="43">
-        <v>3</v>
-      </c>
-      <c r="O66" s="43">
+      <c r="N66" s="42">
+        <v>3</v>
+      </c>
+      <c r="O66" s="42">
         <v>3</v>
       </c>
     </row>
@@ -5220,15 +5200,15 @@
       <c r="I67" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L67" s="44"/>
+      <c r="L67" s="43"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="43">
-        <v>3</v>
-      </c>
-      <c r="O67" s="43">
-        <v>3</v>
-      </c>
-      <c r="P67" s="46"/>
+      <c r="N67" s="42">
+        <v>3</v>
+      </c>
+      <c r="O67" s="42">
+        <v>3</v>
+      </c>
+      <c r="P67" s="45"/>
     </row>
     <row r="68" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A68" s="4" t="str">
@@ -5261,58 +5241,58 @@
       </c>
       <c r="J68"/>
       <c r="K68"/>
-      <c r="L68" s="44"/>
+      <c r="L68" s="43"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="43">
-        <v>3</v>
-      </c>
-      <c r="O68" s="43">
-        <v>3</v>
-      </c>
-      <c r="Q68" s="47"/>
+      <c r="N68" s="42">
+        <v>3</v>
+      </c>
+      <c r="O68" s="42">
+        <v>3</v>
+      </c>
+      <c r="Q68" s="46"/>
     </row>
     <row r="69" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A69" s="48" t="str">
+      <c r="A69" s="47" t="str">
         <f t="shared" si="3"/>
         <v>1020001</v>
       </c>
-      <c r="B69" s="48">
+      <c r="B69" s="47">
         <v>102000</v>
       </c>
-      <c r="C69" s="48">
-        <v>1</v>
-      </c>
-      <c r="D69" s="48" t="s">
+      <c r="C69" s="47">
+        <v>1</v>
+      </c>
+      <c r="D69" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="E69" s="48" t="s">
+      <c r="E69" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="F69" s="48">
-        <v>1</v>
-      </c>
-      <c r="G69" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="H69" s="48">
+      <c r="F69" s="47">
+        <v>1</v>
+      </c>
+      <c r="G69" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H69" s="47">
         <v>2020001</v>
       </c>
-      <c r="I69" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="L69" s="49" t="s">
+      <c r="I69" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69" s="48" t="s">
         <v>137</v>
       </c>
-      <c r="M69" s="48" t="s">
+      <c r="M69" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="N69" s="50">
-        <v>5</v>
-      </c>
-      <c r="O69" s="50">
-        <v>5</v>
-      </c>
-      <c r="Q69" s="47"/>
+      <c r="N69" s="49">
+        <v>5</v>
+      </c>
+      <c r="O69" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q69" s="46"/>
     </row>
     <row r="70" ht="16.5" spans="1:17">
       <c r="A70" s="4" t="str">
@@ -5343,22 +5323,21 @@
       <c r="I70" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L70" s="44" t="s">
+      <c r="L70" s="43" t="s">
         <v>139</v>
       </c>
       <c r="M70" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="N70" s="43">
-        <v>5</v>
-      </c>
-      <c r="O70" s="43">
+      <c r="N70" s="42">
+        <v>5</v>
+      </c>
+      <c r="O70" s="42">
         <v>5</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:17">
-      <c r="A71" s="4" t="str">
-        <f t="shared" si="3"/>
+      <c r="A71" s="50">
         <v>1020003</v>
       </c>
       <c r="B71" s="4">
@@ -5385,65 +5364,63 @@
       <c r="I71" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L71" s="44" t="s">
+      <c r="L71" s="43" t="s">
         <v>141</v>
       </c>
       <c r="M71" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="N71" s="43">
-        <v>5</v>
-      </c>
-      <c r="O71" s="43">
+      <c r="N71" s="42">
+        <v>5</v>
+      </c>
+      <c r="O71" s="42">
         <v>5</v>
       </c>
     </row>
     <row r="72" s="6" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A72" s="51" t="str">
-        <f t="shared" si="3"/>
+      <c r="A72" s="51">
         <v>1020004</v>
       </c>
-      <c r="B72" s="51">
+      <c r="B72" s="52">
         <v>102000</v>
       </c>
-      <c r="C72" s="51">
+      <c r="C72" s="52">
         <v>4</v>
       </c>
-      <c r="D72" s="51" t="s">
+      <c r="D72" s="52" t="s">
         <v>136</v>
       </c>
-      <c r="E72" s="51" t="s">
+      <c r="E72" s="52" t="s">
         <v>143</v>
       </c>
-      <c r="F72" s="51">
-        <v>1</v>
-      </c>
-      <c r="G72" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="H72" s="51">
+      <c r="F72" s="52">
+        <v>1</v>
+      </c>
+      <c r="G72" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="H72" s="52">
         <v>2020002</v>
       </c>
-      <c r="I72" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="L72" s="52">
+      <c r="I72" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72" s="53">
         <v>10200016</v>
       </c>
-      <c r="M72" s="51" t="s">
+      <c r="M72" s="52" t="s">
         <v>144</v>
       </c>
-      <c r="N72" s="53">
-        <v>5</v>
-      </c>
-      <c r="O72" s="53">
-        <v>5</v>
-      </c>
-      <c r="Q72" s="54"/>
+      <c r="N72" s="54">
+        <v>5</v>
+      </c>
+      <c r="O72" s="54">
+        <v>5</v>
+      </c>
+      <c r="Q72" s="55"/>
     </row>
     <row r="73" ht="16.5" spans="1:17">
-      <c r="A73" s="4" t="str">
-        <f t="shared" si="3"/>
+      <c r="A73" s="50">
         <v>1020005</v>
       </c>
       <c r="B73" s="4">
@@ -5470,22 +5447,21 @@
       <c r="I73" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L73" s="44">
+      <c r="L73" s="43">
         <v>10200021</v>
       </c>
       <c r="M73" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="N73" s="43">
-        <v>5</v>
-      </c>
-      <c r="O73" s="43">
+      <c r="N73" s="42">
+        <v>5</v>
+      </c>
+      <c r="O73" s="42">
         <v>5</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:17">
-      <c r="A74" s="4" t="str">
-        <f t="shared" si="3"/>
+      <c r="A74" s="50">
         <v>1038001</v>
       </c>
       <c r="B74" s="4">
@@ -5515,14 +5491,14 @@
       <c r="J74" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="L74" s="44"/>
+      <c r="L74" s="43"/>
       <c r="M74" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="N74" s="43">
-        <v>3</v>
-      </c>
-      <c r="O74" s="43">
+      <c r="N74" s="42">
+        <v>3</v>
+      </c>
+      <c r="O74" s="42">
         <v>5</v>
       </c>
     </row>
@@ -5555,16 +5531,16 @@
       <c r="I75" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L75" s="44">
+      <c r="L75" s="43">
         <v>10380002</v>
       </c>
       <c r="M75" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="N75" s="43">
-        <v>3</v>
-      </c>
-      <c r="O75" s="43">
+      <c r="N75" s="42">
+        <v>3</v>
+      </c>
+      <c r="O75" s="42">
         <v>5</v>
       </c>
     </row>
@@ -5597,16 +5573,16 @@
       <c r="I76" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L76" s="44" t="s">
+      <c r="L76" s="43" t="s">
         <v>152</v>
       </c>
       <c r="M76" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="N76" s="43">
-        <v>3</v>
-      </c>
-      <c r="O76" s="43">
+      <c r="N76" s="42">
+        <v>3</v>
+      </c>
+      <c r="O76" s="42">
         <v>5</v>
       </c>
     </row>
@@ -5639,16 +5615,16 @@
       <c r="I77" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L77" s="44" t="s">
+      <c r="L77" s="43" t="s">
         <v>154</v>
       </c>
       <c r="M77" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="N77" s="43">
-        <v>3</v>
-      </c>
-      <c r="O77" s="43">
+      <c r="N77" s="42">
+        <v>3</v>
+      </c>
+      <c r="O77" s="42">
         <v>5</v>
       </c>
     </row>
@@ -5681,16 +5657,16 @@
       <c r="I78" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L78" s="44" t="s">
+      <c r="L78" s="43" t="s">
         <v>157</v>
       </c>
       <c r="M78" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="N78" s="43">
-        <v>3</v>
-      </c>
-      <c r="O78" s="43">
+      <c r="N78" s="42">
+        <v>3</v>
+      </c>
+      <c r="O78" s="42">
         <v>5</v>
       </c>
     </row>
@@ -5723,16 +5699,16 @@
       <c r="I79" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L79" s="44">
+      <c r="L79" s="43">
         <v>10270003</v>
       </c>
       <c r="M79" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="N79" s="43">
-        <v>3</v>
-      </c>
-      <c r="O79" s="43">
+      <c r="N79" s="42">
+        <v>3</v>
+      </c>
+      <c r="O79" s="42">
         <v>5</v>
       </c>
     </row>
@@ -5765,16 +5741,16 @@
       <c r="I80" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L80" s="44" t="s">
+      <c r="L80" s="43" t="s">
         <v>160</v>
       </c>
       <c r="M80" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="N80" s="43">
-        <v>3</v>
-      </c>
-      <c r="O80" s="43">
+      <c r="N80" s="42">
+        <v>3</v>
+      </c>
+      <c r="O80" s="42">
         <v>5</v>
       </c>
     </row>
@@ -5807,16 +5783,16 @@
       <c r="I81" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L81" s="44" t="s">
+      <c r="L81" s="43" t="s">
         <v>163</v>
       </c>
       <c r="M81" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="N81" s="43">
+      <c r="N81" s="42">
         <v>4</v>
       </c>
-      <c r="O81" s="43">
+      <c r="O81" s="42">
         <v>3</v>
       </c>
     </row>
@@ -5849,16 +5825,16 @@
       <c r="I82" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L82" s="44" t="s">
+      <c r="L82" s="43" t="s">
         <v>166</v>
       </c>
       <c r="M82" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="N82" s="43">
+      <c r="N82" s="42">
         <v>4</v>
       </c>
-      <c r="O82" s="43">
+      <c r="O82" s="42">
         <v>3</v>
       </c>
     </row>
@@ -5891,16 +5867,16 @@
       <c r="I83" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L83" s="44">
+      <c r="L83" s="43">
         <v>10370003</v>
       </c>
       <c r="M83" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="N83" s="43">
+      <c r="N83" s="42">
         <v>4</v>
       </c>
-      <c r="O83" s="43">
+      <c r="O83" s="42">
         <v>3</v>
       </c>
     </row>
@@ -5933,16 +5909,16 @@
       <c r="I84" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L84" s="44" t="s">
+      <c r="L84" s="43" t="s">
         <v>169</v>
       </c>
       <c r="M84" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="N84" s="43">
-        <v>3</v>
-      </c>
-      <c r="O84" s="43">
+      <c r="N84" s="42">
+        <v>3</v>
+      </c>
+      <c r="O84" s="42">
         <v>5</v>
       </c>
     </row>
@@ -5975,16 +5951,16 @@
       <c r="I85" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L85" s="44">
+      <c r="L85" s="43">
         <v>10310008</v>
       </c>
       <c r="M85" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="N85" s="43">
-        <v>3</v>
-      </c>
-      <c r="O85" s="43">
+      <c r="N85" s="42">
+        <v>3</v>
+      </c>
+      <c r="O85" s="42">
         <v>5</v>
       </c>
     </row>
@@ -6017,16 +5993,16 @@
       <c r="I86" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L86" s="44" t="s">
+      <c r="L86" s="43" t="s">
         <v>172</v>
       </c>
       <c r="M86" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="N86" s="43">
-        <v>3</v>
-      </c>
-      <c r="O86" s="43">
+      <c r="N86" s="42">
+        <v>3</v>
+      </c>
+      <c r="O86" s="42">
         <v>5</v>
       </c>
     </row>
@@ -6059,16 +6035,16 @@
       <c r="I87" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L87" s="44" t="s">
+      <c r="L87" s="43" t="s">
         <v>174</v>
       </c>
       <c r="M87" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="N87" s="43">
-        <v>3</v>
-      </c>
-      <c r="O87" s="43">
+      <c r="N87" s="42">
+        <v>3</v>
+      </c>
+      <c r="O87" s="42">
         <v>5</v>
       </c>
     </row>
@@ -6101,16 +6077,16 @@
       <c r="I88" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L88" s="44">
+      <c r="L88" s="43">
         <v>10310003</v>
       </c>
       <c r="M88" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="N88" s="43">
-        <v>3</v>
-      </c>
-      <c r="O88" s="43">
+      <c r="N88" s="42">
+        <v>3</v>
+      </c>
+      <c r="O88" s="42">
         <v>5</v>
       </c>
     </row>
@@ -6143,16 +6119,16 @@
       <c r="I89" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L89" s="44" t="s">
+      <c r="L89" s="43" t="s">
         <v>179</v>
       </c>
       <c r="M89" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="N89" s="43">
-        <v>3</v>
-      </c>
-      <c r="O89" s="43">
+      <c r="N89" s="42">
+        <v>3</v>
+      </c>
+      <c r="O89" s="42">
         <v>5</v>
       </c>
     </row>
@@ -6185,16 +6161,16 @@
       <c r="I90" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L90" s="44" t="s">
+      <c r="L90" s="43" t="s">
         <v>182</v>
       </c>
       <c r="M90" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="N90" s="43">
-        <v>3</v>
-      </c>
-      <c r="O90" s="43">
+      <c r="N90" s="42">
+        <v>3</v>
+      </c>
+      <c r="O90" s="42">
         <v>5</v>
       </c>
     </row>
@@ -6227,16 +6203,16 @@
       <c r="I91" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L91" s="44" t="s">
+      <c r="L91" s="43" t="s">
         <v>184</v>
       </c>
       <c r="M91" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="N91" s="43">
-        <v>3</v>
-      </c>
-      <c r="O91" s="43">
+      <c r="N91" s="42">
+        <v>3</v>
+      </c>
+      <c r="O91" s="42">
         <v>5</v>
       </c>
     </row>
@@ -6269,16 +6245,16 @@
       <c r="I92" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L92" s="44" t="s">
+      <c r="L92" s="43" t="s">
         <v>186</v>
       </c>
       <c r="M92" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="N92" s="43">
-        <v>3</v>
-      </c>
-      <c r="O92" s="43">
+      <c r="N92" s="42">
+        <v>3</v>
+      </c>
+      <c r="O92" s="42">
         <v>5</v>
       </c>
     </row>
@@ -6317,13 +6293,13 @@
       <c r="M93" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="N93" s="43">
-        <v>3</v>
-      </c>
-      <c r="O93" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q93" s="17"/>
+      <c r="N93" s="42">
+        <v>3</v>
+      </c>
+      <c r="O93" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q93" s="16"/>
     </row>
     <row r="94" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A94" s="4" t="str">
@@ -6354,19 +6330,19 @@
       <c r="I94" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L94" s="44">
+      <c r="L94" s="43">
         <v>10390003</v>
       </c>
       <c r="M94" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="N94" s="43">
-        <v>3</v>
-      </c>
-      <c r="O94" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="17"/>
+      <c r="N94" s="42">
+        <v>3</v>
+      </c>
+      <c r="O94" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="16"/>
     </row>
     <row r="95" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A95" s="4" t="str">
@@ -6403,13 +6379,13 @@
       <c r="M95" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="N95" s="43">
-        <v>3</v>
-      </c>
-      <c r="O95" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q95" s="17"/>
+      <c r="N95" s="42">
+        <v>3</v>
+      </c>
+      <c r="O95" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q95" s="16"/>
     </row>
     <row r="96" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A96" s="4" t="str">
@@ -6446,13 +6422,13 @@
       <c r="M96" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="N96" s="43">
+      <c r="N96" s="42">
         <v>6</v>
       </c>
-      <c r="O96" s="43">
+      <c r="O96" s="42">
         <v>6</v>
       </c>
-      <c r="Q96" s="17"/>
+      <c r="Q96" s="16"/>
     </row>
     <row r="97" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A97" s="4" t="str">
@@ -6483,19 +6459,19 @@
       <c r="I97" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L97" s="44">
+      <c r="L97" s="43">
         <v>10160002</v>
       </c>
       <c r="M97" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="N97" s="43">
+      <c r="N97" s="42">
         <v>6</v>
       </c>
-      <c r="O97" s="43">
+      <c r="O97" s="42">
         <v>6</v>
       </c>
-      <c r="Q97" s="17"/>
+      <c r="Q97" s="16"/>
     </row>
     <row r="98" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A98" s="4" t="str">
@@ -6532,13 +6508,13 @@
       <c r="M98" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="N98" s="43">
+      <c r="N98" s="42">
         <v>6</v>
       </c>
-      <c r="O98" s="43">
+      <c r="O98" s="42">
         <v>6</v>
       </c>
-      <c r="Q98" s="17"/>
+      <c r="Q98" s="16"/>
     </row>
     <row r="99" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A99" s="4" t="str">
@@ -6575,13 +6551,13 @@
       <c r="M99" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="N99" s="43">
-        <v>3</v>
-      </c>
-      <c r="O99" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q99" s="17"/>
+      <c r="N99" s="42">
+        <v>3</v>
+      </c>
+      <c r="O99" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q99" s="16"/>
     </row>
     <row r="100" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A100" s="4" t="str">
@@ -6618,13 +6594,13 @@
       <c r="M100" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="N100" s="43">
-        <v>3</v>
-      </c>
-      <c r="O100" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="17"/>
+      <c r="N100" s="42">
+        <v>3</v>
+      </c>
+      <c r="O100" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="16"/>
     </row>
     <row r="101" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A101" s="4" t="str">
@@ -6655,19 +6631,19 @@
       <c r="I101" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L101" s="44">
+      <c r="L101" s="43">
         <v>10150002</v>
       </c>
       <c r="M101" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="N101" s="43">
-        <v>3</v>
-      </c>
-      <c r="O101" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="17"/>
+      <c r="N101" s="42">
+        <v>3</v>
+      </c>
+      <c r="O101" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="16"/>
     </row>
     <row r="102" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A102" s="4" t="str">
@@ -6704,13 +6680,13 @@
       <c r="M102" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="N102" s="43">
-        <v>3</v>
-      </c>
-      <c r="O102" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="17"/>
+      <c r="N102" s="42">
+        <v>3</v>
+      </c>
+      <c r="O102" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="16"/>
     </row>
     <row r="103" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A103" s="4" t="str">
@@ -6741,19 +6717,19 @@
       <c r="I103" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L103" s="44">
+      <c r="L103" s="43">
         <v>10150005</v>
       </c>
       <c r="M103" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="N103" s="43">
-        <v>3</v>
-      </c>
-      <c r="O103" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q103" s="17"/>
+      <c r="N103" s="42">
+        <v>3</v>
+      </c>
+      <c r="O103" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q103" s="16"/>
     </row>
     <row r="104" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A104" s="4" t="str">
@@ -6784,19 +6760,19 @@
       <c r="I104" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L104" s="44">
+      <c r="L104" s="43">
         <v>10150006</v>
       </c>
       <c r="M104" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="N104" s="43">
-        <v>3</v>
-      </c>
-      <c r="O104" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q104" s="17"/>
+      <c r="N104" s="42">
+        <v>3</v>
+      </c>
+      <c r="O104" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q104" s="16"/>
     </row>
     <row r="105" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A105" s="4" t="str">
@@ -6827,19 +6803,19 @@
       <c r="I105" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L105" s="44">
+      <c r="L105" s="43">
         <v>10150007</v>
       </c>
       <c r="M105" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="N105" s="43">
-        <v>3</v>
-      </c>
-      <c r="O105" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q105" s="17"/>
+      <c r="N105" s="42">
+        <v>3</v>
+      </c>
+      <c r="O105" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q105" s="16"/>
     </row>
     <row r="106" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A106" s="4" t="str">
@@ -6870,19 +6846,19 @@
       <c r="I106" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L106" s="44" t="s">
+      <c r="L106" s="43" t="s">
         <v>211</v>
       </c>
       <c r="M106" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="N106" s="43">
+      <c r="N106" s="42">
         <v>6</v>
       </c>
-      <c r="O106" s="43">
+      <c r="O106" s="42">
         <v>6</v>
       </c>
-      <c r="Q106" s="17"/>
+      <c r="Q106" s="16"/>
     </row>
     <row r="107" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A107" s="4" t="str">
@@ -6913,19 +6889,19 @@
       <c r="I107" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L107" s="44" t="s">
+      <c r="L107" s="43" t="s">
         <v>213</v>
       </c>
       <c r="M107" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="N107" s="43">
+      <c r="N107" s="42">
         <v>6</v>
       </c>
-      <c r="O107" s="43">
+      <c r="O107" s="42">
         <v>6</v>
       </c>
-      <c r="Q107" s="17"/>
+      <c r="Q107" s="16"/>
     </row>
     <row r="108" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A108" s="4" t="str">
@@ -6956,19 +6932,19 @@
       <c r="I108" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L108" s="44" t="s">
+      <c r="L108" s="43" t="s">
         <v>214</v>
       </c>
       <c r="M108" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="N108" s="43">
+      <c r="N108" s="42">
         <v>6</v>
       </c>
-      <c r="O108" s="43">
+      <c r="O108" s="42">
         <v>6</v>
       </c>
-      <c r="Q108" s="17"/>
+      <c r="Q108" s="16"/>
     </row>
     <row r="109" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A109" s="4" t="str">
@@ -6999,19 +6975,19 @@
       <c r="I109" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L109" s="44" t="s">
+      <c r="L109" s="43" t="s">
         <v>216</v>
       </c>
       <c r="M109" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="N109" s="43">
+      <c r="N109" s="42">
         <v>6</v>
       </c>
-      <c r="O109" s="43">
+      <c r="O109" s="42">
         <v>6</v>
       </c>
-      <c r="Q109" s="17"/>
+      <c r="Q109" s="16"/>
     </row>
     <row r="110" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A110" s="4" t="str">
@@ -7042,19 +7018,19 @@
       <c r="I110" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L110" s="44" t="s">
+      <c r="L110" s="43" t="s">
         <v>218</v>
       </c>
       <c r="M110" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="N110" s="43">
+      <c r="N110" s="42">
         <v>6</v>
       </c>
-      <c r="O110" s="43">
+      <c r="O110" s="42">
         <v>6</v>
       </c>
-      <c r="Q110" s="17"/>
+      <c r="Q110" s="16"/>
     </row>
     <row r="111" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A111" s="4" t="str">
@@ -7085,19 +7061,19 @@
       <c r="I111" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L111" s="44" t="s">
+      <c r="L111" s="43" t="s">
         <v>220</v>
       </c>
       <c r="M111" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="N111" s="43">
+      <c r="N111" s="42">
         <v>6</v>
       </c>
-      <c r="O111" s="43">
+      <c r="O111" s="42">
         <v>6</v>
       </c>
-      <c r="Q111" s="17"/>
+      <c r="Q111" s="16"/>
     </row>
     <row r="112" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A112" s="4" t="str">
@@ -7128,22 +7104,22 @@
       <c r="I112" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L112" s="44" t="s">
+      <c r="L112" s="43" t="s">
         <v>223</v>
       </c>
       <c r="M112" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="N112" s="43">
+      <c r="N112" s="42">
         <v>6</v>
       </c>
-      <c r="O112" s="43">
+      <c r="O112" s="42">
         <v>6</v>
       </c>
-      <c r="Q112" s="17"/>
+      <c r="Q112" s="16"/>
     </row>
     <row r="113" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A113" s="44">
+      <c r="A113" s="43">
         <v>1051001</v>
       </c>
       <c r="B113" s="4">
@@ -7170,17 +7146,17 @@
       <c r="I113" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L113" s="44"/>
-      <c r="N113" s="43">
+      <c r="L113" s="43"/>
+      <c r="N113" s="42">
         <v>4</v>
       </c>
-      <c r="O113" s="43">
+      <c r="O113" s="42">
         <v>4</v>
       </c>
-      <c r="Q113" s="17"/>
+      <c r="Q113" s="16"/>
     </row>
     <row r="114" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A114" s="44">
+      <c r="A114" s="43">
         <v>1051002</v>
       </c>
       <c r="B114" s="4">
@@ -7207,17 +7183,17 @@
       <c r="I114" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L114" s="44"/>
-      <c r="N114" s="43">
-        <v>5</v>
-      </c>
-      <c r="O114" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q114" s="17"/>
+      <c r="L114" s="43"/>
+      <c r="N114" s="42">
+        <v>5</v>
+      </c>
+      <c r="O114" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q114" s="16"/>
     </row>
     <row r="115" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A115" s="44">
+      <c r="A115" s="43">
         <v>1051003</v>
       </c>
       <c r="B115" s="4">
@@ -7244,17 +7220,17 @@
       <c r="I115" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L115" s="44"/>
-      <c r="N115" s="43">
+      <c r="L115" s="43"/>
+      <c r="N115" s="42">
         <v>6</v>
       </c>
-      <c r="O115" s="43">
+      <c r="O115" s="42">
         <v>6</v>
       </c>
-      <c r="Q115" s="17"/>
+      <c r="Q115" s="16"/>
     </row>
     <row r="116" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A116" s="44">
+      <c r="A116" s="43">
         <v>1051004</v>
       </c>
       <c r="B116" s="4">
@@ -7281,22 +7257,22 @@
       <c r="I116" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L116" s="44">
+      <c r="L116" s="43">
         <v>10510001</v>
       </c>
       <c r="M116" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="N116" s="43">
+      <c r="N116" s="42">
         <v>4</v>
       </c>
-      <c r="O116" s="43">
+      <c r="O116" s="42">
         <v>4</v>
       </c>
-      <c r="Q116" s="17"/>
+      <c r="Q116" s="16"/>
     </row>
     <row r="117" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A117" s="44">
+      <c r="A117" s="43">
         <v>1051005</v>
       </c>
       <c r="B117" s="4">
@@ -7323,22 +7299,22 @@
       <c r="I117" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L117" s="44">
+      <c r="L117" s="43">
         <v>10510002</v>
       </c>
       <c r="M117" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="N117" s="43">
-        <v>5</v>
-      </c>
-      <c r="O117" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q117" s="17"/>
+      <c r="N117" s="42">
+        <v>5</v>
+      </c>
+      <c r="O117" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q117" s="16"/>
     </row>
     <row r="118" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A118" s="44">
+      <c r="A118" s="43">
         <v>1051006</v>
       </c>
       <c r="B118" s="4">
@@ -7365,22 +7341,22 @@
       <c r="I118" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L118" s="44">
+      <c r="L118" s="43">
         <v>10510003</v>
       </c>
       <c r="M118" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="N118" s="43">
+      <c r="N118" s="42">
         <v>6</v>
       </c>
-      <c r="O118" s="43">
+      <c r="O118" s="42">
         <v>6</v>
       </c>
-      <c r="Q118" s="17"/>
+      <c r="Q118" s="16"/>
     </row>
     <row r="119" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A119" s="44">
+      <c r="A119" s="43">
         <v>1051007</v>
       </c>
       <c r="B119" s="4">
@@ -7407,22 +7383,22 @@
       <c r="I119" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L119" s="44">
+      <c r="L119" s="43">
         <v>10510004</v>
       </c>
       <c r="M119" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="N119" s="43">
+      <c r="N119" s="42">
         <v>4</v>
       </c>
-      <c r="O119" s="43">
+      <c r="O119" s="42">
         <v>4</v>
       </c>
-      <c r="Q119" s="17"/>
+      <c r="Q119" s="16"/>
     </row>
     <row r="120" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A120" s="44">
+      <c r="A120" s="43">
         <v>1051008</v>
       </c>
       <c r="B120" s="4">
@@ -7449,22 +7425,22 @@
       <c r="I120" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L120" s="44">
+      <c r="L120" s="43">
         <v>10510005</v>
       </c>
       <c r="M120" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="N120" s="43">
-        <v>5</v>
-      </c>
-      <c r="O120" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q120" s="17"/>
+      <c r="N120" s="42">
+        <v>5</v>
+      </c>
+      <c r="O120" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q120" s="16"/>
     </row>
     <row r="121" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A121" s="44">
+      <c r="A121" s="43">
         <v>1051009</v>
       </c>
       <c r="B121" s="4">
@@ -7491,19 +7467,19 @@
       <c r="I121" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L121" s="44">
+      <c r="L121" s="43">
         <v>10510006</v>
       </c>
       <c r="M121" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="N121" s="43">
+      <c r="N121" s="42">
         <v>6</v>
       </c>
-      <c r="O121" s="43">
+      <c r="O121" s="42">
         <v>6</v>
       </c>
-      <c r="Q121" s="17"/>
+      <c r="Q121" s="16"/>
     </row>
     <row r="122" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A122" s="4" t="str">
@@ -7534,19 +7510,19 @@
       <c r="I122" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L122" s="44" t="s">
+      <c r="L122" s="43" t="s">
         <v>242</v>
       </c>
       <c r="M122" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="N122" s="43">
+      <c r="N122" s="42">
         <v>6</v>
       </c>
-      <c r="O122" s="43">
+      <c r="O122" s="42">
         <v>6</v>
       </c>
-      <c r="Q122" s="17"/>
+      <c r="Q122" s="16"/>
     </row>
     <row r="123" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A123" s="4" t="str">
@@ -7577,19 +7553,19 @@
       <c r="I123" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L123" s="44" t="s">
+      <c r="L123" s="43" t="s">
         <v>244</v>
       </c>
       <c r="M123" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="N123" s="43">
+      <c r="N123" s="42">
         <v>6</v>
       </c>
-      <c r="O123" s="43">
+      <c r="O123" s="42">
         <v>6</v>
       </c>
-      <c r="Q123" s="17"/>
+      <c r="Q123" s="16"/>
     </row>
     <row r="124" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A124" s="4" t="str">
@@ -7620,19 +7596,19 @@
       <c r="I124" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L124" s="44" t="s">
+      <c r="L124" s="43" t="s">
         <v>246</v>
       </c>
       <c r="M124" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="N124" s="43">
+      <c r="N124" s="42">
         <v>6</v>
       </c>
-      <c r="O124" s="43">
+      <c r="O124" s="42">
         <v>6</v>
       </c>
-      <c r="Q124" s="17"/>
+      <c r="Q124" s="16"/>
     </row>
     <row r="125" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A125" s="4" t="str">
@@ -7663,19 +7639,19 @@
       <c r="I125" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L125" s="44" t="s">
+      <c r="L125" s="43" t="s">
         <v>248</v>
       </c>
       <c r="M125" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="N125" s="43">
+      <c r="N125" s="42">
         <v>6</v>
       </c>
-      <c r="O125" s="43">
+      <c r="O125" s="42">
         <v>6</v>
       </c>
-      <c r="Q125" s="17"/>
+      <c r="Q125" s="16"/>
     </row>
     <row r="126" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A126" s="4" t="str">
@@ -7706,19 +7682,19 @@
       <c r="I126" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L126" s="44" t="s">
+      <c r="L126" s="43" t="s">
         <v>250</v>
       </c>
       <c r="M126" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="N126" s="43">
+      <c r="N126" s="42">
         <v>6</v>
       </c>
-      <c r="O126" s="43">
+      <c r="O126" s="42">
         <v>6</v>
       </c>
-      <c r="Q126" s="17"/>
+      <c r="Q126" s="16"/>
     </row>
     <row r="127" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A127" s="4" t="str">
@@ -7749,19 +7725,19 @@
       <c r="I127" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L127" s="44" t="s">
+      <c r="L127" s="43" t="s">
         <v>252</v>
       </c>
       <c r="M127" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="N127" s="43">
+      <c r="N127" s="42">
         <v>6</v>
       </c>
-      <c r="O127" s="43">
+      <c r="O127" s="42">
         <v>6</v>
       </c>
-      <c r="Q127" s="17"/>
+      <c r="Q127" s="16"/>
     </row>
     <row r="128" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A128" s="4" t="str">
@@ -7792,19 +7768,19 @@
       <c r="I128" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L128" s="44" t="s">
+      <c r="L128" s="43" t="s">
         <v>253</v>
       </c>
       <c r="M128" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="N128" s="43">
+      <c r="N128" s="42">
         <v>6</v>
       </c>
-      <c r="O128" s="43">
+      <c r="O128" s="42">
         <v>6</v>
       </c>
-      <c r="Q128" s="17"/>
+      <c r="Q128" s="16"/>
     </row>
     <row r="129" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A129" s="4" t="str">
@@ -7835,19 +7811,19 @@
       <c r="I129" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L129" s="44" t="s">
+      <c r="L129" s="43" t="s">
         <v>255</v>
       </c>
       <c r="M129" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="N129" s="43">
-        <v>5</v>
-      </c>
-      <c r="O129" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q129" s="17"/>
+      <c r="N129" s="42">
+        <v>5</v>
+      </c>
+      <c r="O129" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q129" s="16"/>
     </row>
     <row r="130" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A130" s="4" t="str">
@@ -7878,19 +7854,19 @@
       <c r="I130" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L130" s="44" t="s">
+      <c r="L130" s="43" t="s">
         <v>257</v>
       </c>
       <c r="M130" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="N130" s="43">
-        <v>5</v>
-      </c>
-      <c r="O130" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q130" s="17"/>
+      <c r="N130" s="42">
+        <v>5</v>
+      </c>
+      <c r="O130" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q130" s="16"/>
     </row>
     <row r="131" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A131" s="4" t="str">
@@ -7921,19 +7897,19 @@
       <c r="I131" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L131" s="44" t="s">
+      <c r="L131" s="43" t="s">
         <v>260</v>
       </c>
       <c r="M131" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="N131" s="43">
+      <c r="N131" s="42">
         <v>6</v>
       </c>
-      <c r="O131" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q131" s="17"/>
+      <c r="O131" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q131" s="16"/>
     </row>
     <row r="132" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A132" s="4" t="str">
@@ -7964,19 +7940,19 @@
       <c r="I132" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L132" s="44" t="s">
+      <c r="L132" s="43" t="s">
         <v>262</v>
       </c>
       <c r="M132" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="N132" s="43">
+      <c r="N132" s="42">
         <v>6</v>
       </c>
-      <c r="O132" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q132" s="17"/>
+      <c r="O132" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q132" s="16"/>
     </row>
     <row r="133" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A133" s="4" t="str">
@@ -8007,19 +7983,19 @@
       <c r="I133" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L133" s="44" t="s">
+      <c r="L133" s="43" t="s">
         <v>264</v>
       </c>
       <c r="M133" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="N133" s="43">
+      <c r="N133" s="42">
         <v>6</v>
       </c>
-      <c r="O133" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q133" s="17"/>
+      <c r="O133" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q133" s="16"/>
     </row>
     <row r="134" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A134" s="4" t="str">
@@ -8050,19 +8026,19 @@
       <c r="I134" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L134" s="44">
+      <c r="L134" s="43">
         <v>10580003</v>
       </c>
       <c r="M134" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="N134" s="43">
+      <c r="N134" s="42">
         <v>7</v>
       </c>
-      <c r="O134" s="43">
+      <c r="O134" s="42">
         <v>7</v>
       </c>
-      <c r="Q134" s="17"/>
+      <c r="Q134" s="16"/>
     </row>
     <row r="135" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A135" s="4" t="str">
@@ -8093,19 +8069,19 @@
       <c r="I135" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L135" s="44">
+      <c r="L135" s="43">
         <v>10580002</v>
       </c>
       <c r="M135" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="N135" s="43">
+      <c r="N135" s="42">
         <v>7</v>
       </c>
-      <c r="O135" s="43">
+      <c r="O135" s="42">
         <v>7</v>
       </c>
-      <c r="Q135" s="17"/>
+      <c r="Q135" s="16"/>
     </row>
     <row r="136" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A136" s="4" t="str">
@@ -8136,22 +8112,22 @@
       <c r="I136" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L136" s="44" t="s">
+      <c r="L136" s="43" t="s">
         <v>268</v>
       </c>
       <c r="M136" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="N136" s="43">
+      <c r="N136" s="42">
         <v>7</v>
       </c>
-      <c r="O136" s="43">
+      <c r="O136" s="42">
         <v>7</v>
       </c>
-      <c r="Q136" s="17"/>
+      <c r="Q136" s="16"/>
     </row>
     <row r="137" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A137" s="44">
+      <c r="A137" s="43">
         <v>1055001</v>
       </c>
       <c r="B137" s="4">
@@ -8178,22 +8154,22 @@
       <c r="I137" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L137" s="44">
+      <c r="L137" s="43">
         <v>10550002</v>
       </c>
       <c r="M137" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="N137" s="43">
-        <v>3</v>
-      </c>
-      <c r="O137" s="43">
+      <c r="N137" s="42">
+        <v>3</v>
+      </c>
+      <c r="O137" s="42">
         <v>4</v>
       </c>
-      <c r="Q137" s="17"/>
+      <c r="Q137" s="16"/>
     </row>
     <row r="138" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A138" s="44">
+      <c r="A138" s="43">
         <v>1055002</v>
       </c>
       <c r="B138" s="4">
@@ -8220,22 +8196,22 @@
       <c r="I138" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L138" s="44">
+      <c r="L138" s="43">
         <v>10550001</v>
       </c>
       <c r="M138" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="N138" s="43">
-        <v>3</v>
-      </c>
-      <c r="O138" s="43">
+      <c r="N138" s="42">
+        <v>3</v>
+      </c>
+      <c r="O138" s="42">
         <v>4</v>
       </c>
-      <c r="Q138" s="17"/>
+      <c r="Q138" s="16"/>
     </row>
     <row r="139" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A139" s="44">
+      <c r="A139" s="43">
         <v>1048001</v>
       </c>
       <c r="B139" s="4">
@@ -8247,16 +8223,16 @@
       <c r="D139" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="E139" s="55" t="s">
+      <c r="E139" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="F139" s="16">
+      <c r="F139" s="15">
         <v>1</v>
       </c>
       <c r="G139" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H139" s="56">
+      <c r="H139" s="57">
         <v>2048001</v>
       </c>
       <c r="I139" s="4" t="s">
@@ -8268,16 +8244,16 @@
       <c r="M139" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="N139" s="43">
+      <c r="N139" s="42">
         <v>6</v>
       </c>
-      <c r="O139" s="43">
+      <c r="O139" s="42">
         <v>6</v>
       </c>
-      <c r="Q139" s="17"/>
+      <c r="Q139" s="16"/>
     </row>
     <row r="140" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A140" s="44">
+      <c r="A140" s="43">
         <v>1048002</v>
       </c>
       <c r="B140" s="4">
@@ -8289,37 +8265,37 @@
       <c r="D140" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="E140" s="55" t="s">
+      <c r="E140" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="F140" s="16">
+      <c r="F140" s="15">
         <v>1</v>
       </c>
       <c r="G140" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H140" s="56">
+      <c r="H140" s="57">
         <v>2048001</v>
       </c>
       <c r="I140" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L140" s="44">
+      <c r="L140" s="43">
         <v>10480002</v>
       </c>
       <c r="M140" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="N140" s="43">
+      <c r="N140" s="42">
         <v>6</v>
       </c>
-      <c r="O140" s="43">
+      <c r="O140" s="42">
         <v>6</v>
       </c>
-      <c r="Q140" s="17"/>
+      <c r="Q140" s="16"/>
     </row>
     <row r="141" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A141" s="44">
+      <c r="A141" s="43">
         <v>1048003</v>
       </c>
       <c r="B141" s="4">
@@ -8334,34 +8310,34 @@
       <c r="E141" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F141" s="16">
+      <c r="F141" s="15">
         <v>1</v>
       </c>
       <c r="G141" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H141" s="56">
+      <c r="H141" s="57">
         <v>2048001</v>
       </c>
       <c r="I141" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L141" s="44" t="s">
+      <c r="L141" s="43" t="s">
         <v>274</v>
       </c>
       <c r="M141" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="N141" s="43">
+      <c r="N141" s="42">
         <v>6</v>
       </c>
-      <c r="O141" s="43">
+      <c r="O141" s="42">
         <v>6</v>
       </c>
-      <c r="Q141" s="17"/>
+      <c r="Q141" s="16"/>
     </row>
     <row r="142" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A142" s="44">
+      <c r="A142" s="43">
         <v>1055011</v>
       </c>
       <c r="B142" s="4">
@@ -8388,22 +8364,22 @@
       <c r="I142" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L142" s="44">
+      <c r="L142" s="43">
         <v>10550102</v>
       </c>
       <c r="M142" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="N142" s="43">
-        <v>3</v>
-      </c>
-      <c r="O142" s="43">
+      <c r="N142" s="42">
+        <v>3</v>
+      </c>
+      <c r="O142" s="42">
         <v>4</v>
       </c>
-      <c r="Q142" s="17"/>
+      <c r="Q142" s="16"/>
     </row>
     <row r="143" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A143" s="44">
+      <c r="A143" s="43">
         <v>1055012</v>
       </c>
       <c r="B143" s="4">
@@ -8430,22 +8406,22 @@
       <c r="I143" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L143" s="44">
+      <c r="L143" s="43">
         <v>10550101</v>
       </c>
       <c r="M143" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="N143" s="43">
-        <v>3</v>
-      </c>
-      <c r="O143" s="43">
+      <c r="N143" s="42">
+        <v>3</v>
+      </c>
+      <c r="O143" s="42">
         <v>4</v>
       </c>
-      <c r="Q143" s="17"/>
+      <c r="Q143" s="16"/>
     </row>
     <row r="144" ht="16.5" spans="1:17">
-      <c r="A144" s="44">
+      <c r="A144" s="43">
         <v>1055013</v>
       </c>
       <c r="B144" s="4">
@@ -8457,7 +8433,7 @@
       <c r="D144" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="E144" s="46" t="s">
+      <c r="E144" s="45" t="s">
         <v>276</v>
       </c>
       <c r="F144" s="4">
@@ -8474,146 +8450,146 @@
       </c>
       <c r="J144" s="4"/>
       <c r="K144" s="4"/>
-      <c r="L144" s="44">
+      <c r="L144" s="43">
         <v>10550103</v>
       </c>
       <c r="M144" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="N144" s="43">
-        <v>3</v>
-      </c>
-      <c r="O144" s="43">
+      <c r="N144" s="42">
+        <v>3</v>
+      </c>
+      <c r="O144" s="42">
         <v>4</v>
       </c>
     </row>
-    <row r="145" s="7" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A145" s="57">
+    <row r="145" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A145" s="43">
         <v>1055021</v>
       </c>
-      <c r="B145" s="7">
+      <c r="B145" s="4">
         <v>105502</v>
       </c>
-      <c r="C145" s="7">
-        <v>1</v>
-      </c>
-      <c r="D145" s="7" t="s">
+      <c r="C145" s="4">
+        <v>1</v>
+      </c>
+      <c r="D145" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="E145" s="7" t="s">
+      <c r="E145" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F145" s="7">
-        <v>1</v>
-      </c>
-      <c r="G145" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H145" s="7">
+      <c r="F145" s="4">
+        <v>1</v>
+      </c>
+      <c r="G145" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H145" s="4">
         <v>2055021</v>
       </c>
-      <c r="I145" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L145" s="57">
+      <c r="I145" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L145" s="43">
         <v>10550202</v>
       </c>
-      <c r="M145" s="7" t="s">
+      <c r="M145" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="N145" s="58">
-        <v>3</v>
-      </c>
-      <c r="O145" s="58">
+      <c r="N145" s="42">
+        <v>3</v>
+      </c>
+      <c r="O145" s="42">
         <v>4</v>
       </c>
-      <c r="Q145" s="59"/>
-    </row>
-    <row r="146" s="7" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A146" s="57">
+      <c r="Q145" s="16"/>
+    </row>
+    <row r="146" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A146" s="43">
         <v>1055022</v>
       </c>
-      <c r="B146" s="7">
+      <c r="B146" s="4">
         <v>105502</v>
       </c>
-      <c r="C146" s="7">
+      <c r="C146" s="4">
         <v>2</v>
       </c>
-      <c r="D146" s="7" t="s">
+      <c r="D146" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="E146" s="7" t="s">
+      <c r="E146" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F146" s="7">
-        <v>1</v>
-      </c>
-      <c r="G146" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H146" s="7">
+      <c r="F146" s="4">
+        <v>1</v>
+      </c>
+      <c r="G146" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H146" s="4">
         <v>2055021</v>
       </c>
-      <c r="I146" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L146" s="57">
+      <c r="I146" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L146" s="43">
         <v>10550201</v>
       </c>
-      <c r="M146" s="7" t="s">
+      <c r="M146" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="N146" s="58">
-        <v>3</v>
-      </c>
-      <c r="O146" s="58">
+      <c r="N146" s="42">
+        <v>3</v>
+      </c>
+      <c r="O146" s="42">
         <v>4</v>
       </c>
-      <c r="Q146" s="59"/>
+      <c r="Q146" s="16"/>
     </row>
     <row r="147" ht="16.5" spans="1:17">
-      <c r="A147" s="57">
+      <c r="A147" s="43">
         <v>1055023</v>
       </c>
-      <c r="B147" s="7">
+      <c r="B147" s="4">
         <v>105502</v>
       </c>
-      <c r="C147" s="7">
-        <v>3</v>
-      </c>
-      <c r="D147" s="7" t="s">
+      <c r="C147" s="4">
+        <v>3</v>
+      </c>
+      <c r="D147" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="E147" s="7" t="s">
+      <c r="E147" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="F147" s="7">
-        <v>1</v>
-      </c>
-      <c r="G147" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H147" s="7">
+      <c r="F147" s="4">
+        <v>1</v>
+      </c>
+      <c r="G147" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H147" s="4">
         <v>2055021</v>
       </c>
-      <c r="I147" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L147" s="57">
+      <c r="I147" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L147" s="43">
         <v>10550203</v>
       </c>
-      <c r="M147" s="7" t="s">
+      <c r="M147" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="N147" s="58">
-        <v>3</v>
-      </c>
-      <c r="O147" s="58">
+      <c r="N147" s="42">
+        <v>3</v>
+      </c>
+      <c r="O147" s="42">
         <v>4</v>
       </c>
     </row>
     <row r="148" s="4" customFormat="1" ht="15" customHeight="1" spans="1:17">
-      <c r="A148" s="44">
+      <c r="A148" s="43">
         <v>1041001</v>
       </c>
       <c r="B148" s="4">
@@ -8631,31 +8607,31 @@
       <c r="F148" s="4">
         <v>1</v>
       </c>
-      <c r="G148" s="60" t="s">
-        <v>23</v>
-      </c>
-      <c r="H148" s="56">
+      <c r="G148" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="H148" s="57">
         <v>2041001</v>
       </c>
       <c r="I148" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L148" s="44" t="s">
+      <c r="L148" s="43" t="s">
         <v>282</v>
       </c>
       <c r="M148" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="N148" s="61">
-        <v>3</v>
-      </c>
-      <c r="O148" s="61">
-        <v>5</v>
-      </c>
-      <c r="Q148" s="17"/>
+      <c r="N148" s="59">
+        <v>3</v>
+      </c>
+      <c r="O148" s="59">
+        <v>5</v>
+      </c>
+      <c r="Q148" s="16"/>
     </row>
     <row r="149" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A149" s="44">
+      <c r="A149" s="43">
         <v>1041002</v>
       </c>
       <c r="B149" s="4">
@@ -8667,37 +8643,37 @@
       <c r="D149" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="E149" s="62" t="s">
+      <c r="E149" s="60" t="s">
         <v>55</v>
       </c>
-      <c r="F149" s="63">
-        <v>1</v>
-      </c>
-      <c r="G149" s="60" t="s">
-        <v>23</v>
-      </c>
-      <c r="H149" s="56">
+      <c r="F149" s="61">
+        <v>1</v>
+      </c>
+      <c r="G149" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="H149" s="57">
         <v>2041001</v>
       </c>
       <c r="I149" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L149" s="44">
+      <c r="L149" s="43">
         <v>10410002</v>
       </c>
       <c r="M149" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="N149" s="61">
-        <v>3</v>
-      </c>
-      <c r="O149" s="61">
-        <v>5</v>
-      </c>
-      <c r="Q149" s="17"/>
+      <c r="N149" s="59">
+        <v>3</v>
+      </c>
+      <c r="O149" s="59">
+        <v>5</v>
+      </c>
+      <c r="Q149" s="16"/>
     </row>
     <row r="150" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A150" s="44">
+      <c r="A150" s="43">
         <v>1041003</v>
       </c>
       <c r="B150" s="4">
@@ -8709,37 +8685,37 @@
       <c r="D150" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="E150" s="62" t="s">
+      <c r="E150" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="F150" s="63">
-        <v>1</v>
-      </c>
-      <c r="G150" s="60" t="s">
-        <v>23</v>
-      </c>
-      <c r="H150" s="56">
+      <c r="F150" s="61">
+        <v>1</v>
+      </c>
+      <c r="G150" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="H150" s="57">
         <v>2041001</v>
       </c>
-      <c r="I150" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="L150" s="44" t="s">
+      <c r="I150" s="58" t="s">
+        <v>24</v>
+      </c>
+      <c r="L150" s="43" t="s">
         <v>285</v>
       </c>
       <c r="M150" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="N150" s="61">
-        <v>3</v>
-      </c>
-      <c r="O150" s="61">
-        <v>5</v>
-      </c>
-      <c r="Q150" s="17"/>
+      <c r="N150" s="59">
+        <v>3</v>
+      </c>
+      <c r="O150" s="59">
+        <v>5</v>
+      </c>
+      <c r="Q150" s="16"/>
     </row>
     <row r="151" s="4" customFormat="1" ht="15" customHeight="1" spans="1:17">
-      <c r="A151" s="44">
+      <c r="A151" s="43">
         <v>1042001</v>
       </c>
       <c r="B151" s="4">
@@ -8757,31 +8733,31 @@
       <c r="F151" s="4">
         <v>1</v>
       </c>
-      <c r="G151" s="60" t="s">
-        <v>23</v>
-      </c>
-      <c r="H151" s="56">
+      <c r="G151" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="H151" s="57">
         <v>2042001</v>
       </c>
       <c r="I151" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L151" s="44" t="s">
+      <c r="L151" s="43" t="s">
         <v>288</v>
       </c>
       <c r="M151" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="N151" s="61">
-        <v>3</v>
-      </c>
-      <c r="O151" s="61">
-        <v>5</v>
-      </c>
-      <c r="Q151" s="17"/>
+      <c r="N151" s="59">
+        <v>3</v>
+      </c>
+      <c r="O151" s="59">
+        <v>5</v>
+      </c>
+      <c r="Q151" s="16"/>
     </row>
     <row r="152" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A152" s="44">
+      <c r="A152" s="43">
         <v>1042002</v>
       </c>
       <c r="B152" s="4">
@@ -8793,37 +8769,37 @@
       <c r="D152" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="E152" s="62" t="s">
+      <c r="E152" s="60" t="s">
         <v>55</v>
       </c>
-      <c r="F152" s="63">
-        <v>1</v>
-      </c>
-      <c r="G152" s="60" t="s">
-        <v>23</v>
-      </c>
-      <c r="H152" s="56">
+      <c r="F152" s="61">
+        <v>1</v>
+      </c>
+      <c r="G152" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="H152" s="57">
         <v>2042001</v>
       </c>
       <c r="I152" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L152" s="44">
+      <c r="L152" s="43">
         <v>10420002</v>
       </c>
       <c r="M152" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="N152" s="61">
-        <v>3</v>
-      </c>
-      <c r="O152" s="61">
-        <v>5</v>
-      </c>
-      <c r="Q152" s="9"/>
+      <c r="N152" s="59">
+        <v>3</v>
+      </c>
+      <c r="O152" s="59">
+        <v>5</v>
+      </c>
+      <c r="Q152" s="8"/>
     </row>
     <row r="153" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A153" s="44">
+      <c r="A153" s="43">
         <v>1042003</v>
       </c>
       <c r="B153" s="4">
@@ -8835,34 +8811,34 @@
       <c r="D153" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="E153" s="62" t="s">
+      <c r="E153" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="F153" s="63">
-        <v>1</v>
-      </c>
-      <c r="G153" s="60" t="s">
-        <v>23</v>
-      </c>
-      <c r="H153" s="56">
+      <c r="F153" s="61">
+        <v>1</v>
+      </c>
+      <c r="G153" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="H153" s="57">
         <v>2042001</v>
       </c>
-      <c r="I153" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="L153" s="44" t="s">
+      <c r="I153" s="58" t="s">
+        <v>24</v>
+      </c>
+      <c r="L153" s="43" t="s">
         <v>289</v>
       </c>
       <c r="M153" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="N153" s="61">
-        <v>3</v>
-      </c>
-      <c r="O153" s="61">
-        <v>5</v>
-      </c>
-      <c r="Q153" s="9"/>
+      <c r="N153" s="59">
+        <v>3</v>
+      </c>
+      <c r="O153" s="59">
+        <v>5</v>
+      </c>
+      <c r="Q153" s="8"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:L2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="289">
   <si>
     <t>id</t>
   </si>
@@ -893,13 +893,10 @@
     <t>麻将胡了2</t>
   </si>
   <si>
-    <t>10530001|10530004|10530005</t>
+    <t>10530001|10530004</t>
   </si>
   <si>
     <t>概率出现3个以下SCATTER+概率出金色图标+异形位置改为不中奖图案</t>
-  </si>
-  <si>
-    <t>10530002|10530005</t>
   </si>
   <si>
     <t>概率改出3个scatter+异形位置改为不中奖图案</t>
@@ -1179,12 +1176,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1714,7 +1711,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1823,16 +1820,10 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -5337,7 +5328,7 @@
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:17">
-      <c r="A71" s="50">
+      <c r="A71" s="43">
         <v>1020003</v>
       </c>
       <c r="B71" s="4">
@@ -5378,49 +5369,49 @@
       </c>
     </row>
     <row r="72" s="6" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A72" s="51">
+      <c r="A72" s="50">
         <v>1020004</v>
       </c>
-      <c r="B72" s="52">
+      <c r="B72" s="51">
         <v>102000</v>
       </c>
-      <c r="C72" s="52">
+      <c r="C72" s="51">
         <v>4</v>
       </c>
-      <c r="D72" s="52" t="s">
+      <c r="D72" s="51" t="s">
         <v>136</v>
       </c>
-      <c r="E72" s="52" t="s">
+      <c r="E72" s="51" t="s">
         <v>143</v>
       </c>
-      <c r="F72" s="52">
-        <v>1</v>
-      </c>
-      <c r="G72" s="52" t="s">
-        <v>23</v>
-      </c>
-      <c r="H72" s="52">
+      <c r="F72" s="51">
+        <v>1</v>
+      </c>
+      <c r="G72" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="H72" s="51">
         <v>2020002</v>
       </c>
-      <c r="I72" s="52" t="s">
-        <v>24</v>
-      </c>
-      <c r="L72" s="53">
+      <c r="I72" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72" s="50">
         <v>10200016</v>
       </c>
-      <c r="M72" s="52" t="s">
+      <c r="M72" s="51" t="s">
         <v>144</v>
       </c>
-      <c r="N72" s="54">
-        <v>5</v>
-      </c>
-      <c r="O72" s="54">
-        <v>5</v>
-      </c>
-      <c r="Q72" s="55"/>
+      <c r="N72" s="52">
+        <v>5</v>
+      </c>
+      <c r="O72" s="52">
+        <v>5</v>
+      </c>
+      <c r="Q72" s="53"/>
     </row>
     <row r="73" ht="16.5" spans="1:17">
-      <c r="A73" s="50">
+      <c r="A73" s="43">
         <v>1020005</v>
       </c>
       <c r="B73" s="4">
@@ -5461,7 +5452,7 @@
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:17">
-      <c r="A74" s="50">
+      <c r="A74" s="43">
         <v>1038001</v>
       </c>
       <c r="B74" s="4">
@@ -7854,11 +7845,11 @@
       <c r="I130" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L130" s="43" t="s">
+      <c r="L130" s="43">
+        <v>10530002</v>
+      </c>
+      <c r="M130" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="M130" s="4" t="s">
-        <v>258</v>
       </c>
       <c r="N130" s="42">
         <v>5</v>
@@ -7880,7 +7871,7 @@
         <v>1</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E131" s="4" t="s">
         <v>22</v>
@@ -7898,10 +7889,10 @@
         <v>24</v>
       </c>
       <c r="L131" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="M131" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="M131" s="4" t="s">
-        <v>261</v>
       </c>
       <c r="N131" s="42">
         <v>6</v>
@@ -7923,7 +7914,7 @@
         <v>2</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E132" s="4" t="s">
         <v>55</v>
@@ -7941,10 +7932,10 @@
         <v>24</v>
       </c>
       <c r="L132" s="43" t="s">
+        <v>261</v>
+      </c>
+      <c r="M132" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="M132" s="4" t="s">
-        <v>263</v>
       </c>
       <c r="N132" s="42">
         <v>6</v>
@@ -7966,7 +7957,7 @@
         <v>3</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>81</v>
@@ -7984,10 +7975,10 @@
         <v>24</v>
       </c>
       <c r="L133" s="43" t="s">
+        <v>263</v>
+      </c>
+      <c r="M133" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="M133" s="4" t="s">
-        <v>265</v>
       </c>
       <c r="N133" s="42">
         <v>6</v>
@@ -8009,7 +8000,7 @@
         <v>1</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>22</v>
@@ -8030,7 +8021,7 @@
         <v>10580003</v>
       </c>
       <c r="M134" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N134" s="42">
         <v>7</v>
@@ -8052,7 +8043,7 @@
         <v>2</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>55</v>
@@ -8095,7 +8086,7 @@
         <v>3</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E136" s="4" t="s">
         <v>81</v>
@@ -8113,10 +8104,10 @@
         <v>24</v>
       </c>
       <c r="L136" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="M136" s="4" t="s">
         <v>268</v>
-      </c>
-      <c r="M136" s="4" t="s">
-        <v>269</v>
       </c>
       <c r="N136" s="42">
         <v>7</v>
@@ -8137,7 +8128,7 @@
         <v>1</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E137" s="4" t="s">
         <v>22</v>
@@ -8179,7 +8170,7 @@
         <v>2</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E138" s="4" t="s">
         <v>81</v>
@@ -8221,28 +8212,28 @@
         <v>1</v>
       </c>
       <c r="D139" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E139" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="F139" s="15">
+        <v>1</v>
+      </c>
+      <c r="G139" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H139" s="55">
+        <v>2048001</v>
+      </c>
+      <c r="I139" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L139" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="E139" s="56" t="s">
-        <v>22</v>
-      </c>
-      <c r="F139" s="15">
-        <v>1</v>
-      </c>
-      <c r="G139" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H139" s="57">
-        <v>2048001</v>
-      </c>
-      <c r="I139" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L139" s="4" t="s">
+      <c r="M139" s="4" t="s">
         <v>272</v>
-      </c>
-      <c r="M139" s="4" t="s">
-        <v>273</v>
       </c>
       <c r="N139" s="42">
         <v>6</v>
@@ -8263,9 +8254,9 @@
         <v>2</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="E140" s="56" t="s">
+        <v>270</v>
+      </c>
+      <c r="E140" s="54" t="s">
         <v>55</v>
       </c>
       <c r="F140" s="15">
@@ -8274,7 +8265,7 @@
       <c r="G140" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H140" s="57">
+      <c r="H140" s="55">
         <v>2048001</v>
       </c>
       <c r="I140" s="4" t="s">
@@ -8305,7 +8296,7 @@
         <v>3</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>81</v>
@@ -8316,14 +8307,14 @@
       <c r="G141" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H141" s="57">
+      <c r="H141" s="55">
         <v>2048001</v>
       </c>
       <c r="I141" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L141" s="43" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M141" s="4" t="s">
         <v>196</v>
@@ -8347,7 +8338,7 @@
         <v>1</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E142" s="4" t="s">
         <v>22</v>
@@ -8389,7 +8380,7 @@
         <v>2</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E143" s="4" t="s">
         <v>81</v>
@@ -8431,10 +8422,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="E144" s="45" t="s">
         <v>275</v>
-      </c>
-      <c r="E144" s="45" t="s">
-        <v>276</v>
       </c>
       <c r="F144" s="4">
         <v>1</v>
@@ -8454,7 +8445,7 @@
         <v>10550103</v>
       </c>
       <c r="M144" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N144" s="42">
         <v>3</v>
@@ -8474,7 +8465,7 @@
         <v>1</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>22</v>
@@ -8516,7 +8507,7 @@
         <v>2</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>81</v>
@@ -8558,10 +8549,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="E147" s="4" t="s">
         <v>278</v>
-      </c>
-      <c r="E147" s="4" t="s">
-        <v>279</v>
       </c>
       <c r="F147" s="4">
         <v>1</v>
@@ -8579,7 +8570,7 @@
         <v>10550203</v>
       </c>
       <c r="M147" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N147" s="42">
         <v>3</v>
@@ -8599,7 +8590,7 @@
         <v>1</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>22</v>
@@ -8607,25 +8598,25 @@
       <c r="F148" s="4">
         <v>1</v>
       </c>
-      <c r="G148" s="58" t="s">
-        <v>23</v>
-      </c>
-      <c r="H148" s="57">
+      <c r="G148" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="H148" s="55">
         <v>2041001</v>
       </c>
       <c r="I148" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L148" s="43" t="s">
+        <v>281</v>
+      </c>
+      <c r="M148" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="M148" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="N148" s="59">
-        <v>3</v>
-      </c>
-      <c r="O148" s="59">
+      <c r="N148" s="57">
+        <v>3</v>
+      </c>
+      <c r="O148" s="57">
         <v>5</v>
       </c>
       <c r="Q148" s="16"/>
@@ -8641,18 +8632,18 @@
         <v>2</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="E149" s="60" t="s">
+        <v>280</v>
+      </c>
+      <c r="E149" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="F149" s="61">
-        <v>1</v>
-      </c>
-      <c r="G149" s="58" t="s">
-        <v>23</v>
-      </c>
-      <c r="H149" s="57">
+      <c r="F149" s="59">
+        <v>1</v>
+      </c>
+      <c r="G149" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="H149" s="55">
         <v>2041001</v>
       </c>
       <c r="I149" s="4" t="s">
@@ -8662,12 +8653,12 @@
         <v>10410002</v>
       </c>
       <c r="M149" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="N149" s="59">
-        <v>3</v>
-      </c>
-      <c r="O149" s="59">
+        <v>283</v>
+      </c>
+      <c r="N149" s="57">
+        <v>3</v>
+      </c>
+      <c r="O149" s="57">
         <v>5</v>
       </c>
       <c r="Q149" s="16"/>
@@ -8683,33 +8674,33 @@
         <v>3</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="E150" s="60" t="s">
+        <v>280</v>
+      </c>
+      <c r="E150" s="58" t="s">
         <v>81</v>
       </c>
-      <c r="F150" s="61">
-        <v>1</v>
-      </c>
-      <c r="G150" s="58" t="s">
-        <v>23</v>
-      </c>
-      <c r="H150" s="57">
+      <c r="F150" s="59">
+        <v>1</v>
+      </c>
+      <c r="G150" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="H150" s="55">
         <v>2041001</v>
       </c>
-      <c r="I150" s="58" t="s">
+      <c r="I150" s="56" t="s">
         <v>24</v>
       </c>
       <c r="L150" s="43" t="s">
+        <v>284</v>
+      </c>
+      <c r="M150" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="M150" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="N150" s="59">
-        <v>3</v>
-      </c>
-      <c r="O150" s="59">
+      <c r="N150" s="57">
+        <v>3</v>
+      </c>
+      <c r="O150" s="57">
         <v>5</v>
       </c>
       <c r="Q150" s="16"/>
@@ -8725,7 +8716,7 @@
         <v>1</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E151" s="4" t="s">
         <v>22</v>
@@ -8733,25 +8724,25 @@
       <c r="F151" s="4">
         <v>1</v>
       </c>
-      <c r="G151" s="58" t="s">
-        <v>23</v>
-      </c>
-      <c r="H151" s="57">
+      <c r="G151" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="H151" s="55">
         <v>2042001</v>
       </c>
       <c r="I151" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L151" s="43" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M151" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="N151" s="59">
-        <v>3</v>
-      </c>
-      <c r="O151" s="59">
+        <v>282</v>
+      </c>
+      <c r="N151" s="57">
+        <v>3</v>
+      </c>
+      <c r="O151" s="57">
         <v>5</v>
       </c>
       <c r="Q151" s="16"/>
@@ -8767,18 +8758,18 @@
         <v>2</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="E152" s="60" t="s">
+        <v>286</v>
+      </c>
+      <c r="E152" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="F152" s="61">
-        <v>1</v>
-      </c>
-      <c r="G152" s="58" t="s">
-        <v>23</v>
-      </c>
-      <c r="H152" s="57">
+      <c r="F152" s="59">
+        <v>1</v>
+      </c>
+      <c r="G152" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="H152" s="55">
         <v>2042001</v>
       </c>
       <c r="I152" s="4" t="s">
@@ -8788,12 +8779,12 @@
         <v>10420002</v>
       </c>
       <c r="M152" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="N152" s="59">
-        <v>3</v>
-      </c>
-      <c r="O152" s="59">
+        <v>283</v>
+      </c>
+      <c r="N152" s="57">
+        <v>3</v>
+      </c>
+      <c r="O152" s="57">
         <v>5</v>
       </c>
       <c r="Q152" s="8"/>
@@ -8809,33 +8800,33 @@
         <v>3</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="E153" s="60" t="s">
+        <v>286</v>
+      </c>
+      <c r="E153" s="58" t="s">
         <v>81</v>
       </c>
-      <c r="F153" s="61">
-        <v>1</v>
-      </c>
-      <c r="G153" s="58" t="s">
-        <v>23</v>
-      </c>
-      <c r="H153" s="57">
+      <c r="F153" s="59">
+        <v>1</v>
+      </c>
+      <c r="G153" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="H153" s="55">
         <v>2042001</v>
       </c>
-      <c r="I153" s="58" t="s">
+      <c r="I153" s="56" t="s">
         <v>24</v>
       </c>
       <c r="L153" s="43" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M153" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="N153" s="59">
-        <v>3</v>
-      </c>
-      <c r="O153" s="59">
+        <v>285</v>
+      </c>
+      <c r="N153" s="57">
+        <v>3</v>
+      </c>
+      <c r="O153" s="57">
         <v>5</v>
       </c>
       <c r="Q153" s="8"/>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="292">
   <si>
     <t>id</t>
   </si>
@@ -809,10 +809,19 @@
     <t>第1层，普通模式</t>
   </si>
   <si>
+    <t>概率改出过关图标1图标</t>
+  </si>
+  <si>
     <t>第2层，普通模式</t>
   </si>
   <si>
+    <t>概率改出过关图标2图标</t>
+  </si>
+  <si>
     <t>第3层，普通模式</t>
+  </si>
+  <si>
+    <t>概率改出过关图标3图标</t>
   </si>
   <si>
     <t>第1层，免费游戏-触发局</t>
@@ -7137,7 +7146,12 @@
       <c r="I113" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L113" s="43"/>
+      <c r="L113" s="43">
+        <v>10510007</v>
+      </c>
+      <c r="M113" s="43" t="s">
+        <v>227</v>
+      </c>
       <c r="N113" s="42">
         <v>4</v>
       </c>
@@ -7160,7 +7174,7 @@
         <v>225</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F114" s="4">
         <v>1</v>
@@ -7174,7 +7188,12 @@
       <c r="I114" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L114" s="43"/>
+      <c r="L114" s="43">
+        <v>10510008</v>
+      </c>
+      <c r="M114" s="43" t="s">
+        <v>229</v>
+      </c>
       <c r="N114" s="42">
         <v>5</v>
       </c>
@@ -7197,7 +7216,7 @@
         <v>225</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F115" s="4">
         <v>1</v>
@@ -7211,7 +7230,12 @@
       <c r="I115" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L115" s="43"/>
+      <c r="L115" s="43">
+        <v>10510009</v>
+      </c>
+      <c r="M115" s="43" t="s">
+        <v>231</v>
+      </c>
       <c r="N115" s="42">
         <v>6</v>
       </c>
@@ -7234,7 +7258,7 @@
         <v>225</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F116" s="4">
         <v>1</v>
@@ -7252,7 +7276,7 @@
         <v>10510001</v>
       </c>
       <c r="M116" s="4" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="N116" s="42">
         <v>4</v>
@@ -7276,7 +7300,7 @@
         <v>225</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F117" s="4">
         <v>1</v>
@@ -7294,7 +7318,7 @@
         <v>10510002</v>
       </c>
       <c r="M117" s="4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="N117" s="42">
         <v>5</v>
@@ -7318,7 +7342,7 @@
         <v>225</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F118" s="4">
         <v>1</v>
@@ -7336,7 +7360,7 @@
         <v>10510003</v>
       </c>
       <c r="M118" s="4" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="N118" s="42">
         <v>6</v>
@@ -7360,7 +7384,7 @@
         <v>225</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F119" s="4">
         <v>1</v>
@@ -7378,7 +7402,7 @@
         <v>10510004</v>
       </c>
       <c r="M119" s="4" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="N119" s="42">
         <v>4</v>
@@ -7402,7 +7426,7 @@
         <v>225</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F120" s="4">
         <v>1</v>
@@ -7420,7 +7444,7 @@
         <v>10510005</v>
       </c>
       <c r="M120" s="4" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="N120" s="42">
         <v>5</v>
@@ -7444,7 +7468,7 @@
         <v>225</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F121" s="4">
         <v>1</v>
@@ -7462,7 +7486,7 @@
         <v>10510006</v>
       </c>
       <c r="M121" s="4" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="N121" s="42">
         <v>6</v>
@@ -7484,7 +7508,7 @@
         <v>1</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E122" s="4" t="s">
         <v>111</v>
@@ -7502,10 +7526,10 @@
         <v>24</v>
       </c>
       <c r="L122" s="43" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M122" s="4" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N122" s="42">
         <v>6</v>
@@ -7527,7 +7551,7 @@
         <v>2</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E123" s="4" t="s">
         <v>132</v>
@@ -7545,10 +7569,10 @@
         <v>24</v>
       </c>
       <c r="L123" s="43" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M123" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="N123" s="42">
         <v>6</v>
@@ -7570,7 +7594,7 @@
         <v>3</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E124" s="4" t="s">
         <v>81</v>
@@ -7588,10 +7612,10 @@
         <v>24</v>
       </c>
       <c r="L124" s="43" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M124" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="N124" s="42">
         <v>6</v>
@@ -7613,7 +7637,7 @@
         <v>4</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E125" s="4" t="s">
         <v>222</v>
@@ -7631,7 +7655,7 @@
         <v>24</v>
       </c>
       <c r="L125" s="43" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="M125" s="4" t="s">
         <v>224</v>
@@ -7656,7 +7680,7 @@
         <v>1</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E126" s="4" t="s">
         <v>111</v>
@@ -7674,10 +7698,10 @@
         <v>24</v>
       </c>
       <c r="L126" s="43" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="M126" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N126" s="42">
         <v>6</v>
@@ -7699,7 +7723,7 @@
         <v>2</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>132</v>
@@ -7717,10 +7741,10 @@
         <v>24</v>
       </c>
       <c r="L127" s="43" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="M127" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="N127" s="42">
         <v>6</v>
@@ -7742,7 +7766,7 @@
         <v>3</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>81</v>
@@ -7760,10 +7784,10 @@
         <v>24</v>
       </c>
       <c r="L128" s="43" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M128" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="N128" s="42">
         <v>6</v>
@@ -7785,7 +7809,7 @@
         <v>1</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>22</v>
@@ -7803,10 +7827,10 @@
         <v>24</v>
       </c>
       <c r="L129" s="43" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="M129" s="4" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="N129" s="42">
         <v>5</v>
@@ -7828,7 +7852,7 @@
         <v>2</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E130" s="4" t="s">
         <v>55</v>
@@ -7849,7 +7873,7 @@
         <v>10530002</v>
       </c>
       <c r="M130" s="4" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N130" s="42">
         <v>5</v>
@@ -7871,7 +7895,7 @@
         <v>1</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E131" s="4" t="s">
         <v>22</v>
@@ -7889,10 +7913,10 @@
         <v>24</v>
       </c>
       <c r="L131" s="43" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M131" s="4" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N131" s="42">
         <v>6</v>
@@ -7914,7 +7938,7 @@
         <v>2</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E132" s="4" t="s">
         <v>55</v>
@@ -7932,10 +7956,10 @@
         <v>24</v>
       </c>
       <c r="L132" s="43" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="M132" s="4" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="N132" s="42">
         <v>6</v>
@@ -7957,7 +7981,7 @@
         <v>3</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>81</v>
@@ -7975,10 +7999,10 @@
         <v>24</v>
       </c>
       <c r="L133" s="43" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="M133" s="4" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="N133" s="42">
         <v>6</v>
@@ -8000,7 +8024,7 @@
         <v>1</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>22</v>
@@ -8021,7 +8045,7 @@
         <v>10580003</v>
       </c>
       <c r="M134" s="4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="N134" s="42">
         <v>7</v>
@@ -8043,7 +8067,7 @@
         <v>2</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>55</v>
@@ -8086,7 +8110,7 @@
         <v>3</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E136" s="4" t="s">
         <v>81</v>
@@ -8104,10 +8128,10 @@
         <v>24</v>
       </c>
       <c r="L136" s="43" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="M136" s="4" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="N136" s="42">
         <v>7</v>
@@ -8128,7 +8152,7 @@
         <v>1</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E137" s="4" t="s">
         <v>22</v>
@@ -8170,7 +8194,7 @@
         <v>2</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E138" s="4" t="s">
         <v>81</v>
@@ -8212,7 +8236,7 @@
         <v>1</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E139" s="54" t="s">
         <v>22</v>
@@ -8230,10 +8254,10 @@
         <v>24</v>
       </c>
       <c r="L139" s="4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M139" s="4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N139" s="42">
         <v>6</v>
@@ -8254,7 +8278,7 @@
         <v>2</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E140" s="54" t="s">
         <v>55</v>
@@ -8296,7 +8320,7 @@
         <v>3</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>81</v>
@@ -8314,7 +8338,7 @@
         <v>24</v>
       </c>
       <c r="L141" s="43" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="M141" s="4" t="s">
         <v>196</v>
@@ -8338,7 +8362,7 @@
         <v>1</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E142" s="4" t="s">
         <v>22</v>
@@ -8380,7 +8404,7 @@
         <v>2</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E143" s="4" t="s">
         <v>81</v>
@@ -8422,10 +8446,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E144" s="45" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F144" s="4">
         <v>1</v>
@@ -8445,7 +8469,7 @@
         <v>10550103</v>
       </c>
       <c r="M144" s="4" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="N144" s="42">
         <v>3</v>
@@ -8465,7 +8489,7 @@
         <v>1</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>22</v>
@@ -8507,7 +8531,7 @@
         <v>2</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>81</v>
@@ -8549,10 +8573,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F147" s="4">
         <v>1</v>
@@ -8570,7 +8594,7 @@
         <v>10550203</v>
       </c>
       <c r="M147" s="4" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="N147" s="42">
         <v>3</v>
@@ -8590,7 +8614,7 @@
         <v>1</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>22</v>
@@ -8608,10 +8632,10 @@
         <v>24</v>
       </c>
       <c r="L148" s="43" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="M148" s="4" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="N148" s="57">
         <v>3</v>
@@ -8632,7 +8656,7 @@
         <v>2</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E149" s="58" t="s">
         <v>55</v>
@@ -8653,7 +8677,7 @@
         <v>10410002</v>
       </c>
       <c r="M149" s="4" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="N149" s="57">
         <v>3</v>
@@ -8674,7 +8698,7 @@
         <v>3</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E150" s="58" t="s">
         <v>81</v>
@@ -8692,10 +8716,10 @@
         <v>24</v>
       </c>
       <c r="L150" s="43" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="M150" s="4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="N150" s="57">
         <v>3</v>
@@ -8716,7 +8740,7 @@
         <v>1</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E151" s="4" t="s">
         <v>22</v>
@@ -8734,10 +8758,10 @@
         <v>24</v>
       </c>
       <c r="L151" s="43" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="M151" s="4" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="N151" s="57">
         <v>3</v>
@@ -8758,7 +8782,7 @@
         <v>2</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E152" s="58" t="s">
         <v>55</v>
@@ -8779,7 +8803,7 @@
         <v>10420002</v>
       </c>
       <c r="M152" s="4" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="N152" s="57">
         <v>3</v>
@@ -8800,7 +8824,7 @@
         <v>3</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E153" s="58" t="s">
         <v>81</v>
@@ -8818,10 +8842,10 @@
         <v>24</v>
       </c>
       <c r="L153" s="43" t="s">
+        <v>291</v>
+      </c>
+      <c r="M153" s="4" t="s">
         <v>288</v>
-      </c>
-      <c r="M153" s="4" t="s">
-        <v>285</v>
       </c>
       <c r="N153" s="57">
         <v>3</v>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -704,7 +704,7 @@
     <t>热血足球</t>
   </si>
   <si>
-    <t>10160001|10160003|10160005|10160006|10160007</t>
+    <t>10160001|10160003|10160005|10160006</t>
   </si>
   <si>
     <t>概率出现wild+概率改出3个SCATTER+概率改出占据2、3、4个格子符号</t>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="302">
   <si>
     <t>id</t>
   </si>
@@ -704,7 +704,7 @@
     <t>热血足球</t>
   </si>
   <si>
-    <t>10160001|10160003|10160005|10160006|10160007</t>
+    <t>10160001|10160003|10160005|10160006</t>
   </si>
   <si>
     <t>概率出现wild+概率改出3个SCATTER+概率改出占据2、3、4个格子符号</t>
@@ -1002,6 +1002,36 @@
   </si>
   <si>
     <t>10420005|10420004</t>
+  </si>
+  <si>
+    <t>德古拉黑暗财富</t>
+  </si>
+  <si>
+    <t>10190001|10190003|10190006|10190007</t>
+  </si>
+  <si>
+    <t>概率改出wild符号+概率改出3个及以下scatter符号+概率改出占据2个格子符号+概率改出占据3个格子符号</t>
+  </si>
+  <si>
+    <t>免费模式 - 触发局</t>
+  </si>
+  <si>
+    <t>改出4个以上scatter符号</t>
+  </si>
+  <si>
+    <t>百搭赐福</t>
+  </si>
+  <si>
+    <t>10190008|10190009</t>
+  </si>
+  <si>
+    <t>改出占据2个格子白银符号+改出占据3个格子白银符号</t>
+  </si>
+  <si>
+    <t>10190004|10190010</t>
+  </si>
+  <si>
+    <t>改出3个scatter符号+改出奖池符号</t>
   </si>
 </sst>
 </file>
@@ -1853,6 +1883,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2386,7 +2419,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S153"/>
+  <dimension ref="A1:S158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -8855,6 +8888,190 @@
       </c>
       <c r="Q153" s="8"/>
     </row>
+    <row r="154" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A154" s="43">
+        <v>1019001</v>
+      </c>
+      <c r="B154" s="4">
+        <v>101900</v>
+      </c>
+      <c r="C154" s="4">
+        <v>1</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E154" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="F154" s="59">
+        <v>1</v>
+      </c>
+      <c r="G154" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="H154" s="55">
+        <v>2019001</v>
+      </c>
+      <c r="I154" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="L154" s="43" t="s">
+        <v>293</v>
+      </c>
+      <c r="M154" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="N154" s="57">
+        <v>6</v>
+      </c>
+      <c r="O154" s="57">
+        <v>6</v>
+      </c>
+      <c r="Q154" s="8"/>
+    </row>
+    <row r="155" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A155" s="43">
+        <v>1019002</v>
+      </c>
+      <c r="B155" s="4">
+        <v>101900</v>
+      </c>
+      <c r="C155" s="4">
+        <v>2</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E155" s="58" t="s">
+        <v>295</v>
+      </c>
+      <c r="F155" s="59">
+        <v>1</v>
+      </c>
+      <c r="G155" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="H155" s="55">
+        <v>2019001</v>
+      </c>
+      <c r="I155" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="L155" s="43">
+        <v>10190002</v>
+      </c>
+      <c r="M155" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="N155" s="57">
+        <v>6</v>
+      </c>
+      <c r="O155" s="57">
+        <v>6</v>
+      </c>
+      <c r="Q155" s="8"/>
+    </row>
+    <row r="156" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A156" s="43">
+        <v>1019003</v>
+      </c>
+      <c r="B156" s="4">
+        <v>101900</v>
+      </c>
+      <c r="C156" s="4">
+        <v>3</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E156" s="58" t="s">
+        <v>297</v>
+      </c>
+      <c r="F156" s="59">
+        <v>1</v>
+      </c>
+      <c r="G156" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="H156" s="55">
+        <v>2019001</v>
+      </c>
+      <c r="I156" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="L156" s="60" t="s">
+        <v>298</v>
+      </c>
+      <c r="M156" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="N156" s="57">
+        <v>6</v>
+      </c>
+      <c r="O156" s="57">
+        <v>6</v>
+      </c>
+      <c r="Q156" s="8"/>
+    </row>
+    <row r="157" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A157" s="43">
+        <v>1019004</v>
+      </c>
+      <c r="B157" s="4">
+        <v>101900</v>
+      </c>
+      <c r="C157" s="4">
+        <v>4</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E157" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="F157" s="59">
+        <v>1</v>
+      </c>
+      <c r="G157" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="H157" s="55">
+        <v>2019001</v>
+      </c>
+      <c r="I157" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="L157" s="43" t="s">
+        <v>300</v>
+      </c>
+      <c r="M157" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="N157" s="57">
+        <v>6</v>
+      </c>
+      <c r="O157" s="57">
+        <v>6</v>
+      </c>
+      <c r="Q157" s="8"/>
+    </row>
+    <row r="158" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A158" s="43"/>
+      <c r="B158" s="4"/>
+      <c r="C158" s="4"/>
+      <c r="D158" s="4"/>
+      <c r="E158" s="58"/>
+      <c r="F158" s="59"/>
+      <c r="G158" s="56"/>
+      <c r="H158" s="55"/>
+      <c r="I158" s="56"/>
+      <c r="L158" s="43"/>
+      <c r="M158" s="4"/>
+      <c r="N158" s="57"/>
+      <c r="O158" s="57"/>
+      <c r="Q158" s="8"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="J2:L2">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -8590,9 +8590,7 @@
       <c r="I147" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L147" s="43">
-        <v>10550203</v>
-      </c>
+      <c r="L147" s="43"/>
       <c r="M147" s="4" t="s">
         <v>282</v>
       </c>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="299">
   <si>
     <t>id</t>
   </si>
@@ -914,22 +914,13 @@
     <t>赏金大对决</t>
   </si>
   <si>
-    <t>10570001|10570004|10570006</t>
-  </si>
-  <si>
-    <t>概率改出scatter符号+概率改出金框符号+异形位置改为不中奖图案</t>
-  </si>
-  <si>
-    <t>10570002|10570006</t>
-  </si>
-  <si>
-    <t>改出3个以上SCATTER+异形位置改为不中奖图案</t>
-  </si>
-  <si>
-    <t>10570001|10570005|10570006</t>
-  </si>
-  <si>
-    <t>改出2个SCATTER+奖池符号+异形位置改为不中奖图案</t>
+    <t>10570001|10570004</t>
+  </si>
+  <si>
+    <t>概率改出scatter符号+概率改出金框符号</t>
+  </si>
+  <si>
+    <t>10570001|10570005</t>
   </si>
   <si>
     <t>极速糖果1000</t>
@@ -7988,11 +7979,11 @@
       <c r="I132" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L132" s="43" t="s">
-        <v>264</v>
+      <c r="L132" s="43">
+        <v>10570002</v>
       </c>
       <c r="M132" s="4" t="s">
-        <v>265</v>
+        <v>102</v>
       </c>
       <c r="N132" s="42">
         <v>6</v>
@@ -8032,10 +8023,10 @@
         <v>24</v>
       </c>
       <c r="L133" s="43" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="M133" s="4" t="s">
-        <v>267</v>
+        <v>203</v>
       </c>
       <c r="N133" s="42">
         <v>6</v>
@@ -8057,7 +8048,7 @@
         <v>1</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>22</v>
@@ -8078,7 +8069,7 @@
         <v>10580003</v>
       </c>
       <c r="M134" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="N134" s="42">
         <v>7</v>
@@ -8100,7 +8091,7 @@
         <v>2</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>55</v>
@@ -8143,7 +8134,7 @@
         <v>3</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E136" s="4" t="s">
         <v>81</v>
@@ -8161,10 +8152,10 @@
         <v>24</v>
       </c>
       <c r="L136" s="43" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="M136" s="4" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="N136" s="42">
         <v>7</v>
@@ -8185,7 +8176,7 @@
         <v>1</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E137" s="4" t="s">
         <v>22</v>
@@ -8227,7 +8218,7 @@
         <v>2</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E138" s="4" t="s">
         <v>81</v>
@@ -8269,7 +8260,7 @@
         <v>1</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E139" s="54" t="s">
         <v>22</v>
@@ -8287,10 +8278,10 @@
         <v>24</v>
       </c>
       <c r="L139" s="4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M139" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="N139" s="42">
         <v>6</v>
@@ -8311,7 +8302,7 @@
         <v>2</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E140" s="54" t="s">
         <v>55</v>
@@ -8353,7 +8344,7 @@
         <v>3</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>81</v>
@@ -8371,7 +8362,7 @@
         <v>24</v>
       </c>
       <c r="L141" s="43" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="M141" s="4" t="s">
         <v>196</v>
@@ -8395,7 +8386,7 @@
         <v>1</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E142" s="4" t="s">
         <v>22</v>
@@ -8437,7 +8428,7 @@
         <v>2</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E143" s="4" t="s">
         <v>81</v>
@@ -8479,10 +8470,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E144" s="45" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F144" s="4">
         <v>1</v>
@@ -8502,7 +8493,7 @@
         <v>10550103</v>
       </c>
       <c r="M144" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="N144" s="42">
         <v>3</v>
@@ -8522,7 +8513,7 @@
         <v>1</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>22</v>
@@ -8564,7 +8555,7 @@
         <v>2</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>81</v>
@@ -8606,10 +8597,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F147" s="4">
         <v>1</v>
@@ -8623,11 +8614,9 @@
       <c r="I147" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L147" s="43">
-        <v>10550203</v>
-      </c>
+      <c r="L147" s="43"/>
       <c r="M147" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="N147" s="42">
         <v>3</v>
@@ -8647,7 +8636,7 @@
         <v>1</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>22</v>
@@ -8665,10 +8654,10 @@
         <v>24</v>
       </c>
       <c r="L148" s="43" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="M148" s="4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="N148" s="57">
         <v>3</v>
@@ -8689,7 +8678,7 @@
         <v>2</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E149" s="58" t="s">
         <v>55</v>
@@ -8710,7 +8699,7 @@
         <v>10410002</v>
       </c>
       <c r="M149" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="N149" s="57">
         <v>3</v>
@@ -8731,7 +8720,7 @@
         <v>3</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E150" s="58" t="s">
         <v>81</v>
@@ -8749,10 +8738,10 @@
         <v>24</v>
       </c>
       <c r="L150" s="43" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="M150" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N150" s="57">
         <v>3</v>
@@ -8773,7 +8762,7 @@
         <v>1</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E151" s="4" t="s">
         <v>22</v>
@@ -8791,10 +8780,10 @@
         <v>24</v>
       </c>
       <c r="L151" s="43" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="M151" s="4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="N151" s="57">
         <v>3</v>
@@ -8815,7 +8804,7 @@
         <v>2</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E152" s="58" t="s">
         <v>55</v>
@@ -8836,7 +8825,7 @@
         <v>10420002</v>
       </c>
       <c r="M152" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="N152" s="57">
         <v>3</v>
@@ -8857,7 +8846,7 @@
         <v>3</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E153" s="58" t="s">
         <v>81</v>
@@ -8875,10 +8864,10 @@
         <v>24</v>
       </c>
       <c r="L153" s="43" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="M153" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N153" s="57">
         <v>3</v>
@@ -8899,7 +8888,7 @@
         <v>1</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E154" s="58" t="s">
         <v>111</v>
@@ -8917,10 +8906,10 @@
         <v>24</v>
       </c>
       <c r="L154" s="43" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="M154" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="N154" s="57">
         <v>6</v>
@@ -8941,10 +8930,10 @@
         <v>2</v>
       </c>
       <c r="D155" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="E155" s="58" t="s">
         <v>292</v>
-      </c>
-      <c r="E155" s="58" t="s">
-        <v>295</v>
       </c>
       <c r="F155" s="59">
         <v>1</v>
@@ -8962,7 +8951,7 @@
         <v>10190002</v>
       </c>
       <c r="M155" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="N155" s="57">
         <v>6</v>
@@ -8983,10 +8972,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E156" s="58" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F156" s="59">
         <v>1</v>
@@ -9001,10 +8990,10 @@
         <v>24</v>
       </c>
       <c r="L156" s="60" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="M156" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="N156" s="57">
         <v>6</v>
@@ -9025,7 +9014,7 @@
         <v>4</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E157" s="58" t="s">
         <v>81</v>
@@ -9043,10 +9032,10 @@
         <v>24</v>
       </c>
       <c r="L157" s="43" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="M157" s="4" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="N157" s="57">
         <v>6</v>
